--- a/output/2024-08-25.xlsx
+++ b/output/2024-08-25.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="F14" t="n">
-        <v>5.53</v>
+        <v>5.26</v>
       </c>
       <c r="G14" t="n">
-        <v>240.6</v>
+        <v>228.5</v>
       </c>
       <c r="H14" t="n">
-        <v>19.9</v>
+        <v>12.1</v>
       </c>
       <c r="I14" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J14" t="n">
-        <v>-26.59</v>
+        <v>40.33</v>
       </c>
       <c r="K14" t="n">
-        <v>62.57</v>
+        <v>-44.27</v>
       </c>
       <c r="L14" t="n">
-        <v>67.98</v>
+        <v>59.89</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:08:15</t>
+          <t>06:07:25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="F15" t="n">
-        <v>5.09</v>
+        <v>4.8</v>
       </c>
       <c r="G15" t="n">
-        <v>233.2</v>
+        <v>240.2</v>
       </c>
       <c r="H15" t="n">
-        <v>17.3</v>
+        <v>11.6</v>
       </c>
       <c r="I15" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J15" t="n">
-        <v>59.59</v>
+        <v>-32.47</v>
       </c>
       <c r="K15" t="n">
-        <v>-10</v>
+        <v>108.08</v>
       </c>
       <c r="L15" t="n">
-        <v>60.42</v>
+        <v>112.85</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:09:24</t>
+          <t>06:08:54</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.79</v>
+        <v>1.4</v>
       </c>
       <c r="F16" t="n">
-        <v>5.16</v>
+        <v>5.51</v>
       </c>
       <c r="G16" t="n">
-        <v>233.9</v>
+        <v>229.5</v>
       </c>
       <c r="H16" t="n">
-        <v>14.1</v>
+        <v>9.4</v>
       </c>
       <c r="I16" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J16" t="n">
-        <v>-10.97</v>
+        <v>57.41</v>
       </c>
       <c r="K16" t="n">
-        <v>-115.92</v>
+        <v>15.47</v>
       </c>
       <c r="L16" t="n">
-        <v>116.44</v>
+        <v>59.46</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:13:37</t>
+          <t>06:14:10</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="F17" t="n">
-        <v>4.84</v>
+        <v>5.45</v>
       </c>
       <c r="G17" t="n">
-        <v>227.4</v>
+        <v>241.1</v>
       </c>
       <c r="H17" t="n">
-        <v>2.7</v>
+        <v>12.6</v>
       </c>
       <c r="I17" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>-61.08</v>
+        <v>-48.95</v>
       </c>
       <c r="K17" t="n">
-        <v>57.91</v>
+        <v>-54.07</v>
       </c>
       <c r="L17" t="n">
-        <v>84.17</v>
+        <v>72.94</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:15:20</t>
+          <t>06:15:15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="F18" t="n">
-        <v>5.77</v>
+        <v>5.47</v>
       </c>
       <c r="G18" t="n">
-        <v>232.4</v>
+        <v>230.4</v>
       </c>
       <c r="H18" t="n">
-        <v>21.6</v>
+        <v>10.8</v>
       </c>
       <c r="I18" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J18" t="n">
-        <v>174.83</v>
+        <v>-146.24</v>
       </c>
       <c r="K18" t="n">
-        <v>-148.22</v>
+        <v>-79.55</v>
       </c>
       <c r="L18" t="n">
-        <v>229.21</v>
+        <v>166.47</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:17:36</t>
+          <t>06:17:40</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.51</v>
+        <v>1.28</v>
       </c>
       <c r="F19" t="n">
-        <v>6.17</v>
+        <v>5.24</v>
       </c>
       <c r="G19" t="n">
-        <v>231.5</v>
+        <v>219.8</v>
       </c>
       <c r="H19" t="n">
-        <v>17.4</v>
+        <v>11.5</v>
       </c>
       <c r="I19" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>-62.84</v>
+        <v>68.38</v>
       </c>
       <c r="K19" t="n">
-        <v>-66.70999999999999</v>
+        <v>42.71</v>
       </c>
       <c r="L19" t="n">
-        <v>91.64</v>
+        <v>80.62</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:23:43</t>
+          <t>06:22:59</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="F20" t="n">
-        <v>6.5</v>
+        <v>5.1</v>
       </c>
       <c r="G20" t="n">
-        <v>220.4</v>
+        <v>225.7</v>
       </c>
       <c r="H20" t="n">
-        <v>9.699999999999999</v>
+        <v>5.3</v>
       </c>
       <c r="I20" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-162.28</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>138.6</v>
+        <v>43.4</v>
       </c>
       <c r="L20" t="n">
-        <v>213.41</v>
+        <v>96.59</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:25:19</t>
+          <t>06:24:34</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1.22</v>
+        <v>1.74</v>
       </c>
       <c r="F21" t="n">
-        <v>6.01</v>
+        <v>5.3</v>
       </c>
       <c r="G21" t="n">
-        <v>223.1</v>
+        <v>230.7</v>
       </c>
       <c r="H21" t="n">
-        <v>14.4</v>
+        <v>17.7</v>
       </c>
       <c r="I21" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J21" t="n">
-        <v>-59.54</v>
+        <v>87.39</v>
       </c>
       <c r="K21" t="n">
-        <v>-75.2</v>
+        <v>-34.93</v>
       </c>
       <c r="L21" t="n">
-        <v>95.92</v>
+        <v>94.11</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:27:25</t>
+          <t>06:25:57</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>1.69</v>
+        <v>1.41</v>
       </c>
       <c r="F22" t="n">
-        <v>5.11</v>
+        <v>5.67</v>
       </c>
       <c r="G22" t="n">
-        <v>223.7</v>
+        <v>229.6</v>
       </c>
       <c r="H22" t="n">
-        <v>16.4</v>
+        <v>14.3</v>
       </c>
       <c r="I22" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>29.89</v>
+        <v>63.87</v>
       </c>
       <c r="K22" t="n">
-        <v>51.11</v>
+        <v>105.12</v>
       </c>
       <c r="L22" t="n">
-        <v>59.2</v>
+        <v>123</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:30:17</t>
+          <t>06:30:45</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="F23" t="n">
-        <v>4.98</v>
+        <v>5.52</v>
       </c>
       <c r="G23" t="n">
-        <v>225.4</v>
+        <v>219.5</v>
       </c>
       <c r="H23" t="n">
-        <v>17.2</v>
+        <v>20.7</v>
       </c>
       <c r="I23" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J23" t="n">
-        <v>124.53</v>
+        <v>-23.36</v>
       </c>
       <c r="K23" t="n">
-        <v>-322.31</v>
+        <v>-106.05</v>
       </c>
       <c r="L23" t="n">
-        <v>345.53</v>
+        <v>108.59</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:31:55</t>
+          <t>06:32:47</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="F24" t="n">
-        <v>4.87</v>
+        <v>5.96</v>
       </c>
       <c r="G24" t="n">
-        <v>245.2</v>
+        <v>229.2</v>
       </c>
       <c r="H24" t="n">
-        <v>14.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J24" t="n">
-        <v>117.77</v>
+        <v>-135.93</v>
       </c>
       <c r="K24" t="n">
-        <v>389.95</v>
+        <v>124.64</v>
       </c>
       <c r="L24" t="n">
-        <v>407.35</v>
+        <v>184.42</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:33:34</t>
+          <t>06:34:31</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>1.63</v>
+        <v>2.3</v>
       </c>
       <c r="F25" t="n">
-        <v>5.94</v>
+        <v>5.26</v>
       </c>
       <c r="G25" t="n">
-        <v>225.3</v>
+        <v>224.3</v>
       </c>
       <c r="H25" t="n">
-        <v>12.5</v>
+        <v>11.4</v>
       </c>
       <c r="I25" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.93</v>
+        <v>-357.99</v>
       </c>
       <c r="K25" t="n">
-        <v>-163.69</v>
+        <v>-255.22</v>
       </c>
       <c r="L25" t="n">
-        <v>163.72</v>
+        <v>439.65</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:37:57</t>
+          <t>06:39:28</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1.63</v>
+        <v>1.32</v>
       </c>
       <c r="F26" t="n">
-        <v>5.11</v>
+        <v>4.75</v>
       </c>
       <c r="G26" t="n">
-        <v>240.2</v>
+        <v>226.8</v>
       </c>
       <c r="H26" t="n">
-        <v>17.1</v>
+        <v>11</v>
       </c>
       <c r="I26" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="J26" t="n">
-        <v>83.47</v>
+        <v>192.24</v>
       </c>
       <c r="K26" t="n">
-        <v>280.17</v>
+        <v>48.93</v>
       </c>
       <c r="L26" t="n">
-        <v>292.34</v>
+        <v>198.37</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:39:58</t>
+          <t>06:40:31</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.78</v>
+        <v>1.54</v>
       </c>
       <c r="F27" t="n">
-        <v>6</v>
+        <v>5.66</v>
       </c>
       <c r="G27" t="n">
-        <v>233.6</v>
+        <v>221.5</v>
       </c>
       <c r="H27" t="n">
-        <v>8.1</v>
+        <v>14.1</v>
       </c>
       <c r="I27" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>142.58</v>
+        <v>-161.62</v>
       </c>
       <c r="K27" t="n">
-        <v>95.02</v>
+        <v>186.8</v>
       </c>
       <c r="L27" t="n">
-        <v>171.34</v>
+        <v>247.01</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:41:54</t>
+          <t>06:41:28</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>1.35</v>
+        <v>1.54</v>
       </c>
       <c r="F28" t="n">
-        <v>5.13</v>
+        <v>5.71</v>
       </c>
       <c r="G28" t="n">
-        <v>233.4</v>
+        <v>220.7</v>
       </c>
       <c r="H28" t="n">
-        <v>16.2</v>
+        <v>21.6</v>
       </c>
       <c r="I28" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>245.52</v>
+        <v>-252.74</v>
       </c>
       <c r="K28" t="n">
-        <v>-125.89</v>
+        <v>-156.73</v>
       </c>
       <c r="L28" t="n">
-        <v>275.91</v>
+        <v>297.4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:52:11</t>
+          <t>06:53:26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="F29" t="n">
-        <v>5</v>
+        <v>4.64</v>
       </c>
       <c r="G29" t="n">
-        <v>220.3</v>
+        <v>236.1</v>
       </c>
       <c r="H29" t="n">
-        <v>11.8</v>
+        <v>12.7</v>
       </c>
       <c r="I29" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J29" t="n">
-        <v>36.86</v>
+        <v>37.65</v>
       </c>
       <c r="K29" t="n">
-        <v>-65.31</v>
+        <v>31.14</v>
       </c>
       <c r="L29" t="n">
-        <v>75</v>
+        <v>48.86</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06:54:08</t>
+          <t>06:55:19</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="F30" t="n">
-        <v>5.51</v>
+        <v>5</v>
       </c>
       <c r="G30" t="n">
-        <v>240.1</v>
+        <v>229</v>
       </c>
       <c r="H30" t="n">
-        <v>11.9</v>
+        <v>18.8</v>
       </c>
       <c r="I30" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>28</v>
+        <v>100.83</v>
       </c>
       <c r="K30" t="n">
-        <v>-78.02</v>
+        <v>-52.49</v>
       </c>
       <c r="L30" t="n">
-        <v>82.90000000000001</v>
+        <v>113.68</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06:56:41</t>
+          <t>06:57:38</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="F31" t="n">
-        <v>5.5</v>
+        <v>5.01</v>
       </c>
       <c r="G31" t="n">
-        <v>241.1</v>
+        <v>232.9</v>
       </c>
       <c r="H31" t="n">
-        <v>15</v>
+        <v>6.5</v>
       </c>
       <c r="I31" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>59.18</v>
+        <v>-104.66</v>
       </c>
       <c r="K31" t="n">
-        <v>-43.51</v>
+        <v>71.3</v>
       </c>
       <c r="L31" t="n">
-        <v>73.45</v>
+        <v>126.64</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:01:03</t>
+          <t>07:02:03</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1.61</v>
+        <v>1.45</v>
       </c>
       <c r="F32" t="n">
-        <v>5.2</v>
+        <v>5.52</v>
       </c>
       <c r="G32" t="n">
-        <v>235.8</v>
+        <v>230.7</v>
       </c>
       <c r="H32" t="n">
-        <v>14.8</v>
+        <v>15.8</v>
       </c>
       <c r="I32" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>-142.71</v>
+        <v>11.52</v>
       </c>
       <c r="K32" t="n">
-        <v>29.56</v>
+        <v>-71.51000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>145.73</v>
+        <v>72.43000000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:03:13</t>
+          <t>07:03:44</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="F33" t="n">
-        <v>4.95</v>
+        <v>5.54</v>
       </c>
       <c r="G33" t="n">
-        <v>228.1</v>
+        <v>238.2</v>
       </c>
       <c r="H33" t="n">
-        <v>16.1</v>
+        <v>15.2</v>
       </c>
       <c r="I33" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>-47.57</v>
+        <v>-165.85</v>
       </c>
       <c r="K33" t="n">
-        <v>-70.98999999999999</v>
+        <v>-58.78</v>
       </c>
       <c r="L33" t="n">
-        <v>85.45</v>
+        <v>175.96</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:05:17</t>
+          <t>07:05:57</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>1.7</v>
+        <v>1.37</v>
       </c>
       <c r="F34" t="n">
-        <v>5.27</v>
+        <v>6.14</v>
       </c>
       <c r="G34" t="n">
-        <v>236.4</v>
+        <v>230.1</v>
       </c>
       <c r="H34" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="I34" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J34" t="n">
-        <v>-177.11</v>
+        <v>139.42</v>
       </c>
       <c r="K34" t="n">
-        <v>-77.76000000000001</v>
+        <v>51.79</v>
       </c>
       <c r="L34" t="n">
-        <v>193.42</v>
+        <v>148.73</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:10:58</t>
+          <t>07:10:32</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>1.45</v>
+        <v>1.79</v>
       </c>
       <c r="F35" t="n">
-        <v>5.13</v>
+        <v>5.15</v>
       </c>
       <c r="G35" t="n">
-        <v>231.7</v>
+        <v>229.3</v>
       </c>
       <c r="H35" t="n">
-        <v>14.1</v>
+        <v>11.7</v>
       </c>
       <c r="I35" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>-81.88</v>
+        <v>54.49</v>
       </c>
       <c r="K35" t="n">
-        <v>-100.33</v>
+        <v>-146.95</v>
       </c>
       <c r="L35" t="n">
-        <v>129.5</v>
+        <v>156.72</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:13:19</t>
+          <t>07:13:03</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>1.63</v>
+        <v>1.35</v>
       </c>
       <c r="F36" t="n">
-        <v>5.81</v>
+        <v>5.31</v>
       </c>
       <c r="G36" t="n">
-        <v>217.7</v>
+        <v>221.5</v>
       </c>
       <c r="H36" t="n">
-        <v>6.6</v>
+        <v>12.6</v>
       </c>
       <c r="I36" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J36" t="n">
-        <v>-111.64</v>
+        <v>66.41</v>
       </c>
       <c r="K36" t="n">
-        <v>-52.46</v>
+        <v>-82.44</v>
       </c>
       <c r="L36" t="n">
-        <v>123.36</v>
+        <v>105.86</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:15:12</t>
+          <t>07:14:57</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="F37" t="n">
-        <v>5.37</v>
+        <v>5.88</v>
       </c>
       <c r="G37" t="n">
-        <v>245.1</v>
+        <v>232.2</v>
       </c>
       <c r="H37" t="n">
-        <v>15.7</v>
+        <v>17.1</v>
       </c>
       <c r="I37" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>-63.25</v>
+        <v>-60.36</v>
       </c>
       <c r="K37" t="n">
-        <v>41.64</v>
+        <v>173.37</v>
       </c>
       <c r="L37" t="n">
-        <v>75.73</v>
+        <v>183.57</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:20:56</t>
+          <t>07:18:51</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="F38" t="n">
-        <v>5.52</v>
+        <v>5.01</v>
       </c>
       <c r="G38" t="n">
-        <v>240.8</v>
+        <v>213.6</v>
       </c>
       <c r="H38" t="n">
-        <v>16.1</v>
+        <v>16.3</v>
       </c>
       <c r="I38" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>286.28</v>
+        <v>-276.29</v>
       </c>
       <c r="K38" t="n">
-        <v>-300.08</v>
+        <v>126.57</v>
       </c>
       <c r="L38" t="n">
-        <v>414.74</v>
+        <v>303.9</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:22:23</t>
+          <t>07:20:58</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>1.56</v>
+        <v>1.98</v>
       </c>
       <c r="F39" t="n">
-        <v>5.45</v>
+        <v>5.39</v>
       </c>
       <c r="G39" t="n">
-        <v>227.3</v>
+        <v>231.1</v>
       </c>
       <c r="H39" t="n">
-        <v>12.4</v>
+        <v>19.4</v>
       </c>
       <c r="I39" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>257.21</v>
+        <v>96.36</v>
       </c>
       <c r="K39" t="n">
-        <v>77.13</v>
+        <v>166.15</v>
       </c>
       <c r="L39" t="n">
-        <v>268.52</v>
+        <v>192.07</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:24:02</t>
+          <t>07:22:34</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="F40" t="n">
-        <v>4.3</v>
+        <v>5.76</v>
       </c>
       <c r="G40" t="n">
-        <v>231.2</v>
+        <v>216.7</v>
       </c>
       <c r="H40" t="n">
-        <v>20.5</v>
+        <v>13.3</v>
       </c>
       <c r="I40" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J40" t="n">
-        <v>-117.99</v>
+        <v>93.81</v>
       </c>
       <c r="K40" t="n">
-        <v>81.18000000000001</v>
+        <v>113.72</v>
       </c>
       <c r="L40" t="n">
-        <v>143.22</v>
+        <v>147.42</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:28:47</t>
+          <t>07:26:33</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="F41" t="n">
-        <v>5.74</v>
+        <v>5.37</v>
       </c>
       <c r="G41" t="n">
-        <v>225.3</v>
+        <v>246.4</v>
       </c>
       <c r="H41" t="n">
-        <v>12.3</v>
+        <v>17.3</v>
       </c>
       <c r="I41" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>128.5</v>
+        <v>171.89</v>
       </c>
       <c r="K41" t="n">
-        <v>176.25</v>
+        <v>-187.1</v>
       </c>
       <c r="L41" t="n">
-        <v>218.12</v>
+        <v>254.07</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:30:03</t>
+          <t>07:27:24</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="F42" t="n">
-        <v>6.05</v>
+        <v>5.07</v>
       </c>
       <c r="G42" t="n">
-        <v>236.8</v>
+        <v>232</v>
       </c>
       <c r="H42" t="n">
-        <v>20.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J42" t="n">
-        <v>-347.15</v>
+        <v>29.91</v>
       </c>
       <c r="K42" t="n">
-        <v>143.35</v>
+        <v>-590.79</v>
       </c>
       <c r="L42" t="n">
-        <v>375.59</v>
+        <v>591.55</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:32:52</t>
+          <t>07:28:42</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="F43" t="n">
-        <v>5.39</v>
+        <v>5.12</v>
       </c>
       <c r="G43" t="n">
-        <v>209.4</v>
+        <v>235.4</v>
       </c>
       <c r="H43" t="n">
-        <v>19</v>
+        <v>15.1</v>
       </c>
       <c r="I43" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>-304.15</v>
+        <v>-30.81</v>
       </c>
       <c r="K43" t="n">
-        <v>-254.73</v>
+        <v>-133.02</v>
       </c>
       <c r="L43" t="n">
-        <v>396.73</v>
+        <v>136.54</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:45:37</t>
+          <t>07:37:11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="F44" t="n">
-        <v>4.89</v>
+        <v>5.79</v>
       </c>
       <c r="G44" t="n">
-        <v>241.1</v>
+        <v>222.8</v>
       </c>
       <c r="H44" t="n">
-        <v>11.9</v>
+        <v>8.6</v>
       </c>
       <c r="I44" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>15.7</v>
+        <v>-16.34</v>
       </c>
       <c r="K44" t="n">
-        <v>-64.55</v>
+        <v>74.56</v>
       </c>
       <c r="L44" t="n">
-        <v>66.43000000000001</v>
+        <v>76.33</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:46:21</t>
+          <t>07:39:06</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="F45" t="n">
-        <v>5.75</v>
+        <v>4.78</v>
       </c>
       <c r="G45" t="n">
-        <v>237.8</v>
+        <v>227.4</v>
       </c>
       <c r="H45" t="n">
-        <v>16.8</v>
+        <v>14.5</v>
       </c>
       <c r="I45" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>-31.65</v>
+        <v>12.6</v>
       </c>
       <c r="K45" t="n">
-        <v>12.94</v>
+        <v>30.95</v>
       </c>
       <c r="L45" t="n">
-        <v>34.19</v>
+        <v>33.42</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:48:48</t>
+          <t>07:41:30</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>1.45</v>
+        <v>1.73</v>
       </c>
       <c r="F46" t="n">
         <v>5.86</v>
       </c>
       <c r="G46" t="n">
-        <v>241.5</v>
+        <v>236.7</v>
       </c>
       <c r="H46" t="n">
-        <v>15</v>
+        <v>14.7</v>
       </c>
       <c r="I46" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J46" t="n">
-        <v>-82.88</v>
+        <v>31.31</v>
       </c>
       <c r="K46" t="n">
-        <v>-48.18</v>
+        <v>-108.71</v>
       </c>
       <c r="L46" t="n">
-        <v>95.87</v>
+        <v>113.13</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:52:32</t>
+          <t>07:45:18</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="F47" t="n">
-        <v>5.43</v>
+        <v>5.38</v>
       </c>
       <c r="G47" t="n">
-        <v>238.9</v>
+        <v>221.8</v>
       </c>
       <c r="H47" t="n">
-        <v>16.4</v>
+        <v>18</v>
       </c>
       <c r="I47" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J47" t="n">
-        <v>58.77</v>
+        <v>80.45</v>
       </c>
       <c r="K47" t="n">
-        <v>-35.61</v>
+        <v>-153.33</v>
       </c>
       <c r="L47" t="n">
-        <v>68.72</v>
+        <v>173.16</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:54:25</t>
+          <t>07:46:57</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>1.66</v>
+        <v>1.28</v>
       </c>
       <c r="F48" t="n">
-        <v>4.86</v>
+        <v>5.64</v>
       </c>
       <c r="G48" t="n">
-        <v>237.1</v>
+        <v>230.7</v>
       </c>
       <c r="H48" t="n">
-        <v>10.5</v>
+        <v>3.4</v>
       </c>
       <c r="I48" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="J48" t="n">
-        <v>-120.33</v>
+        <v>-53.74</v>
       </c>
       <c r="K48" t="n">
-        <v>-129.91</v>
+        <v>12.8</v>
       </c>
       <c r="L48" t="n">
-        <v>177.07</v>
+        <v>55.24</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:55:17</t>
+          <t>07:49:13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="F49" t="n">
-        <v>5.52</v>
+        <v>5.46</v>
       </c>
       <c r="G49" t="n">
-        <v>236.7</v>
+        <v>224.6</v>
       </c>
       <c r="H49" t="n">
-        <v>10.9</v>
+        <v>14.6</v>
       </c>
       <c r="I49" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>-92.66</v>
+        <v>73.55</v>
       </c>
       <c r="K49" t="n">
-        <v>39.52</v>
+        <v>-36.17</v>
       </c>
       <c r="L49" t="n">
-        <v>100.73</v>
+        <v>81.95999999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:00:13</t>
+          <t>07:54:26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="F50" t="n">
-        <v>5.83</v>
+        <v>5.04</v>
       </c>
       <c r="G50" t="n">
-        <v>228.1</v>
+        <v>230.8</v>
       </c>
       <c r="H50" t="n">
-        <v>8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I50" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>9.6</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="K50" t="n">
-        <v>8.42</v>
+        <v>-115.03</v>
       </c>
       <c r="L50" t="n">
-        <v>12.77</v>
+        <v>140.83</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:00:51</t>
+          <t>07:55:59</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2182,31 +2182,31 @@
         <v>1.72</v>
       </c>
       <c r="F51" t="n">
-        <v>4.96</v>
+        <v>5.61</v>
       </c>
       <c r="G51" t="n">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="H51" t="n">
-        <v>6.5</v>
+        <v>11.1</v>
       </c>
       <c r="I51" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>-250.35</v>
+        <v>115.88</v>
       </c>
       <c r="K51" t="n">
-        <v>-158.67</v>
+        <v>-133.51</v>
       </c>
       <c r="L51" t="n">
-        <v>296.4</v>
+        <v>176.78</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:02:45</t>
+          <t>07:58:16</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.15</v>
+        <v>1.62</v>
       </c>
       <c r="F52" t="n">
-        <v>5.24</v>
+        <v>4.97</v>
       </c>
       <c r="G52" t="n">
-        <v>223</v>
+        <v>225.8</v>
       </c>
       <c r="H52" t="n">
-        <v>17.1</v>
+        <v>5.8</v>
       </c>
       <c r="I52" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>-8.33</v>
+        <v>-64.5</v>
       </c>
       <c r="K52" t="n">
-        <v>-33.31</v>
+        <v>80</v>
       </c>
       <c r="L52" t="n">
-        <v>34.34</v>
+        <v>102.76</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:07:49</t>
+          <t>08:03:38</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1.88</v>
+        <v>1.74</v>
       </c>
       <c r="F53" t="n">
-        <v>5.62</v>
+        <v>6.37</v>
       </c>
       <c r="G53" t="n">
-        <v>231.7</v>
+        <v>235.3</v>
       </c>
       <c r="H53" t="n">
-        <v>18.3</v>
+        <v>13.5</v>
       </c>
       <c r="I53" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>26.18</v>
+        <v>-189.46</v>
       </c>
       <c r="K53" t="n">
-        <v>-214.46</v>
+        <v>-23.19</v>
       </c>
       <c r="L53" t="n">
-        <v>216.05</v>
+        <v>190.87</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:09:22</t>
+          <t>08:04:55</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="F54" t="n">
-        <v>5.07</v>
+        <v>5.62</v>
       </c>
       <c r="G54" t="n">
-        <v>232.4</v>
+        <v>211.2</v>
       </c>
       <c r="H54" t="n">
-        <v>13.1</v>
+        <v>15.4</v>
       </c>
       <c r="I54" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>214.45</v>
+        <v>-26.39</v>
       </c>
       <c r="K54" t="n">
-        <v>-218.74</v>
+        <v>260.8</v>
       </c>
       <c r="L54" t="n">
-        <v>306.33</v>
+        <v>262.13</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:11:36</t>
+          <t>08:07:14</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="F55" t="n">
-        <v>5.39</v>
+        <v>5.94</v>
       </c>
       <c r="G55" t="n">
-        <v>244.2</v>
+        <v>216.5</v>
       </c>
       <c r="H55" t="n">
-        <v>13.4</v>
+        <v>14.2</v>
       </c>
       <c r="I55" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>-21.66</v>
+        <v>-101.6</v>
       </c>
       <c r="K55" t="n">
-        <v>-459.57</v>
+        <v>-64.3</v>
       </c>
       <c r="L55" t="n">
-        <v>460.08</v>
+        <v>120.24</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:15:02</t>
+          <t>08:11:18</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="F56" t="n">
-        <v>5.51</v>
+        <v>5.67</v>
       </c>
       <c r="G56" t="n">
-        <v>249.1</v>
+        <v>224.6</v>
       </c>
       <c r="H56" t="n">
-        <v>14.4</v>
+        <v>14.2</v>
       </c>
       <c r="I56" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>-8.49</v>
+        <v>386.55</v>
       </c>
       <c r="K56" t="n">
-        <v>-15.57</v>
+        <v>-66.3</v>
       </c>
       <c r="L56" t="n">
-        <v>17.74</v>
+        <v>392.2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:16:57</t>
+          <t>08:13:27</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="F57" t="n">
-        <v>5.46</v>
+        <v>6.08</v>
       </c>
       <c r="G57" t="n">
-        <v>221.3</v>
+        <v>223.9</v>
       </c>
       <c r="H57" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="I57" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>43.93</v>
+        <v>-339.19</v>
       </c>
       <c r="K57" t="n">
-        <v>9.880000000000001</v>
+        <v>-195.36</v>
       </c>
       <c r="L57" t="n">
-        <v>45.02</v>
+        <v>391.43</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:18:21</t>
+          <t>08:15:27</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="F58" t="n">
-        <v>6.28</v>
+        <v>4.85</v>
       </c>
       <c r="G58" t="n">
-        <v>236.4</v>
+        <v>235.1</v>
       </c>
       <c r="H58" t="n">
-        <v>5.6</v>
+        <v>13.1</v>
       </c>
       <c r="I58" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>345.55</v>
+        <v>355.86</v>
       </c>
       <c r="K58" t="n">
-        <v>-14.52</v>
+        <v>114.05</v>
       </c>
       <c r="L58" t="n">
-        <v>345.86</v>
+        <v>373.69</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:27:20</t>
+          <t>08:25:48</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="F59" t="n">
-        <v>5.77</v>
+        <v>5.41</v>
       </c>
       <c r="G59" t="n">
-        <v>236.7</v>
+        <v>231.3</v>
       </c>
       <c r="H59" t="n">
-        <v>15</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>-61.1</v>
+        <v>-43.99</v>
       </c>
       <c r="K59" t="n">
-        <v>68.62</v>
+        <v>-37.53</v>
       </c>
       <c r="L59" t="n">
-        <v>91.88</v>
+        <v>57.82</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:27:54</t>
+          <t>08:27:10</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="F60" t="n">
-        <v>4.99</v>
+        <v>5.09</v>
       </c>
       <c r="G60" t="n">
-        <v>233.2</v>
+        <v>222.5</v>
       </c>
       <c r="H60" t="n">
-        <v>13.4</v>
+        <v>11.8</v>
       </c>
       <c r="I60" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J60" t="n">
-        <v>56.92</v>
+        <v>-62.37</v>
       </c>
       <c r="K60" t="n">
-        <v>-18.69</v>
+        <v>-57.42</v>
       </c>
       <c r="L60" t="n">
-        <v>59.91</v>
+        <v>84.78</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:28:57</t>
+          <t>08:28:47</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="F61" t="n">
-        <v>5.37</v>
+        <v>5.46</v>
       </c>
       <c r="G61" t="n">
-        <v>215.6</v>
+        <v>229.4</v>
       </c>
       <c r="H61" t="n">
-        <v>13.3</v>
+        <v>12.1</v>
       </c>
       <c r="I61" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J61" t="n">
-        <v>-16.44</v>
+        <v>86.92</v>
       </c>
       <c r="K61" t="n">
-        <v>45.21</v>
+        <v>76.78</v>
       </c>
       <c r="L61" t="n">
-        <v>48.11</v>
+        <v>115.97</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:33:47</t>
+          <t>08:33:26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="F62" t="n">
-        <v>5.89</v>
+        <v>5.87</v>
       </c>
       <c r="G62" t="n">
-        <v>220.8</v>
+        <v>240.4</v>
       </c>
       <c r="H62" t="n">
-        <v>21.1</v>
+        <v>16.5</v>
       </c>
       <c r="I62" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>-4.58</v>
+        <v>62.97</v>
       </c>
       <c r="K62" t="n">
-        <v>16.77</v>
+        <v>65.2</v>
       </c>
       <c r="L62" t="n">
-        <v>17.38</v>
+        <v>90.64</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:35:23</t>
+          <t>08:35:08</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="F63" t="n">
-        <v>4.5</v>
+        <v>5.12</v>
       </c>
       <c r="G63" t="n">
-        <v>226.9</v>
+        <v>223.9</v>
       </c>
       <c r="H63" t="n">
-        <v>12.2</v>
+        <v>10.3</v>
       </c>
       <c r="I63" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J63" t="n">
-        <v>-36.54</v>
+        <v>21.33</v>
       </c>
       <c r="K63" t="n">
-        <v>-46</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>58.75</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:37:59</t>
+          <t>08:36:50</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="F64" t="n">
-        <v>5.15</v>
+        <v>5.1</v>
       </c>
       <c r="G64" t="n">
-        <v>240.5</v>
+        <v>240.7</v>
       </c>
       <c r="H64" t="n">
-        <v>16.2</v>
+        <v>18.8</v>
       </c>
       <c r="I64" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>39.61</v>
+        <v>84.84</v>
       </c>
       <c r="K64" t="n">
-        <v>-34.31</v>
+        <v>127.71</v>
       </c>
       <c r="L64" t="n">
-        <v>52.4</v>
+        <v>153.32</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:42:23</t>
+          <t>08:41:56</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="F65" t="n">
-        <v>5.44</v>
+        <v>5.9</v>
       </c>
       <c r="G65" t="n">
-        <v>219.9</v>
+        <v>233.8</v>
       </c>
       <c r="H65" t="n">
-        <v>12.1</v>
+        <v>15</v>
       </c>
       <c r="I65" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>-161.36</v>
+        <v>134.14</v>
       </c>
       <c r="K65" t="n">
-        <v>-64.81999999999999</v>
+        <v>-95.13</v>
       </c>
       <c r="L65" t="n">
-        <v>173.9</v>
+        <v>164.45</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:43:18</t>
+          <t>08:44:03</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>1.86</v>
+        <v>1.57</v>
       </c>
       <c r="F66" t="n">
-        <v>6.18</v>
+        <v>4.72</v>
       </c>
       <c r="G66" t="n">
-        <v>220.6</v>
+        <v>241.2</v>
       </c>
       <c r="H66" t="n">
-        <v>9.9</v>
+        <v>10.3</v>
       </c>
       <c r="I66" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J66" t="n">
-        <v>24.92</v>
+        <v>45.21</v>
       </c>
       <c r="K66" t="n">
-        <v>191.84</v>
+        <v>-35.67</v>
       </c>
       <c r="L66" t="n">
-        <v>193.45</v>
+        <v>57.59</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:45:38</t>
+          <t>08:46:38</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>1.8</v>
+        <v>1.59</v>
       </c>
       <c r="F67" t="n">
-        <v>4.95</v>
+        <v>5.09</v>
       </c>
       <c r="G67" t="n">
-        <v>223.9</v>
+        <v>238.3</v>
       </c>
       <c r="H67" t="n">
-        <v>9.4</v>
+        <v>11.4</v>
       </c>
       <c r="I67" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>-33.67</v>
+        <v>-178.8</v>
       </c>
       <c r="K67" t="n">
-        <v>-106.2</v>
+        <v>62.01</v>
       </c>
       <c r="L67" t="n">
-        <v>111.41</v>
+        <v>189.25</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:49:57</t>
+          <t>08:49:54</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>1.82</v>
+        <v>1.37</v>
       </c>
       <c r="F68" t="n">
-        <v>5.29</v>
+        <v>5.11</v>
       </c>
       <c r="G68" t="n">
-        <v>236.6</v>
+        <v>207</v>
       </c>
       <c r="H68" t="n">
-        <v>9</v>
+        <v>12.9</v>
       </c>
       <c r="I68" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J68" t="n">
-        <v>36.36</v>
+        <v>-112.01</v>
       </c>
       <c r="K68" t="n">
-        <v>-165.98</v>
+        <v>-67.61</v>
       </c>
       <c r="L68" t="n">
-        <v>169.91</v>
+        <v>130.83</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:51:34</t>
+          <t>08:50:52</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="F69" t="n">
-        <v>5.42</v>
+        <v>5.3</v>
       </c>
       <c r="G69" t="n">
-        <v>228.4</v>
+        <v>239</v>
       </c>
       <c r="H69" t="n">
-        <v>13.4</v>
+        <v>16.8</v>
       </c>
       <c r="I69" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J69" t="n">
-        <v>-101.52</v>
+        <v>-189.32</v>
       </c>
       <c r="K69" t="n">
-        <v>35.49</v>
+        <v>6.37</v>
       </c>
       <c r="L69" t="n">
-        <v>107.55</v>
+        <v>189.43</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:53:38</t>
+          <t>08:52:24</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>1.41</v>
+        <v>1.8</v>
       </c>
       <c r="F70" t="n">
-        <v>6.37</v>
+        <v>4.98</v>
       </c>
       <c r="G70" t="n">
-        <v>221.6</v>
+        <v>231.9</v>
       </c>
       <c r="H70" t="n">
-        <v>9.1</v>
+        <v>15.1</v>
       </c>
       <c r="I70" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>197.59</v>
+        <v>-45.94</v>
       </c>
       <c r="K70" t="n">
-        <v>-29.93</v>
+        <v>288.89</v>
       </c>
       <c r="L70" t="n">
-        <v>199.84</v>
+        <v>292.52</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:58:23</t>
+          <t>08:56:18</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="F71" t="n">
-        <v>5.42</v>
+        <v>5.12</v>
       </c>
       <c r="G71" t="n">
-        <v>228.3</v>
+        <v>223.6</v>
       </c>
       <c r="H71" t="n">
-        <v>14.6</v>
+        <v>14.4</v>
       </c>
       <c r="I71" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>-428.87</v>
+        <v>24.98</v>
       </c>
       <c r="K71" t="n">
-        <v>443.32</v>
+        <v>-202.77</v>
       </c>
       <c r="L71" t="n">
-        <v>616.8099999999999</v>
+        <v>204.31</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:00:16</t>
+          <t>08:57:19</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="F72" t="n">
-        <v>5.34</v>
+        <v>5.8</v>
       </c>
       <c r="G72" t="n">
-        <v>232.7</v>
+        <v>221.6</v>
       </c>
       <c r="H72" t="n">
-        <v>12.2</v>
+        <v>16.9</v>
       </c>
       <c r="I72" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J72" t="n">
-        <v>51.46</v>
+        <v>293.17</v>
       </c>
       <c r="K72" t="n">
-        <v>-335.17</v>
+        <v>234.28</v>
       </c>
       <c r="L72" t="n">
-        <v>339.09</v>
+        <v>375.28</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:02:09</t>
+          <t>08:58:39</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>1.54</v>
+        <v>1.76</v>
       </c>
       <c r="F73" t="n">
-        <v>4.81</v>
+        <v>5.25</v>
       </c>
       <c r="G73" t="n">
-        <v>229.1</v>
+        <v>235.4</v>
       </c>
       <c r="H73" t="n">
-        <v>8.800000000000001</v>
+        <v>12.3</v>
       </c>
       <c r="I73" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="J73" t="n">
-        <v>-156.52</v>
+        <v>-316.62</v>
       </c>
       <c r="K73" t="n">
-        <v>101.1</v>
+        <v>86.97</v>
       </c>
       <c r="L73" t="n">
-        <v>186.33</v>
+        <v>328.35</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:11:21</t>
+          <t>09:08:30</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="F74" t="n">
-        <v>5.4</v>
+        <v>5.09</v>
       </c>
       <c r="G74" t="n">
-        <v>221.3</v>
+        <v>232.5</v>
       </c>
       <c r="H74" t="n">
-        <v>15.2</v>
+        <v>18.1</v>
       </c>
       <c r="I74" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J74" t="n">
-        <v>75.72</v>
+        <v>11.27</v>
       </c>
       <c r="K74" t="n">
-        <v>-59.52</v>
+        <v>-41.52</v>
       </c>
       <c r="L74" t="n">
-        <v>96.31999999999999</v>
+        <v>43.02</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:12:47</t>
+          <t>09:10:36</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3190,31 +3190,31 @@
         <v>1.87</v>
       </c>
       <c r="F75" t="n">
-        <v>5.19</v>
+        <v>5.95</v>
       </c>
       <c r="G75" t="n">
-        <v>210.2</v>
+        <v>240.7</v>
       </c>
       <c r="H75" t="n">
-        <v>15.3</v>
+        <v>12.8</v>
       </c>
       <c r="I75" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>-66.03</v>
+        <v>2.92</v>
       </c>
       <c r="K75" t="n">
-        <v>36.25</v>
+        <v>-93.06</v>
       </c>
       <c r="L75" t="n">
-        <v>75.31999999999999</v>
+        <v>93.11</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:15:14</t>
+          <t>09:11:40</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>1.74</v>
+        <v>2.08</v>
       </c>
       <c r="F76" t="n">
-        <v>5.83</v>
+        <v>5.42</v>
       </c>
       <c r="G76" t="n">
-        <v>225.8</v>
+        <v>211.2</v>
       </c>
       <c r="H76" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="I76" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>76.38</v>
+        <v>54.6</v>
       </c>
       <c r="K76" t="n">
-        <v>-7.96</v>
+        <v>-37.55</v>
       </c>
       <c r="L76" t="n">
-        <v>76.79000000000001</v>
+        <v>66.27</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:18:10</t>
+          <t>09:17:43</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.24</v>
+        <v>1.75</v>
       </c>
       <c r="F77" t="n">
-        <v>5.92</v>
+        <v>5.94</v>
       </c>
       <c r="G77" t="n">
-        <v>220.4</v>
+        <v>230.9</v>
       </c>
       <c r="H77" t="n">
-        <v>13.4</v>
+        <v>11.2</v>
       </c>
       <c r="I77" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>61.04</v>
+        <v>99.63</v>
       </c>
       <c r="K77" t="n">
-        <v>-59.91</v>
+        <v>4.68</v>
       </c>
       <c r="L77" t="n">
-        <v>85.53</v>
+        <v>99.73999999999999</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:19:36</t>
+          <t>09:19:24</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>1.74</v>
+        <v>2.05</v>
       </c>
       <c r="F78" t="n">
-        <v>5.3</v>
+        <v>5.58</v>
       </c>
       <c r="G78" t="n">
-        <v>235.8</v>
+        <v>246.6</v>
       </c>
       <c r="H78" t="n">
-        <v>13</v>
+        <v>21.6</v>
       </c>
       <c r="I78" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J78" t="n">
-        <v>-6.42</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="K78" t="n">
-        <v>173.9</v>
+        <v>-29.2</v>
       </c>
       <c r="L78" t="n">
-        <v>174.02</v>
+        <v>30.31</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:21:21</t>
+          <t>09:21:01</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>1.7</v>
+        <v>2.81</v>
       </c>
       <c r="F79" t="n">
-        <v>6.25</v>
+        <v>4.8</v>
       </c>
       <c r="G79" t="n">
-        <v>230.8</v>
+        <v>230.2</v>
       </c>
       <c r="H79" t="n">
-        <v>21.8</v>
+        <v>21.4</v>
       </c>
       <c r="I79" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J79" t="n">
-        <v>71.59</v>
+        <v>-134.48</v>
       </c>
       <c r="K79" t="n">
-        <v>-95.45999999999999</v>
+        <v>-62.69</v>
       </c>
       <c r="L79" t="n">
-        <v>119.32</v>
+        <v>148.37</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:25:15</t>
+          <t>09:24:59</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="F80" t="n">
-        <v>5.36</v>
+        <v>4.81</v>
       </c>
       <c r="G80" t="n">
-        <v>217.3</v>
+        <v>223.4</v>
       </c>
       <c r="H80" t="n">
-        <v>14.5</v>
+        <v>7.7</v>
       </c>
       <c r="I80" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>-277.26</v>
+        <v>147.29</v>
       </c>
       <c r="K80" t="n">
-        <v>64.15000000000001</v>
+        <v>-160.43</v>
       </c>
       <c r="L80" t="n">
-        <v>284.58</v>
+        <v>217.79</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:26:07</t>
+          <t>09:27:03</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="F81" t="n">
-        <v>4.78</v>
+        <v>5.16</v>
       </c>
       <c r="G81" t="n">
-        <v>213.7</v>
+        <v>220.8</v>
       </c>
       <c r="H81" t="n">
-        <v>13.5</v>
+        <v>5.6</v>
       </c>
       <c r="I81" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>-172.61</v>
+        <v>-22.27</v>
       </c>
       <c r="K81" t="n">
-        <v>27.51</v>
+        <v>-154.77</v>
       </c>
       <c r="L81" t="n">
-        <v>174.79</v>
+        <v>156.36</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:27:48</t>
+          <t>09:29:04</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="F82" t="n">
-        <v>5.52</v>
+        <v>5.07</v>
       </c>
       <c r="G82" t="n">
-        <v>230.8</v>
+        <v>221.6</v>
       </c>
       <c r="H82" t="n">
-        <v>12</v>
+        <v>15.6</v>
       </c>
       <c r="I82" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J82" t="n">
-        <v>-316.45</v>
+        <v>221.59</v>
       </c>
       <c r="K82" t="n">
-        <v>172.4</v>
+        <v>278.76</v>
       </c>
       <c r="L82" t="n">
-        <v>360.36</v>
+        <v>356.1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:31:16</t>
+          <t>09:33:30</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="F83" t="n">
-        <v>5.17</v>
+        <v>5.43</v>
       </c>
       <c r="G83" t="n">
-        <v>217.7</v>
+        <v>212.1</v>
       </c>
       <c r="H83" t="n">
-        <v>11</v>
+        <v>18.2</v>
       </c>
       <c r="I83" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>-100.71</v>
+        <v>-277.5</v>
       </c>
       <c r="K83" t="n">
-        <v>187.38</v>
+        <v>-196.94</v>
       </c>
       <c r="L83" t="n">
-        <v>212.73</v>
+        <v>340.28</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:32:17</t>
+          <t>09:34:52</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3568,31 +3568,31 @@
         <v>1.72</v>
       </c>
       <c r="F84" t="n">
-        <v>5.18</v>
+        <v>5.78</v>
       </c>
       <c r="G84" t="n">
-        <v>235.5</v>
+        <v>232.2</v>
       </c>
       <c r="H84" t="n">
-        <v>14.8</v>
+        <v>17.5</v>
       </c>
       <c r="I84" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>385.7</v>
+        <v>-152.85</v>
       </c>
       <c r="K84" t="n">
-        <v>15.65</v>
+        <v>-45.07</v>
       </c>
       <c r="L84" t="n">
-        <v>386.02</v>
+        <v>159.35</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:33:26</t>
+          <t>09:36:22</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="F85" t="n">
-        <v>5.51</v>
+        <v>5.59</v>
       </c>
       <c r="G85" t="n">
-        <v>246.6</v>
+        <v>232.1</v>
       </c>
       <c r="H85" t="n">
-        <v>15.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I85" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>-407.3</v>
+        <v>-129.84</v>
       </c>
       <c r="K85" t="n">
-        <v>-92.93000000000001</v>
+        <v>-125.7</v>
       </c>
       <c r="L85" t="n">
-        <v>417.77</v>
+        <v>180.72</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:38:08</t>
+          <t>09:41:07</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
       <c r="F86" t="n">
-        <v>4.63</v>
+        <v>4.85</v>
       </c>
       <c r="G86" t="n">
-        <v>229.8</v>
+        <v>239.4</v>
       </c>
       <c r="H86" t="n">
-        <v>21.3</v>
+        <v>11.7</v>
       </c>
       <c r="I86" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>489.06</v>
+        <v>-183.65</v>
       </c>
       <c r="K86" t="n">
-        <v>287.98</v>
+        <v>216.03</v>
       </c>
       <c r="L86" t="n">
-        <v>567.55</v>
+        <v>283.54</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:39:45</t>
+          <t>09:43:25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3.25</v>
+        <v>2.51</v>
       </c>
       <c r="F87" t="n">
-        <v>4.82</v>
+        <v>6.13</v>
       </c>
       <c r="G87" t="n">
-        <v>227.1</v>
+        <v>224.8</v>
       </c>
       <c r="H87" t="n">
-        <v>17.4</v>
+        <v>12.1</v>
       </c>
       <c r="I87" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>615.04</v>
+        <v>-228.7</v>
       </c>
       <c r="K87" t="n">
-        <v>-633.34</v>
+        <v>-473.13</v>
       </c>
       <c r="L87" t="n">
-        <v>882.84</v>
+        <v>525.51</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:40:57</t>
+          <t>09:44:24</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>1.61</v>
+        <v>2.15</v>
       </c>
       <c r="F88" t="n">
-        <v>5.45</v>
+        <v>5.46</v>
       </c>
       <c r="G88" t="n">
-        <v>224.1</v>
+        <v>232.6</v>
       </c>
       <c r="H88" t="n">
-        <v>12</v>
+        <v>21.7</v>
       </c>
       <c r="I88" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>-186.48</v>
+        <v>537.8</v>
       </c>
       <c r="K88" t="n">
-        <v>-25.46</v>
+        <v>-569.25</v>
       </c>
       <c r="L88" t="n">
-        <v>188.21</v>
+        <v>783.12</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-08-25.xlsx
+++ b/output/2024-08-25.xlsx
@@ -640,13 +640,13 @@
         <v>29</v>
       </c>
       <c r="J14" t="n">
-        <v>40.33</v>
+        <v>33.45</v>
       </c>
       <c r="K14" t="n">
-        <v>-44.27</v>
+        <v>-36.72</v>
       </c>
       <c r="L14" t="n">
-        <v>59.89</v>
+        <v>49.67</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>27</v>
       </c>
       <c r="J15" t="n">
-        <v>-32.47</v>
+        <v>-24.06</v>
       </c>
       <c r="K15" t="n">
-        <v>108.08</v>
+        <v>80.09</v>
       </c>
       <c r="L15" t="n">
-        <v>112.85</v>
+        <v>83.63</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>27</v>
       </c>
       <c r="J16" t="n">
-        <v>57.41</v>
+        <v>52.47</v>
       </c>
       <c r="K16" t="n">
-        <v>15.47</v>
+        <v>14.14</v>
       </c>
       <c r="L16" t="n">
-        <v>59.46</v>
+        <v>54.35</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>-48.95</v>
+        <v>-54.13</v>
       </c>
       <c r="K17" t="n">
-        <v>-54.07</v>
+        <v>-59.79</v>
       </c>
       <c r="L17" t="n">
-        <v>72.94</v>
+        <v>80.66</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>24</v>
       </c>
       <c r="J18" t="n">
-        <v>-146.24</v>
+        <v>-116.1</v>
       </c>
       <c r="K18" t="n">
-        <v>-79.55</v>
+        <v>-63.16</v>
       </c>
       <c r="L18" t="n">
-        <v>166.47</v>
+        <v>132.17</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>68.38</v>
+        <v>69.89</v>
       </c>
       <c r="K19" t="n">
-        <v>42.71</v>
+        <v>43.66</v>
       </c>
       <c r="L19" t="n">
-        <v>80.62</v>
+        <v>82.40000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>86.29000000000001</v>
+        <v>110.13</v>
       </c>
       <c r="K20" t="n">
-        <v>43.4</v>
+        <v>55.4</v>
       </c>
       <c r="L20" t="n">
-        <v>96.59</v>
+        <v>123.28</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>23</v>
       </c>
       <c r="J21" t="n">
-        <v>87.39</v>
+        <v>112.56</v>
       </c>
       <c r="K21" t="n">
-        <v>-34.93</v>
+        <v>-44.99</v>
       </c>
       <c r="L21" t="n">
-        <v>94.11</v>
+        <v>121.22</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>63.87</v>
+        <v>65.05</v>
       </c>
       <c r="K22" t="n">
-        <v>105.12</v>
+        <v>107.06</v>
       </c>
       <c r="L22" t="n">
-        <v>123</v>
+        <v>125.27</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>28</v>
       </c>
       <c r="J23" t="n">
-        <v>-23.36</v>
+        <v>-29.95</v>
       </c>
       <c r="K23" t="n">
-        <v>-106.05</v>
+        <v>-135.96</v>
       </c>
       <c r="L23" t="n">
-        <v>108.59</v>
+        <v>139.22</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>28</v>
       </c>
       <c r="J24" t="n">
-        <v>-135.93</v>
+        <v>-140.36</v>
       </c>
       <c r="K24" t="n">
-        <v>124.64</v>
+        <v>128.71</v>
       </c>
       <c r="L24" t="n">
-        <v>184.42</v>
+        <v>190.44</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>-357.99</v>
+        <v>-315.84</v>
       </c>
       <c r="K25" t="n">
-        <v>-255.22</v>
+        <v>-225.17</v>
       </c>
       <c r="L25" t="n">
-        <v>439.65</v>
+        <v>387.89</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>29</v>
       </c>
       <c r="J26" t="n">
-        <v>192.24</v>
+        <v>224.77</v>
       </c>
       <c r="K26" t="n">
-        <v>48.93</v>
+        <v>57.2</v>
       </c>
       <c r="L26" t="n">
-        <v>198.37</v>
+        <v>231.94</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>-161.62</v>
+        <v>-221.77</v>
       </c>
       <c r="K27" t="n">
-        <v>186.8</v>
+        <v>256.31</v>
       </c>
       <c r="L27" t="n">
-        <v>247.01</v>
+        <v>338.93</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>-252.74</v>
+        <v>-289.48</v>
       </c>
       <c r="K28" t="n">
-        <v>-156.73</v>
+        <v>-179.51</v>
       </c>
       <c r="L28" t="n">
-        <v>297.4</v>
+        <v>340.62</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>29</v>
       </c>
       <c r="J29" t="n">
-        <v>37.65</v>
+        <v>34.18</v>
       </c>
       <c r="K29" t="n">
-        <v>31.14</v>
+        <v>28.27</v>
       </c>
       <c r="L29" t="n">
-        <v>48.86</v>
+        <v>44.36</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>100.83</v>
+        <v>83.06</v>
       </c>
       <c r="K30" t="n">
-        <v>-52.49</v>
+        <v>-43.24</v>
       </c>
       <c r="L30" t="n">
-        <v>113.68</v>
+        <v>93.64</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>-104.66</v>
+        <v>-79.38</v>
       </c>
       <c r="K31" t="n">
-        <v>71.3</v>
+        <v>54.07</v>
       </c>
       <c r="L31" t="n">
-        <v>126.64</v>
+        <v>96.05</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>11.52</v>
+        <v>12.21</v>
       </c>
       <c r="K32" t="n">
-        <v>-71.51000000000001</v>
+        <v>-75.77</v>
       </c>
       <c r="L32" t="n">
-        <v>72.43000000000001</v>
+        <v>76.75</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>-165.85</v>
+        <v>-116.63</v>
       </c>
       <c r="K33" t="n">
-        <v>-58.78</v>
+        <v>-41.33</v>
       </c>
       <c r="L33" t="n">
-        <v>175.96</v>
+        <v>123.74</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>28</v>
       </c>
       <c r="J34" t="n">
-        <v>139.42</v>
+        <v>97.26000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>51.79</v>
+        <v>36.13</v>
       </c>
       <c r="L34" t="n">
-        <v>148.73</v>
+        <v>103.76</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>54.49</v>
+        <v>53.98</v>
       </c>
       <c r="K35" t="n">
-        <v>-146.95</v>
+        <v>-145.59</v>
       </c>
       <c r="L35" t="n">
-        <v>156.72</v>
+        <v>155.27</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>27</v>
       </c>
       <c r="J36" t="n">
-        <v>66.41</v>
+        <v>68.48999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>-82.44</v>
+        <v>-85.02</v>
       </c>
       <c r="L36" t="n">
-        <v>105.86</v>
+        <v>109.18</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>-60.36</v>
+        <v>-55.26</v>
       </c>
       <c r="K37" t="n">
-        <v>173.37</v>
+        <v>158.72</v>
       </c>
       <c r="L37" t="n">
-        <v>183.57</v>
+        <v>168.06</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-276.29</v>
+        <v>-264.31</v>
       </c>
       <c r="K38" t="n">
-        <v>126.57</v>
+        <v>121.08</v>
       </c>
       <c r="L38" t="n">
-        <v>303.9</v>
+        <v>290.73</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>96.36</v>
+        <v>107.11</v>
       </c>
       <c r="K39" t="n">
-        <v>166.15</v>
+        <v>184.69</v>
       </c>
       <c r="L39" t="n">
-        <v>192.07</v>
+        <v>213.5</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>29</v>
       </c>
       <c r="J40" t="n">
-        <v>93.81</v>
+        <v>98.18000000000001</v>
       </c>
       <c r="K40" t="n">
-        <v>113.72</v>
+        <v>119.02</v>
       </c>
       <c r="L40" t="n">
-        <v>147.42</v>
+        <v>154.29</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>171.89</v>
+        <v>191.8</v>
       </c>
       <c r="K41" t="n">
-        <v>-187.1</v>
+        <v>-208.78</v>
       </c>
       <c r="L41" t="n">
-        <v>254.07</v>
+        <v>283.51</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>26</v>
       </c>
       <c r="J42" t="n">
-        <v>29.91</v>
+        <v>27.99</v>
       </c>
       <c r="K42" t="n">
-        <v>-590.79</v>
+        <v>-552.96</v>
       </c>
       <c r="L42" t="n">
-        <v>591.55</v>
+        <v>553.67</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>-30.81</v>
+        <v>-52.25</v>
       </c>
       <c r="K43" t="n">
-        <v>-133.02</v>
+        <v>-225.58</v>
       </c>
       <c r="L43" t="n">
-        <v>136.54</v>
+        <v>231.56</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>-16.34</v>
+        <v>-12.1</v>
       </c>
       <c r="K44" t="n">
-        <v>74.56</v>
+        <v>55.22</v>
       </c>
       <c r="L44" t="n">
-        <v>76.33</v>
+        <v>56.53</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>12.6</v>
+        <v>18.08</v>
       </c>
       <c r="K45" t="n">
-        <v>30.95</v>
+        <v>44.4</v>
       </c>
       <c r="L45" t="n">
-        <v>33.42</v>
+        <v>47.94</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>28</v>
       </c>
       <c r="J46" t="n">
-        <v>31.31</v>
+        <v>21.06</v>
       </c>
       <c r="K46" t="n">
-        <v>-108.71</v>
+        <v>-73.11</v>
       </c>
       <c r="L46" t="n">
-        <v>113.13</v>
+        <v>76.08</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>24</v>
       </c>
       <c r="J47" t="n">
-        <v>80.45</v>
+        <v>63</v>
       </c>
       <c r="K47" t="n">
-        <v>-153.33</v>
+        <v>-120.06</v>
       </c>
       <c r="L47" t="n">
-        <v>173.16</v>
+        <v>135.59</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>29</v>
       </c>
       <c r="J48" t="n">
-        <v>-53.74</v>
+        <v>-51.12</v>
       </c>
       <c r="K48" t="n">
-        <v>12.8</v>
+        <v>12.18</v>
       </c>
       <c r="L48" t="n">
-        <v>55.24</v>
+        <v>52.55</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>73.55</v>
+        <v>66.69</v>
       </c>
       <c r="K49" t="n">
-        <v>-36.17</v>
+        <v>-32.8</v>
       </c>
       <c r="L49" t="n">
-        <v>81.95999999999999</v>
+        <v>74.31999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>81.26000000000001</v>
+        <v>84.73</v>
       </c>
       <c r="K50" t="n">
-        <v>-115.03</v>
+        <v>-119.94</v>
       </c>
       <c r="L50" t="n">
-        <v>140.83</v>
+        <v>146.85</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>115.88</v>
+        <v>103.21</v>
       </c>
       <c r="K51" t="n">
-        <v>-133.51</v>
+        <v>-118.91</v>
       </c>
       <c r="L51" t="n">
-        <v>176.78</v>
+        <v>157.45</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>-64.5</v>
+        <v>-71.7</v>
       </c>
       <c r="K52" t="n">
-        <v>80</v>
+        <v>88.94</v>
       </c>
       <c r="L52" t="n">
-        <v>102.76</v>
+        <v>114.24</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>-189.46</v>
+        <v>-204.48</v>
       </c>
       <c r="K53" t="n">
-        <v>-23.19</v>
+        <v>-25.03</v>
       </c>
       <c r="L53" t="n">
-        <v>190.87</v>
+        <v>206</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-26.39</v>
+        <v>-28.32</v>
       </c>
       <c r="K54" t="n">
-        <v>260.8</v>
+        <v>279.84</v>
       </c>
       <c r="L54" t="n">
-        <v>262.13</v>
+        <v>281.27</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>-101.6</v>
+        <v>-144.45</v>
       </c>
       <c r="K55" t="n">
-        <v>-64.3</v>
+        <v>-91.41</v>
       </c>
       <c r="L55" t="n">
-        <v>120.24</v>
+        <v>170.95</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>386.55</v>
+        <v>386.41</v>
       </c>
       <c r="K56" t="n">
-        <v>-66.3</v>
+        <v>-66.28</v>
       </c>
       <c r="L56" t="n">
-        <v>392.2</v>
+        <v>392.06</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>-339.19</v>
+        <v>-341.4</v>
       </c>
       <c r="K57" t="n">
-        <v>-195.36</v>
+        <v>-196.64</v>
       </c>
       <c r="L57" t="n">
-        <v>391.43</v>
+        <v>393.98</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>355.86</v>
+        <v>310.58</v>
       </c>
       <c r="K58" t="n">
-        <v>114.05</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="L58" t="n">
-        <v>373.69</v>
+        <v>326.14</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>-43.99</v>
+        <v>-42.72</v>
       </c>
       <c r="K59" t="n">
-        <v>-37.53</v>
+        <v>-36.45</v>
       </c>
       <c r="L59" t="n">
-        <v>57.82</v>
+        <v>56.16</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>28</v>
       </c>
       <c r="J60" t="n">
-        <v>-62.37</v>
+        <v>-48.51</v>
       </c>
       <c r="K60" t="n">
-        <v>-57.42</v>
+        <v>-44.66</v>
       </c>
       <c r="L60" t="n">
-        <v>84.78</v>
+        <v>65.94</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>28</v>
       </c>
       <c r="J61" t="n">
-        <v>86.92</v>
+        <v>55.91</v>
       </c>
       <c r="K61" t="n">
-        <v>76.78</v>
+        <v>49.39</v>
       </c>
       <c r="L61" t="n">
-        <v>115.97</v>
+        <v>74.59999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>62.97</v>
+        <v>54.71</v>
       </c>
       <c r="K62" t="n">
-        <v>65.2</v>
+        <v>56.64</v>
       </c>
       <c r="L62" t="n">
-        <v>90.64</v>
+        <v>78.73999999999999</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>29</v>
       </c>
       <c r="J63" t="n">
-        <v>21.33</v>
+        <v>36</v>
       </c>
       <c r="K63" t="n">
-        <v>-9.369999999999999</v>
+        <v>-15.82</v>
       </c>
       <c r="L63" t="n">
-        <v>23.3</v>
+        <v>39.32</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>84.84</v>
+        <v>63.71</v>
       </c>
       <c r="K64" t="n">
-        <v>127.71</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="L64" t="n">
-        <v>153.32</v>
+        <v>115.13</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>134.14</v>
+        <v>125.12</v>
       </c>
       <c r="K65" t="n">
-        <v>-95.13</v>
+        <v>-88.73</v>
       </c>
       <c r="L65" t="n">
-        <v>164.45</v>
+        <v>153.39</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>27</v>
       </c>
       <c r="J66" t="n">
-        <v>45.21</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="K66" t="n">
-        <v>-35.67</v>
+        <v>-51.41</v>
       </c>
       <c r="L66" t="n">
-        <v>57.59</v>
+        <v>82.98999999999999</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>-178.8</v>
+        <v>-174.32</v>
       </c>
       <c r="K67" t="n">
-        <v>62.01</v>
+        <v>60.45</v>
       </c>
       <c r="L67" t="n">
-        <v>189.25</v>
+        <v>184.5</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>27</v>
       </c>
       <c r="J68" t="n">
-        <v>-112.01</v>
+        <v>-140.35</v>
       </c>
       <c r="K68" t="n">
-        <v>-67.61</v>
+        <v>-84.72</v>
       </c>
       <c r="L68" t="n">
-        <v>130.83</v>
+        <v>163.94</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>28</v>
       </c>
       <c r="J69" t="n">
-        <v>-189.32</v>
+        <v>-191.21</v>
       </c>
       <c r="K69" t="n">
-        <v>6.37</v>
+        <v>6.43</v>
       </c>
       <c r="L69" t="n">
-        <v>189.43</v>
+        <v>191.31</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>-45.94</v>
+        <v>-44.01</v>
       </c>
       <c r="K70" t="n">
-        <v>288.89</v>
+        <v>276.72</v>
       </c>
       <c r="L70" t="n">
-        <v>292.52</v>
+        <v>280.2</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>24.98</v>
+        <v>34.44</v>
       </c>
       <c r="K71" t="n">
-        <v>-202.77</v>
+        <v>-279.53</v>
       </c>
       <c r="L71" t="n">
-        <v>204.31</v>
+        <v>281.65</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>28</v>
       </c>
       <c r="J72" t="n">
-        <v>293.17</v>
+        <v>278.7</v>
       </c>
       <c r="K72" t="n">
-        <v>234.28</v>
+        <v>222.71</v>
       </c>
       <c r="L72" t="n">
-        <v>375.28</v>
+        <v>356.75</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>29</v>
       </c>
       <c r="J73" t="n">
-        <v>-316.62</v>
+        <v>-303.93</v>
       </c>
       <c r="K73" t="n">
-        <v>86.97</v>
+        <v>83.48</v>
       </c>
       <c r="L73" t="n">
-        <v>328.35</v>
+        <v>315.18</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>29</v>
       </c>
       <c r="J74" t="n">
-        <v>11.27</v>
+        <v>10</v>
       </c>
       <c r="K74" t="n">
-        <v>-41.52</v>
+        <v>-36.85</v>
       </c>
       <c r="L74" t="n">
-        <v>43.02</v>
+        <v>38.18</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>2.92</v>
+        <v>2.08</v>
       </c>
       <c r="K75" t="n">
-        <v>-93.06</v>
+        <v>-66.34999999999999</v>
       </c>
       <c r="L75" t="n">
-        <v>93.11</v>
+        <v>66.38</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>54.6</v>
+        <v>46.16</v>
       </c>
       <c r="K76" t="n">
-        <v>-37.55</v>
+        <v>-31.75</v>
       </c>
       <c r="L76" t="n">
-        <v>66.27</v>
+        <v>56.03</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>99.63</v>
+        <v>95.27</v>
       </c>
       <c r="K77" t="n">
-        <v>4.68</v>
+        <v>4.48</v>
       </c>
       <c r="L77" t="n">
-        <v>99.73999999999999</v>
+        <v>95.37</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>29</v>
       </c>
       <c r="J78" t="n">
-        <v>-8.130000000000001</v>
+        <v>-11.33</v>
       </c>
       <c r="K78" t="n">
-        <v>-29.2</v>
+        <v>-40.69</v>
       </c>
       <c r="L78" t="n">
-        <v>30.31</v>
+        <v>42.23</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>28</v>
       </c>
       <c r="J79" t="n">
-        <v>-134.48</v>
+        <v>-113.09</v>
       </c>
       <c r="K79" t="n">
-        <v>-62.69</v>
+        <v>-52.72</v>
       </c>
       <c r="L79" t="n">
-        <v>148.37</v>
+        <v>124.77</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>147.29</v>
+        <v>124.89</v>
       </c>
       <c r="K80" t="n">
-        <v>-160.43</v>
+        <v>-136.04</v>
       </c>
       <c r="L80" t="n">
-        <v>217.79</v>
+        <v>184.67</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>-22.27</v>
+        <v>-22.4</v>
       </c>
       <c r="K81" t="n">
-        <v>-154.77</v>
+        <v>-155.74</v>
       </c>
       <c r="L81" t="n">
-        <v>156.36</v>
+        <v>157.34</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>23</v>
       </c>
       <c r="J82" t="n">
-        <v>221.59</v>
+        <v>177.31</v>
       </c>
       <c r="K82" t="n">
-        <v>278.76</v>
+        <v>223.05</v>
       </c>
       <c r="L82" t="n">
-        <v>356.1</v>
+        <v>284.94</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>-277.5</v>
+        <v>-244.83</v>
       </c>
       <c r="K83" t="n">
-        <v>-196.94</v>
+        <v>-173.75</v>
       </c>
       <c r="L83" t="n">
-        <v>340.28</v>
+        <v>300.22</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>-152.85</v>
+        <v>-169.3</v>
       </c>
       <c r="K84" t="n">
-        <v>-45.07</v>
+        <v>-49.92</v>
       </c>
       <c r="L84" t="n">
-        <v>159.35</v>
+        <v>176.51</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>-129.84</v>
+        <v>-136.6</v>
       </c>
       <c r="K85" t="n">
-        <v>-125.7</v>
+        <v>-132.24</v>
       </c>
       <c r="L85" t="n">
-        <v>180.72</v>
+        <v>190.13</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>-183.65</v>
+        <v>-206.3</v>
       </c>
       <c r="K86" t="n">
-        <v>216.03</v>
+        <v>242.68</v>
       </c>
       <c r="L86" t="n">
-        <v>283.54</v>
+        <v>318.52</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>-228.7</v>
+        <v>-242.45</v>
       </c>
       <c r="K87" t="n">
-        <v>-473.13</v>
+        <v>-501.57</v>
       </c>
       <c r="L87" t="n">
-        <v>525.51</v>
+        <v>557.1</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>537.8</v>
+        <v>451.03</v>
       </c>
       <c r="K88" t="n">
-        <v>-569.25</v>
+        <v>-477.4</v>
       </c>
       <c r="L88" t="n">
-        <v>783.12</v>
+        <v>656.77</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-08-25.xlsx
+++ b/output/2024-08-25.xlsx
@@ -640,13 +640,13 @@
         <v>29</v>
       </c>
       <c r="J14" t="n">
-        <v>33.45</v>
+        <v>34.15</v>
       </c>
       <c r="K14" t="n">
-        <v>-36.72</v>
+        <v>-37.48</v>
       </c>
       <c r="L14" t="n">
-        <v>49.67</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>27</v>
       </c>
       <c r="J15" t="n">
-        <v>-24.06</v>
+        <v>-22.47</v>
       </c>
       <c r="K15" t="n">
-        <v>80.09</v>
+        <v>74.81</v>
       </c>
       <c r="L15" t="n">
-        <v>83.63</v>
+        <v>78.11</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>27</v>
       </c>
       <c r="J16" t="n">
-        <v>52.47</v>
+        <v>48.95</v>
       </c>
       <c r="K16" t="n">
-        <v>14.14</v>
+        <v>13.19</v>
       </c>
       <c r="L16" t="n">
-        <v>54.35</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>-54.13</v>
+        <v>-42.45</v>
       </c>
       <c r="K17" t="n">
-        <v>-59.79</v>
+        <v>-46.89</v>
       </c>
       <c r="L17" t="n">
-        <v>80.66</v>
+        <v>63.26</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>24</v>
       </c>
       <c r="J18" t="n">
-        <v>-116.1</v>
+        <v>-94.67</v>
       </c>
       <c r="K18" t="n">
-        <v>-63.16</v>
+        <v>-51.5</v>
       </c>
       <c r="L18" t="n">
-        <v>132.17</v>
+        <v>107.77</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>69.89</v>
+        <v>55.88</v>
       </c>
       <c r="K19" t="n">
-        <v>43.66</v>
+        <v>34.9</v>
       </c>
       <c r="L19" t="n">
-        <v>82.40000000000001</v>
+        <v>65.89</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>110.13</v>
+        <v>74.2</v>
       </c>
       <c r="K20" t="n">
-        <v>55.4</v>
+        <v>37.32</v>
       </c>
       <c r="L20" t="n">
-        <v>123.28</v>
+        <v>83.06</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>23</v>
       </c>
       <c r="J21" t="n">
-        <v>112.56</v>
+        <v>75.27</v>
       </c>
       <c r="K21" t="n">
-        <v>-44.99</v>
+        <v>-30.09</v>
       </c>
       <c r="L21" t="n">
-        <v>121.22</v>
+        <v>81.06</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>65.05</v>
+        <v>49.14</v>
       </c>
       <c r="K22" t="n">
-        <v>107.06</v>
+        <v>80.88</v>
       </c>
       <c r="L22" t="n">
-        <v>125.27</v>
+        <v>94.64</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>28</v>
       </c>
       <c r="J23" t="n">
-        <v>-29.95</v>
+        <v>-20.76</v>
       </c>
       <c r="K23" t="n">
-        <v>-135.96</v>
+        <v>-94.26000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>139.22</v>
+        <v>96.52</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>28</v>
       </c>
       <c r="J24" t="n">
-        <v>-140.36</v>
+        <v>-97.34</v>
       </c>
       <c r="K24" t="n">
-        <v>128.71</v>
+        <v>89.25</v>
       </c>
       <c r="L24" t="n">
-        <v>190.44</v>
+        <v>132.06</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>-315.84</v>
+        <v>-201.63</v>
       </c>
       <c r="K25" t="n">
-        <v>-225.17</v>
+        <v>-143.74</v>
       </c>
       <c r="L25" t="n">
-        <v>387.89</v>
+        <v>247.62</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>29</v>
       </c>
       <c r="J26" t="n">
-        <v>224.77</v>
+        <v>151.91</v>
       </c>
       <c r="K26" t="n">
-        <v>57.2</v>
+        <v>38.66</v>
       </c>
       <c r="L26" t="n">
-        <v>231.94</v>
+        <v>156.76</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>-221.77</v>
+        <v>-117.07</v>
       </c>
       <c r="K27" t="n">
-        <v>256.31</v>
+        <v>135.31</v>
       </c>
       <c r="L27" t="n">
-        <v>338.93</v>
+        <v>178.92</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>-289.48</v>
+        <v>-170.38</v>
       </c>
       <c r="K28" t="n">
-        <v>-179.51</v>
+        <v>-105.66</v>
       </c>
       <c r="L28" t="n">
-        <v>340.62</v>
+        <v>200.49</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>29</v>
       </c>
       <c r="J29" t="n">
-        <v>34.18</v>
+        <v>34.94</v>
       </c>
       <c r="K29" t="n">
-        <v>28.27</v>
+        <v>28.9</v>
       </c>
       <c r="L29" t="n">
-        <v>44.36</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>83.06</v>
+        <v>68.97</v>
       </c>
       <c r="K30" t="n">
-        <v>-43.24</v>
+        <v>-35.9</v>
       </c>
       <c r="L30" t="n">
-        <v>93.64</v>
+        <v>77.76000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>-79.38</v>
+        <v>-68.04000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>54.07</v>
+        <v>46.35</v>
       </c>
       <c r="L31" t="n">
-        <v>96.05</v>
+        <v>82.31999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>12.21</v>
+        <v>10</v>
       </c>
       <c r="K32" t="n">
-        <v>-75.77</v>
+        <v>-62.1</v>
       </c>
       <c r="L32" t="n">
-        <v>76.75</v>
+        <v>62.9</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>-116.63</v>
+        <v>-107.4</v>
       </c>
       <c r="K33" t="n">
-        <v>-41.33</v>
+        <v>-38.06</v>
       </c>
       <c r="L33" t="n">
-        <v>123.74</v>
+        <v>113.94</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>28</v>
       </c>
       <c r="J34" t="n">
-        <v>97.26000000000001</v>
+        <v>94.06</v>
       </c>
       <c r="K34" t="n">
-        <v>36.13</v>
+        <v>34.94</v>
       </c>
       <c r="L34" t="n">
-        <v>103.76</v>
+        <v>100.34</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>53.98</v>
+        <v>37.27</v>
       </c>
       <c r="K35" t="n">
-        <v>-145.59</v>
+        <v>-100.53</v>
       </c>
       <c r="L35" t="n">
-        <v>155.27</v>
+        <v>107.21</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>27</v>
       </c>
       <c r="J36" t="n">
-        <v>68.48999999999999</v>
+        <v>54.08</v>
       </c>
       <c r="K36" t="n">
-        <v>-85.02</v>
+        <v>-67.13</v>
       </c>
       <c r="L36" t="n">
-        <v>109.18</v>
+        <v>86.2</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>-55.26</v>
+        <v>-40.2</v>
       </c>
       <c r="K37" t="n">
-        <v>158.72</v>
+        <v>115.45</v>
       </c>
       <c r="L37" t="n">
-        <v>168.06</v>
+        <v>122.25</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-264.31</v>
+        <v>-168.11</v>
       </c>
       <c r="K38" t="n">
-        <v>121.08</v>
+        <v>77.01000000000001</v>
       </c>
       <c r="L38" t="n">
-        <v>290.73</v>
+        <v>184.91</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>107.11</v>
+        <v>66.48999999999999</v>
       </c>
       <c r="K39" t="n">
-        <v>184.69</v>
+        <v>114.65</v>
       </c>
       <c r="L39" t="n">
-        <v>213.5</v>
+        <v>132.54</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>29</v>
       </c>
       <c r="J40" t="n">
-        <v>98.18000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K40" t="n">
-        <v>119.02</v>
+        <v>86.56</v>
       </c>
       <c r="L40" t="n">
-        <v>154.29</v>
+        <v>112.21</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>191.8</v>
+        <v>123.27</v>
       </c>
       <c r="K41" t="n">
-        <v>-208.78</v>
+        <v>-134.18</v>
       </c>
       <c r="L41" t="n">
-        <v>283.51</v>
+        <v>182.2</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>26</v>
       </c>
       <c r="J42" t="n">
-        <v>27.99</v>
+        <v>16.54</v>
       </c>
       <c r="K42" t="n">
-        <v>-552.96</v>
+        <v>-326.69</v>
       </c>
       <c r="L42" t="n">
-        <v>553.67</v>
+        <v>327.1</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>-52.25</v>
+        <v>-29.52</v>
       </c>
       <c r="K43" t="n">
-        <v>-225.58</v>
+        <v>-127.42</v>
       </c>
       <c r="L43" t="n">
-        <v>231.56</v>
+        <v>130.8</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>-12.1</v>
+        <v>-11.9</v>
       </c>
       <c r="K44" t="n">
-        <v>55.22</v>
+        <v>54.31</v>
       </c>
       <c r="L44" t="n">
-        <v>56.53</v>
+        <v>55.59</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>18.08</v>
+        <v>14.48</v>
       </c>
       <c r="K45" t="n">
-        <v>44.4</v>
+        <v>35.56</v>
       </c>
       <c r="L45" t="n">
-        <v>47.94</v>
+        <v>38.39</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>28</v>
       </c>
       <c r="J46" t="n">
-        <v>21.06</v>
+        <v>20.39</v>
       </c>
       <c r="K46" t="n">
-        <v>-73.11</v>
+        <v>-70.79000000000001</v>
       </c>
       <c r="L46" t="n">
-        <v>76.08</v>
+        <v>73.67</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>24</v>
       </c>
       <c r="J47" t="n">
-        <v>63</v>
+        <v>51.09</v>
       </c>
       <c r="K47" t="n">
-        <v>-120.06</v>
+        <v>-97.36</v>
       </c>
       <c r="L47" t="n">
-        <v>135.59</v>
+        <v>109.95</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>29</v>
       </c>
       <c r="J48" t="n">
-        <v>-51.12</v>
+        <v>-52.15</v>
       </c>
       <c r="K48" t="n">
-        <v>12.18</v>
+        <v>12.42</v>
       </c>
       <c r="L48" t="n">
-        <v>52.55</v>
+        <v>53.61</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>66.69</v>
+        <v>60.42</v>
       </c>
       <c r="K49" t="n">
-        <v>-32.8</v>
+        <v>-29.71</v>
       </c>
       <c r="L49" t="n">
-        <v>74.31999999999999</v>
+        <v>67.33</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>84.73</v>
+        <v>58.66</v>
       </c>
       <c r="K50" t="n">
-        <v>-119.94</v>
+        <v>-83.03</v>
       </c>
       <c r="L50" t="n">
-        <v>146.85</v>
+        <v>101.67</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>103.21</v>
+        <v>77.01000000000001</v>
       </c>
       <c r="K51" t="n">
-        <v>-118.91</v>
+        <v>-88.73</v>
       </c>
       <c r="L51" t="n">
-        <v>157.45</v>
+        <v>117.49</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>-71.7</v>
+        <v>-53.71</v>
       </c>
       <c r="K52" t="n">
-        <v>88.94</v>
+        <v>66.62</v>
       </c>
       <c r="L52" t="n">
-        <v>114.24</v>
+        <v>85.56999999999999</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>-204.48</v>
+        <v>-129.93</v>
       </c>
       <c r="K53" t="n">
-        <v>-25.03</v>
+        <v>-15.91</v>
       </c>
       <c r="L53" t="n">
-        <v>206</v>
+        <v>130.9</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-28.32</v>
+        <v>-16.14</v>
       </c>
       <c r="K54" t="n">
-        <v>279.84</v>
+        <v>159.49</v>
       </c>
       <c r="L54" t="n">
-        <v>281.27</v>
+        <v>160.31</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>-144.45</v>
+        <v>-88.43000000000001</v>
       </c>
       <c r="K55" t="n">
-        <v>-91.41</v>
+        <v>-55.96</v>
       </c>
       <c r="L55" t="n">
-        <v>170.95</v>
+        <v>104.65</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>386.41</v>
+        <v>236.73</v>
       </c>
       <c r="K56" t="n">
-        <v>-66.28</v>
+        <v>-40.61</v>
       </c>
       <c r="L56" t="n">
-        <v>392.06</v>
+        <v>240.19</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>-341.4</v>
+        <v>-209.38</v>
       </c>
       <c r="K57" t="n">
-        <v>-196.64</v>
+        <v>-120.6</v>
       </c>
       <c r="L57" t="n">
-        <v>393.98</v>
+        <v>241.62</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>310.58</v>
+        <v>190.13</v>
       </c>
       <c r="K58" t="n">
-        <v>99.54000000000001</v>
+        <v>60.93</v>
       </c>
       <c r="L58" t="n">
-        <v>326.14</v>
+        <v>199.66</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>-42.72</v>
+        <v>-36.52</v>
       </c>
       <c r="K59" t="n">
-        <v>-36.45</v>
+        <v>-31.16</v>
       </c>
       <c r="L59" t="n">
-        <v>56.16</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>28</v>
       </c>
       <c r="J60" t="n">
-        <v>-48.51</v>
+        <v>-47.21</v>
       </c>
       <c r="K60" t="n">
-        <v>-44.66</v>
+        <v>-43.47</v>
       </c>
       <c r="L60" t="n">
-        <v>65.94</v>
+        <v>64.17</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>28</v>
       </c>
       <c r="J61" t="n">
-        <v>55.91</v>
+        <v>54.99</v>
       </c>
       <c r="K61" t="n">
-        <v>49.39</v>
+        <v>48.57</v>
       </c>
       <c r="L61" t="n">
-        <v>74.59999999999999</v>
+        <v>73.37</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>54.71</v>
+        <v>49.92</v>
       </c>
       <c r="K62" t="n">
-        <v>56.64</v>
+        <v>51.68</v>
       </c>
       <c r="L62" t="n">
-        <v>78.73999999999999</v>
+        <v>71.84999999999999</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>29</v>
       </c>
       <c r="J63" t="n">
-        <v>36</v>
+        <v>35.83</v>
       </c>
       <c r="K63" t="n">
-        <v>-15.82</v>
+        <v>-15.75</v>
       </c>
       <c r="L63" t="n">
-        <v>39.32</v>
+        <v>39.14</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>63.71</v>
+        <v>55.46</v>
       </c>
       <c r="K64" t="n">
-        <v>95.90000000000001</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="L64" t="n">
-        <v>115.13</v>
+        <v>100.23</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>125.12</v>
+        <v>94.2</v>
       </c>
       <c r="K65" t="n">
-        <v>-88.73</v>
+        <v>-66.81</v>
       </c>
       <c r="L65" t="n">
-        <v>153.39</v>
+        <v>115.49</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>27</v>
       </c>
       <c r="J66" t="n">
-        <v>65.15000000000001</v>
+        <v>50.98</v>
       </c>
       <c r="K66" t="n">
-        <v>-51.41</v>
+        <v>-40.22</v>
       </c>
       <c r="L66" t="n">
-        <v>82.98999999999999</v>
+        <v>64.93000000000001</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>-174.32</v>
+        <v>-117.26</v>
       </c>
       <c r="K67" t="n">
-        <v>60.45</v>
+        <v>40.66</v>
       </c>
       <c r="L67" t="n">
-        <v>184.5</v>
+        <v>124.11</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>27</v>
       </c>
       <c r="J68" t="n">
-        <v>-140.35</v>
+        <v>-93.17</v>
       </c>
       <c r="K68" t="n">
-        <v>-84.72</v>
+        <v>-56.23</v>
       </c>
       <c r="L68" t="n">
-        <v>163.94</v>
+        <v>108.82</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>28</v>
       </c>
       <c r="J69" t="n">
-        <v>-191.21</v>
+        <v>-132.52</v>
       </c>
       <c r="K69" t="n">
-        <v>6.43</v>
+        <v>4.46</v>
       </c>
       <c r="L69" t="n">
-        <v>191.31</v>
+        <v>132.6</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>-44.01</v>
+        <v>-26.89</v>
       </c>
       <c r="K70" t="n">
-        <v>276.72</v>
+        <v>169.1</v>
       </c>
       <c r="L70" t="n">
-        <v>280.2</v>
+        <v>171.22</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>34.44</v>
+        <v>19.41</v>
       </c>
       <c r="K71" t="n">
-        <v>-279.53</v>
+        <v>-157.57</v>
       </c>
       <c r="L71" t="n">
-        <v>281.65</v>
+        <v>158.76</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>28</v>
       </c>
       <c r="J72" t="n">
-        <v>278.7</v>
+        <v>180.54</v>
       </c>
       <c r="K72" t="n">
-        <v>222.71</v>
+        <v>144.28</v>
       </c>
       <c r="L72" t="n">
-        <v>356.75</v>
+        <v>231.11</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>29</v>
       </c>
       <c r="J73" t="n">
-        <v>-303.93</v>
+        <v>-204.02</v>
       </c>
       <c r="K73" t="n">
-        <v>83.48</v>
+        <v>56.04</v>
       </c>
       <c r="L73" t="n">
-        <v>315.18</v>
+        <v>211.58</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>29</v>
       </c>
       <c r="J74" t="n">
-        <v>10</v>
+        <v>10.44</v>
       </c>
       <c r="K74" t="n">
-        <v>-36.85</v>
+        <v>-38.49</v>
       </c>
       <c r="L74" t="n">
-        <v>38.18</v>
+        <v>39.89</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="K75" t="n">
-        <v>-66.34999999999999</v>
+        <v>-62.02</v>
       </c>
       <c r="L75" t="n">
-        <v>66.38</v>
+        <v>62.05</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>46.16</v>
+        <v>44.76</v>
       </c>
       <c r="K76" t="n">
-        <v>-31.75</v>
+        <v>-30.79</v>
       </c>
       <c r="L76" t="n">
-        <v>56.03</v>
+        <v>54.33</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>95.27</v>
+        <v>74.36</v>
       </c>
       <c r="K77" t="n">
-        <v>4.48</v>
+        <v>3.49</v>
       </c>
       <c r="L77" t="n">
-        <v>95.37</v>
+        <v>74.44</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>29</v>
       </c>
       <c r="J78" t="n">
-        <v>-11.33</v>
+        <v>-11.78</v>
       </c>
       <c r="K78" t="n">
-        <v>-40.69</v>
+        <v>-42.29</v>
       </c>
       <c r="L78" t="n">
-        <v>42.23</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>28</v>
       </c>
       <c r="J79" t="n">
-        <v>-113.09</v>
+        <v>-104.92</v>
       </c>
       <c r="K79" t="n">
-        <v>-52.72</v>
+        <v>-48.91</v>
       </c>
       <c r="L79" t="n">
-        <v>124.77</v>
+        <v>115.76</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>124.89</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="K80" t="n">
-        <v>-136.04</v>
+        <v>-97.17</v>
       </c>
       <c r="L80" t="n">
-        <v>184.67</v>
+        <v>131.91</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>-22.4</v>
+        <v>-15.54</v>
       </c>
       <c r="K81" t="n">
-        <v>-155.74</v>
+        <v>-108.03</v>
       </c>
       <c r="L81" t="n">
-        <v>157.34</v>
+        <v>109.14</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>23</v>
       </c>
       <c r="J82" t="n">
-        <v>177.31</v>
+        <v>118.17</v>
       </c>
       <c r="K82" t="n">
-        <v>223.05</v>
+        <v>148.66</v>
       </c>
       <c r="L82" t="n">
-        <v>284.94</v>
+        <v>189.9</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>-244.83</v>
+        <v>-162.28</v>
       </c>
       <c r="K83" t="n">
-        <v>-173.75</v>
+        <v>-115.17</v>
       </c>
       <c r="L83" t="n">
-        <v>300.22</v>
+        <v>198.99</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>-169.3</v>
+        <v>-117.29</v>
       </c>
       <c r="K84" t="n">
-        <v>-49.92</v>
+        <v>-34.59</v>
       </c>
       <c r="L84" t="n">
-        <v>176.51</v>
+        <v>122.29</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>-136.6</v>
+        <v>-89.97</v>
       </c>
       <c r="K85" t="n">
-        <v>-132.24</v>
+        <v>-87.09999999999999</v>
       </c>
       <c r="L85" t="n">
-        <v>190.13</v>
+        <v>125.22</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>-206.3</v>
+        <v>-123.73</v>
       </c>
       <c r="K86" t="n">
-        <v>242.68</v>
+        <v>145.55</v>
       </c>
       <c r="L86" t="n">
-        <v>318.52</v>
+        <v>191.03</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>-242.45</v>
+        <v>-135.5</v>
       </c>
       <c r="K87" t="n">
-        <v>-501.57</v>
+        <v>-280.31</v>
       </c>
       <c r="L87" t="n">
-        <v>557.1</v>
+        <v>311.34</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>451.03</v>
+        <v>280.23</v>
       </c>
       <c r="K88" t="n">
-        <v>-477.4</v>
+        <v>-296.62</v>
       </c>
       <c r="L88" t="n">
-        <v>656.77</v>
+        <v>408.06</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-08-25.xlsx
+++ b/output/2024-08-25.xlsx
@@ -640,13 +640,13 @@
         <v>29</v>
       </c>
       <c r="J14" t="n">
-        <v>34.15</v>
+        <v>30.51</v>
       </c>
       <c r="K14" t="n">
-        <v>-37.48</v>
+        <v>-33.49</v>
       </c>
       <c r="L14" t="n">
-        <v>50.7</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>27</v>
       </c>
       <c r="J15" t="n">
-        <v>-22.47</v>
+        <v>-20.09</v>
       </c>
       <c r="K15" t="n">
-        <v>74.81</v>
+        <v>66.86</v>
       </c>
       <c r="L15" t="n">
-        <v>78.11</v>
+        <v>69.81</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>27</v>
       </c>
       <c r="J16" t="n">
-        <v>48.95</v>
+        <v>43.73</v>
       </c>
       <c r="K16" t="n">
-        <v>13.19</v>
+        <v>11.79</v>
       </c>
       <c r="L16" t="n">
-        <v>50.7</v>
+        <v>45.29</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>-42.45</v>
+        <v>-40.55</v>
       </c>
       <c r="K17" t="n">
-        <v>-46.89</v>
+        <v>-44.78</v>
       </c>
       <c r="L17" t="n">
-        <v>63.26</v>
+        <v>60.41</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>24</v>
       </c>
       <c r="J18" t="n">
-        <v>-94.67</v>
+        <v>-89.63</v>
       </c>
       <c r="K18" t="n">
-        <v>-51.5</v>
+        <v>-48.76</v>
       </c>
       <c r="L18" t="n">
-        <v>107.77</v>
+        <v>102.04</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>55.88</v>
+        <v>53.06</v>
       </c>
       <c r="K19" t="n">
-        <v>34.9</v>
+        <v>33.14</v>
       </c>
       <c r="L19" t="n">
-        <v>65.89</v>
+        <v>62.56</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>74.2</v>
+        <v>74.16</v>
       </c>
       <c r="K20" t="n">
-        <v>37.32</v>
+        <v>37.3</v>
       </c>
       <c r="L20" t="n">
-        <v>83.06</v>
+        <v>83.01000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>23</v>
       </c>
       <c r="J21" t="n">
-        <v>75.27</v>
+        <v>76.61</v>
       </c>
       <c r="K21" t="n">
-        <v>-30.09</v>
+        <v>-30.62</v>
       </c>
       <c r="L21" t="n">
-        <v>81.06</v>
+        <v>82.51000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>49.14</v>
+        <v>49.02</v>
       </c>
       <c r="K22" t="n">
-        <v>80.88</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>94.64</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>28</v>
       </c>
       <c r="J23" t="n">
-        <v>-20.76</v>
+        <v>-21.45</v>
       </c>
       <c r="K23" t="n">
-        <v>-94.26000000000001</v>
+        <v>-97.37</v>
       </c>
       <c r="L23" t="n">
-        <v>96.52</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>28</v>
       </c>
       <c r="J24" t="n">
-        <v>-97.34</v>
+        <v>-98.95</v>
       </c>
       <c r="K24" t="n">
-        <v>89.25</v>
+        <v>90.73</v>
       </c>
       <c r="L24" t="n">
-        <v>132.06</v>
+        <v>134.25</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>-201.63</v>
+        <v>-208.3</v>
       </c>
       <c r="K25" t="n">
-        <v>-143.74</v>
+        <v>-148.5</v>
       </c>
       <c r="L25" t="n">
-        <v>247.62</v>
+        <v>255.82</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>29</v>
       </c>
       <c r="J26" t="n">
-        <v>151.91</v>
+        <v>155.75</v>
       </c>
       <c r="K26" t="n">
-        <v>38.66</v>
+        <v>39.64</v>
       </c>
       <c r="L26" t="n">
-        <v>156.76</v>
+        <v>160.71</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>-117.07</v>
+        <v>-124.34</v>
       </c>
       <c r="K27" t="n">
-        <v>135.31</v>
+        <v>143.71</v>
       </c>
       <c r="L27" t="n">
-        <v>178.92</v>
+        <v>190.03</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>-170.38</v>
+        <v>-180.18</v>
       </c>
       <c r="K28" t="n">
-        <v>-105.66</v>
+        <v>-111.73</v>
       </c>
       <c r="L28" t="n">
-        <v>200.49</v>
+        <v>212.01</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>29</v>
       </c>
       <c r="J29" t="n">
-        <v>34.94</v>
+        <v>31.14</v>
       </c>
       <c r="K29" t="n">
-        <v>28.9</v>
+        <v>25.76</v>
       </c>
       <c r="L29" t="n">
-        <v>45.34</v>
+        <v>40.41</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>68.97</v>
+        <v>63.47</v>
       </c>
       <c r="K30" t="n">
-        <v>-35.9</v>
+        <v>-33.04</v>
       </c>
       <c r="L30" t="n">
-        <v>77.76000000000001</v>
+        <v>71.55</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>-68.04000000000001</v>
+        <v>-61.82</v>
       </c>
       <c r="K31" t="n">
-        <v>46.35</v>
+        <v>42.11</v>
       </c>
       <c r="L31" t="n">
-        <v>82.31999999999999</v>
+        <v>74.79000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>10</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>-62.1</v>
+        <v>-59.16</v>
       </c>
       <c r="L32" t="n">
-        <v>62.9</v>
+        <v>59.93</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>-107.4</v>
+        <v>-100.62</v>
       </c>
       <c r="K33" t="n">
-        <v>-38.06</v>
+        <v>-35.66</v>
       </c>
       <c r="L33" t="n">
-        <v>113.94</v>
+        <v>106.76</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>28</v>
       </c>
       <c r="J34" t="n">
-        <v>94.06</v>
+        <v>87.45999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>34.94</v>
+        <v>32.49</v>
       </c>
       <c r="L34" t="n">
-        <v>100.34</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>37.27</v>
+        <v>37.42</v>
       </c>
       <c r="K35" t="n">
-        <v>-100.53</v>
+        <v>-100.93</v>
       </c>
       <c r="L35" t="n">
-        <v>107.21</v>
+        <v>107.64</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>27</v>
       </c>
       <c r="J36" t="n">
-        <v>54.08</v>
+        <v>53.51</v>
       </c>
       <c r="K36" t="n">
-        <v>-67.13</v>
+        <v>-66.43000000000001</v>
       </c>
       <c r="L36" t="n">
-        <v>86.2</v>
+        <v>85.3</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>-40.2</v>
+        <v>-40.47</v>
       </c>
       <c r="K37" t="n">
-        <v>115.45</v>
+        <v>116.24</v>
       </c>
       <c r="L37" t="n">
-        <v>122.25</v>
+        <v>123.09</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-168.11</v>
+        <v>-174.49</v>
       </c>
       <c r="K38" t="n">
-        <v>77.01000000000001</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="L38" t="n">
-        <v>184.91</v>
+        <v>191.93</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>66.48999999999999</v>
+        <v>69.86</v>
       </c>
       <c r="K39" t="n">
-        <v>114.65</v>
+        <v>120.45</v>
       </c>
       <c r="L39" t="n">
-        <v>132.54</v>
+        <v>139.24</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>29</v>
       </c>
       <c r="J40" t="n">
-        <v>71.40000000000001</v>
+        <v>72.53</v>
       </c>
       <c r="K40" t="n">
-        <v>86.56</v>
+        <v>87.92</v>
       </c>
       <c r="L40" t="n">
-        <v>112.21</v>
+        <v>113.98</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>123.27</v>
+        <v>128.19</v>
       </c>
       <c r="K41" t="n">
-        <v>-134.18</v>
+        <v>-139.54</v>
       </c>
       <c r="L41" t="n">
-        <v>182.2</v>
+        <v>189.49</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>26</v>
       </c>
       <c r="J42" t="n">
-        <v>16.54</v>
+        <v>17.22</v>
       </c>
       <c r="K42" t="n">
-        <v>-326.69</v>
+        <v>-340.13</v>
       </c>
       <c r="L42" t="n">
-        <v>327.1</v>
+        <v>340.57</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>-29.52</v>
+        <v>-31.05</v>
       </c>
       <c r="K43" t="n">
-        <v>-127.42</v>
+        <v>-134.03</v>
       </c>
       <c r="L43" t="n">
-        <v>130.8</v>
+        <v>137.58</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>-11.9</v>
+        <v>-10.82</v>
       </c>
       <c r="K44" t="n">
-        <v>54.31</v>
+        <v>49.35</v>
       </c>
       <c r="L44" t="n">
-        <v>55.59</v>
+        <v>50.52</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>14.48</v>
+        <v>13.38</v>
       </c>
       <c r="K45" t="n">
-        <v>35.56</v>
+        <v>32.85</v>
       </c>
       <c r="L45" t="n">
-        <v>38.39</v>
+        <v>35.47</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>28</v>
       </c>
       <c r="J46" t="n">
-        <v>20.39</v>
+        <v>18.58</v>
       </c>
       <c r="K46" t="n">
-        <v>-70.79000000000001</v>
+        <v>-64.51000000000001</v>
       </c>
       <c r="L46" t="n">
-        <v>73.67</v>
+        <v>67.13</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>24</v>
       </c>
       <c r="J47" t="n">
-        <v>51.09</v>
+        <v>48.94</v>
       </c>
       <c r="K47" t="n">
-        <v>-97.36</v>
+        <v>-93.27</v>
       </c>
       <c r="L47" t="n">
-        <v>109.95</v>
+        <v>105.33</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>29</v>
       </c>
       <c r="J48" t="n">
-        <v>-52.15</v>
+        <v>-47.37</v>
       </c>
       <c r="K48" t="n">
-        <v>12.42</v>
+        <v>11.28</v>
       </c>
       <c r="L48" t="n">
-        <v>53.61</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>60.42</v>
+        <v>56.76</v>
       </c>
       <c r="K49" t="n">
-        <v>-29.71</v>
+        <v>-27.91</v>
       </c>
       <c r="L49" t="n">
-        <v>67.33</v>
+        <v>63.25</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>58.66</v>
+        <v>58.72</v>
       </c>
       <c r="K50" t="n">
-        <v>-83.03</v>
+        <v>-83.12</v>
       </c>
       <c r="L50" t="n">
-        <v>101.67</v>
+        <v>101.77</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>77.01000000000001</v>
+        <v>76.45</v>
       </c>
       <c r="K51" t="n">
-        <v>-88.73</v>
+        <v>-88.08</v>
       </c>
       <c r="L51" t="n">
-        <v>117.49</v>
+        <v>116.64</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>-53.71</v>
+        <v>-52.9</v>
       </c>
       <c r="K52" t="n">
-        <v>66.62</v>
+        <v>65.62</v>
       </c>
       <c r="L52" t="n">
-        <v>85.56999999999999</v>
+        <v>84.29000000000001</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>-129.93</v>
+        <v>-134.28</v>
       </c>
       <c r="K53" t="n">
-        <v>-15.91</v>
+        <v>-16.44</v>
       </c>
       <c r="L53" t="n">
-        <v>130.9</v>
+        <v>135.29</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-16.14</v>
+        <v>-16.99</v>
       </c>
       <c r="K54" t="n">
-        <v>159.49</v>
+        <v>167.85</v>
       </c>
       <c r="L54" t="n">
-        <v>160.31</v>
+        <v>168.7</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>-88.43000000000001</v>
+        <v>-92</v>
       </c>
       <c r="K55" t="n">
-        <v>-55.96</v>
+        <v>-58.22</v>
       </c>
       <c r="L55" t="n">
-        <v>104.65</v>
+        <v>108.87</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>236.73</v>
+        <v>246.13</v>
       </c>
       <c r="K56" t="n">
-        <v>-40.61</v>
+        <v>-42.22</v>
       </c>
       <c r="L56" t="n">
-        <v>240.19</v>
+        <v>249.73</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>-209.38</v>
+        <v>-218.4</v>
       </c>
       <c r="K57" t="n">
-        <v>-120.6</v>
+        <v>-125.79</v>
       </c>
       <c r="L57" t="n">
-        <v>241.62</v>
+        <v>252.04</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>190.13</v>
+        <v>197.29</v>
       </c>
       <c r="K58" t="n">
-        <v>60.93</v>
+        <v>63.23</v>
       </c>
       <c r="L58" t="n">
-        <v>199.66</v>
+        <v>207.18</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>-36.52</v>
+        <v>-33.5</v>
       </c>
       <c r="K59" t="n">
-        <v>-31.16</v>
+        <v>-28.59</v>
       </c>
       <c r="L59" t="n">
-        <v>48.01</v>
+        <v>44.04</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>28</v>
       </c>
       <c r="J60" t="n">
-        <v>-47.21</v>
+        <v>-42.34</v>
       </c>
       <c r="K60" t="n">
-        <v>-43.47</v>
+        <v>-38.98</v>
       </c>
       <c r="L60" t="n">
-        <v>64.17</v>
+        <v>57.55</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>28</v>
       </c>
       <c r="J61" t="n">
-        <v>54.99</v>
+        <v>50.23</v>
       </c>
       <c r="K61" t="n">
-        <v>48.57</v>
+        <v>44.37</v>
       </c>
       <c r="L61" t="n">
-        <v>73.37</v>
+        <v>67.02</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>49.92</v>
+        <v>46.95</v>
       </c>
       <c r="K62" t="n">
-        <v>51.68</v>
+        <v>48.61</v>
       </c>
       <c r="L62" t="n">
-        <v>71.84999999999999</v>
+        <v>67.58</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>29</v>
       </c>
       <c r="J63" t="n">
-        <v>35.83</v>
+        <v>33.06</v>
       </c>
       <c r="K63" t="n">
-        <v>-15.75</v>
+        <v>-14.53</v>
       </c>
       <c r="L63" t="n">
-        <v>39.14</v>
+        <v>36.11</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>55.46</v>
+        <v>52.78</v>
       </c>
       <c r="K64" t="n">
-        <v>83.48999999999999</v>
+        <v>79.45</v>
       </c>
       <c r="L64" t="n">
-        <v>100.23</v>
+        <v>95.38</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>94.2</v>
+        <v>94.56</v>
       </c>
       <c r="K65" t="n">
-        <v>-66.81</v>
+        <v>-67.06</v>
       </c>
       <c r="L65" t="n">
-        <v>115.49</v>
+        <v>115.92</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>27</v>
       </c>
       <c r="J66" t="n">
-        <v>50.98</v>
+        <v>50.27</v>
       </c>
       <c r="K66" t="n">
-        <v>-40.22</v>
+        <v>-39.67</v>
       </c>
       <c r="L66" t="n">
-        <v>64.93000000000001</v>
+        <v>64.04000000000001</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>-117.26</v>
+        <v>-118.25</v>
       </c>
       <c r="K67" t="n">
-        <v>40.66</v>
+        <v>41.01</v>
       </c>
       <c r="L67" t="n">
-        <v>124.11</v>
+        <v>125.16</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>27</v>
       </c>
       <c r="J68" t="n">
-        <v>-93.17</v>
+        <v>-95.72</v>
       </c>
       <c r="K68" t="n">
-        <v>-56.23</v>
+        <v>-57.77</v>
       </c>
       <c r="L68" t="n">
-        <v>108.82</v>
+        <v>111.8</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>28</v>
       </c>
       <c r="J69" t="n">
-        <v>-132.52</v>
+        <v>-136.12</v>
       </c>
       <c r="K69" t="n">
-        <v>4.46</v>
+        <v>4.58</v>
       </c>
       <c r="L69" t="n">
-        <v>132.6</v>
+        <v>136.19</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>-26.89</v>
+        <v>-28</v>
       </c>
       <c r="K70" t="n">
-        <v>169.1</v>
+        <v>176.09</v>
       </c>
       <c r="L70" t="n">
-        <v>171.22</v>
+        <v>178.3</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>19.41</v>
+        <v>20.38</v>
       </c>
       <c r="K71" t="n">
-        <v>-157.57</v>
+        <v>-165.41</v>
       </c>
       <c r="L71" t="n">
-        <v>158.76</v>
+        <v>166.67</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>28</v>
       </c>
       <c r="J72" t="n">
-        <v>180.54</v>
+        <v>186.96</v>
       </c>
       <c r="K72" t="n">
-        <v>144.28</v>
+        <v>149.4</v>
       </c>
       <c r="L72" t="n">
-        <v>231.11</v>
+        <v>239.32</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>29</v>
       </c>
       <c r="J73" t="n">
-        <v>-204.02</v>
+        <v>-208.93</v>
       </c>
       <c r="K73" t="n">
-        <v>56.04</v>
+        <v>57.39</v>
       </c>
       <c r="L73" t="n">
-        <v>211.58</v>
+        <v>216.67</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>29</v>
       </c>
       <c r="J74" t="n">
-        <v>10.44</v>
+        <v>9.57</v>
       </c>
       <c r="K74" t="n">
-        <v>-38.49</v>
+        <v>-35.26</v>
       </c>
       <c r="L74" t="n">
-        <v>39.89</v>
+        <v>36.54</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="K75" t="n">
-        <v>-62.02</v>
+        <v>-57.03</v>
       </c>
       <c r="L75" t="n">
-        <v>62.05</v>
+        <v>57.06</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>44.76</v>
+        <v>41.83</v>
       </c>
       <c r="K76" t="n">
-        <v>-30.79</v>
+        <v>-28.77</v>
       </c>
       <c r="L76" t="n">
-        <v>54.33</v>
+        <v>50.77</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>74.36</v>
+        <v>70.94</v>
       </c>
       <c r="K77" t="n">
-        <v>3.49</v>
+        <v>3.33</v>
       </c>
       <c r="L77" t="n">
-        <v>74.44</v>
+        <v>71.02</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>29</v>
       </c>
       <c r="J78" t="n">
-        <v>-11.78</v>
+        <v>-11.12</v>
       </c>
       <c r="K78" t="n">
-        <v>-42.29</v>
+        <v>-39.92</v>
       </c>
       <c r="L78" t="n">
-        <v>43.9</v>
+        <v>41.44</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>28</v>
       </c>
       <c r="J79" t="n">
-        <v>-104.92</v>
+        <v>-101.04</v>
       </c>
       <c r="K79" t="n">
-        <v>-48.91</v>
+        <v>-47.1</v>
       </c>
       <c r="L79" t="n">
-        <v>115.76</v>
+        <v>111.48</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>89.20999999999999</v>
+        <v>88.59</v>
       </c>
       <c r="K80" t="n">
-        <v>-97.17</v>
+        <v>-96.5</v>
       </c>
       <c r="L80" t="n">
-        <v>131.91</v>
+        <v>130.99</v>
       </c>
     </row>
     <row r="81">
@@ -3457,10 +3457,10 @@
         <v>-15.54</v>
       </c>
       <c r="K81" t="n">
-        <v>-108.03</v>
+        <v>-108.02</v>
       </c>
       <c r="L81" t="n">
-        <v>109.14</v>
+        <v>109.13</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>23</v>
       </c>
       <c r="J82" t="n">
-        <v>118.17</v>
+        <v>119.91</v>
       </c>
       <c r="K82" t="n">
-        <v>148.66</v>
+        <v>150.84</v>
       </c>
       <c r="L82" t="n">
-        <v>189.9</v>
+        <v>192.7</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>-162.28</v>
+        <v>-167.97</v>
       </c>
       <c r="K83" t="n">
-        <v>-115.17</v>
+        <v>-119.21</v>
       </c>
       <c r="L83" t="n">
-        <v>198.99</v>
+        <v>205.97</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>-117.29</v>
+        <v>-120.59</v>
       </c>
       <c r="K84" t="n">
-        <v>-34.59</v>
+        <v>-35.56</v>
       </c>
       <c r="L84" t="n">
-        <v>122.29</v>
+        <v>125.72</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>-89.97</v>
+        <v>-92.31</v>
       </c>
       <c r="K85" t="n">
-        <v>-87.09999999999999</v>
+        <v>-89.36</v>
       </c>
       <c r="L85" t="n">
-        <v>125.22</v>
+        <v>128.48</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>-123.73</v>
+        <v>-128.51</v>
       </c>
       <c r="K86" t="n">
-        <v>145.55</v>
+        <v>151.17</v>
       </c>
       <c r="L86" t="n">
-        <v>191.03</v>
+        <v>198.41</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>-135.5</v>
+        <v>-141.37</v>
       </c>
       <c r="K87" t="n">
-        <v>-280.31</v>
+        <v>-292.45</v>
       </c>
       <c r="L87" t="n">
-        <v>311.34</v>
+        <v>324.82</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>280.23</v>
+        <v>294.59</v>
       </c>
       <c r="K88" t="n">
-        <v>-296.62</v>
+        <v>-311.81</v>
       </c>
       <c r="L88" t="n">
-        <v>408.06</v>
+        <v>428.96</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-08-25.xlsx
+++ b/output/2024-08-25.xlsx
@@ -640,13 +640,13 @@
         <v>29</v>
       </c>
       <c r="J14" t="n">
-        <v>30.51</v>
+        <v>22.88</v>
       </c>
       <c r="K14" t="n">
-        <v>-33.49</v>
+        <v>-25.12</v>
       </c>
       <c r="L14" t="n">
-        <v>45.3</v>
+        <v>33.98</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>27</v>
       </c>
       <c r="J15" t="n">
-        <v>-20.09</v>
+        <v>-15.06</v>
       </c>
       <c r="K15" t="n">
-        <v>66.86</v>
+        <v>50.14</v>
       </c>
       <c r="L15" t="n">
-        <v>69.81</v>
+        <v>52.36</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>27</v>
       </c>
       <c r="J16" t="n">
-        <v>43.73</v>
+        <v>32.8</v>
       </c>
       <c r="K16" t="n">
-        <v>11.79</v>
+        <v>8.84</v>
       </c>
       <c r="L16" t="n">
-        <v>45.29</v>
+        <v>33.97</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>-40.55</v>
+        <v>-30.41</v>
       </c>
       <c r="K17" t="n">
-        <v>-44.78</v>
+        <v>-33.59</v>
       </c>
       <c r="L17" t="n">
-        <v>60.41</v>
+        <v>45.31</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>24</v>
       </c>
       <c r="J18" t="n">
-        <v>-89.63</v>
+        <v>-67.23</v>
       </c>
       <c r="K18" t="n">
-        <v>-48.76</v>
+        <v>-36.57</v>
       </c>
       <c r="L18" t="n">
-        <v>102.04</v>
+        <v>76.53</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>53.06</v>
+        <v>39.8</v>
       </c>
       <c r="K19" t="n">
-        <v>33.14</v>
+        <v>24.86</v>
       </c>
       <c r="L19" t="n">
-        <v>62.56</v>
+        <v>46.92</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>74.16</v>
+        <v>55.62</v>
       </c>
       <c r="K20" t="n">
-        <v>37.3</v>
+        <v>27.98</v>
       </c>
       <c r="L20" t="n">
-        <v>83.01000000000001</v>
+        <v>62.26</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>23</v>
       </c>
       <c r="J21" t="n">
-        <v>76.61</v>
+        <v>57.46</v>
       </c>
       <c r="K21" t="n">
-        <v>-30.62</v>
+        <v>-22.97</v>
       </c>
       <c r="L21" t="n">
-        <v>82.51000000000001</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>49.02</v>
+        <v>36.76</v>
       </c>
       <c r="K22" t="n">
-        <v>80.68000000000001</v>
+        <v>60.51</v>
       </c>
       <c r="L22" t="n">
-        <v>94.40000000000001</v>
+        <v>70.8</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>28</v>
       </c>
       <c r="J23" t="n">
-        <v>-21.45</v>
+        <v>-16.09</v>
       </c>
       <c r="K23" t="n">
-        <v>-97.37</v>
+        <v>-73.03</v>
       </c>
       <c r="L23" t="n">
-        <v>99.7</v>
+        <v>74.78</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>28</v>
       </c>
       <c r="J24" t="n">
-        <v>-98.95</v>
+        <v>-74.20999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>90.73</v>
+        <v>68.05</v>
       </c>
       <c r="L24" t="n">
-        <v>134.25</v>
+        <v>100.69</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>-208.3</v>
+        <v>-140.88</v>
       </c>
       <c r="K25" t="n">
-        <v>-148.5</v>
+        <v>-100.44</v>
       </c>
       <c r="L25" t="n">
-        <v>255.82</v>
+        <v>173.02</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>29</v>
       </c>
       <c r="J26" t="n">
-        <v>155.75</v>
+        <v>116.81</v>
       </c>
       <c r="K26" t="n">
-        <v>39.64</v>
+        <v>29.73</v>
       </c>
       <c r="L26" t="n">
-        <v>160.71</v>
+        <v>120.53</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>-124.34</v>
+        <v>-93.26000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>143.71</v>
+        <v>107.78</v>
       </c>
       <c r="L27" t="n">
-        <v>190.03</v>
+        <v>142.52</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>-180.18</v>
+        <v>-135.13</v>
       </c>
       <c r="K28" t="n">
-        <v>-111.73</v>
+        <v>-83.8</v>
       </c>
       <c r="L28" t="n">
-        <v>212.01</v>
+        <v>159.01</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>29</v>
       </c>
       <c r="J29" t="n">
-        <v>31.14</v>
+        <v>23.35</v>
       </c>
       <c r="K29" t="n">
-        <v>25.76</v>
+        <v>19.32</v>
       </c>
       <c r="L29" t="n">
-        <v>40.41</v>
+        <v>30.31</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>63.47</v>
+        <v>47.6</v>
       </c>
       <c r="K30" t="n">
-        <v>-33.04</v>
+        <v>-24.78</v>
       </c>
       <c r="L30" t="n">
-        <v>71.55</v>
+        <v>53.66</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>-61.82</v>
+        <v>-46.36</v>
       </c>
       <c r="K31" t="n">
-        <v>42.11</v>
+        <v>31.58</v>
       </c>
       <c r="L31" t="n">
-        <v>74.79000000000001</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>9.529999999999999</v>
+        <v>7.15</v>
       </c>
       <c r="K32" t="n">
-        <v>-59.16</v>
+        <v>-44.37</v>
       </c>
       <c r="L32" t="n">
-        <v>59.93</v>
+        <v>44.94</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>-100.62</v>
+        <v>-75.47</v>
       </c>
       <c r="K33" t="n">
-        <v>-35.66</v>
+        <v>-26.74</v>
       </c>
       <c r="L33" t="n">
-        <v>106.76</v>
+        <v>80.06999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>28</v>
       </c>
       <c r="J34" t="n">
-        <v>87.45999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>32.49</v>
+        <v>24.37</v>
       </c>
       <c r="L34" t="n">
-        <v>93.3</v>
+        <v>69.98</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>37.42</v>
+        <v>28.07</v>
       </c>
       <c r="K35" t="n">
-        <v>-100.93</v>
+        <v>-75.7</v>
       </c>
       <c r="L35" t="n">
-        <v>107.64</v>
+        <v>80.73</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>27</v>
       </c>
       <c r="J36" t="n">
-        <v>53.51</v>
+        <v>40.14</v>
       </c>
       <c r="K36" t="n">
-        <v>-66.43000000000001</v>
+        <v>-49.82</v>
       </c>
       <c r="L36" t="n">
-        <v>85.3</v>
+        <v>63.98</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>-40.47</v>
+        <v>-30.35</v>
       </c>
       <c r="K37" t="n">
-        <v>116.24</v>
+        <v>87.18000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>123.09</v>
+        <v>92.31</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-174.49</v>
+        <v>-130.87</v>
       </c>
       <c r="K38" t="n">
-        <v>79.93000000000001</v>
+        <v>59.95</v>
       </c>
       <c r="L38" t="n">
-        <v>191.93</v>
+        <v>143.95</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>69.86</v>
+        <v>50.71</v>
       </c>
       <c r="K39" t="n">
-        <v>120.45</v>
+        <v>87.45</v>
       </c>
       <c r="L39" t="n">
-        <v>139.24</v>
+        <v>101.09</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>29</v>
       </c>
       <c r="J40" t="n">
-        <v>72.53</v>
+        <v>54.4</v>
       </c>
       <c r="K40" t="n">
-        <v>87.92</v>
+        <v>65.94</v>
       </c>
       <c r="L40" t="n">
-        <v>113.98</v>
+        <v>85.48</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>128.19</v>
+        <v>96.14</v>
       </c>
       <c r="K41" t="n">
-        <v>-139.54</v>
+        <v>-104.65</v>
       </c>
       <c r="L41" t="n">
-        <v>189.49</v>
+        <v>142.11</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>26</v>
       </c>
       <c r="J42" t="n">
-        <v>17.22</v>
+        <v>12.91</v>
       </c>
       <c r="K42" t="n">
-        <v>-340.13</v>
+        <v>-255.1</v>
       </c>
       <c r="L42" t="n">
-        <v>340.57</v>
+        <v>255.43</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>-31.05</v>
+        <v>-23.29</v>
       </c>
       <c r="K43" t="n">
-        <v>-134.03</v>
+        <v>-100.52</v>
       </c>
       <c r="L43" t="n">
-        <v>137.58</v>
+        <v>103.19</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>-10.82</v>
+        <v>-8.02</v>
       </c>
       <c r="K44" t="n">
-        <v>49.35</v>
+        <v>36.59</v>
       </c>
       <c r="L44" t="n">
-        <v>50.52</v>
+        <v>37.46</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>13.38</v>
+        <v>10.03</v>
       </c>
       <c r="K45" t="n">
-        <v>32.85</v>
+        <v>24.64</v>
       </c>
       <c r="L45" t="n">
-        <v>35.47</v>
+        <v>26.61</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>28</v>
       </c>
       <c r="J46" t="n">
-        <v>18.58</v>
+        <v>13.94</v>
       </c>
       <c r="K46" t="n">
-        <v>-64.51000000000001</v>
+        <v>-48.38</v>
       </c>
       <c r="L46" t="n">
-        <v>67.13</v>
+        <v>50.35</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>24</v>
       </c>
       <c r="J47" t="n">
-        <v>48.94</v>
+        <v>36.7</v>
       </c>
       <c r="K47" t="n">
-        <v>-93.27</v>
+        <v>-69.95</v>
       </c>
       <c r="L47" t="n">
-        <v>105.33</v>
+        <v>79</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>29</v>
       </c>
       <c r="J48" t="n">
-        <v>-47.37</v>
+        <v>-35.53</v>
       </c>
       <c r="K48" t="n">
-        <v>11.28</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="L48" t="n">
-        <v>48.7</v>
+        <v>36.53</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>56.76</v>
+        <v>42.57</v>
       </c>
       <c r="K49" t="n">
-        <v>-27.91</v>
+        <v>-20.94</v>
       </c>
       <c r="L49" t="n">
-        <v>63.25</v>
+        <v>47.44</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>58.72</v>
+        <v>44.04</v>
       </c>
       <c r="K50" t="n">
-        <v>-83.12</v>
+        <v>-62.34</v>
       </c>
       <c r="L50" t="n">
-        <v>101.77</v>
+        <v>76.33</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>76.45</v>
+        <v>57.34</v>
       </c>
       <c r="K51" t="n">
-        <v>-88.08</v>
+        <v>-66.06</v>
       </c>
       <c r="L51" t="n">
-        <v>116.64</v>
+        <v>87.48</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>-52.9</v>
+        <v>-39.68</v>
       </c>
       <c r="K52" t="n">
-        <v>65.62</v>
+        <v>49.22</v>
       </c>
       <c r="L52" t="n">
-        <v>84.29000000000001</v>
+        <v>63.22</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>-134.28</v>
+        <v>-100.71</v>
       </c>
       <c r="K53" t="n">
-        <v>-16.44</v>
+        <v>-12.33</v>
       </c>
       <c r="L53" t="n">
-        <v>135.29</v>
+        <v>101.46</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-16.99</v>
+        <v>-12.74</v>
       </c>
       <c r="K54" t="n">
-        <v>167.85</v>
+        <v>125.88</v>
       </c>
       <c r="L54" t="n">
-        <v>168.7</v>
+        <v>126.53</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>-92</v>
+        <v>-69</v>
       </c>
       <c r="K55" t="n">
-        <v>-58.22</v>
+        <v>-43.66</v>
       </c>
       <c r="L55" t="n">
-        <v>108.87</v>
+        <v>81.65000000000001</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>246.13</v>
+        <v>184.6</v>
       </c>
       <c r="K56" t="n">
-        <v>-42.22</v>
+        <v>-31.66</v>
       </c>
       <c r="L56" t="n">
-        <v>249.73</v>
+        <v>187.29</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>-218.4</v>
+        <v>-163.8</v>
       </c>
       <c r="K57" t="n">
-        <v>-125.79</v>
+        <v>-94.34999999999999</v>
       </c>
       <c r="L57" t="n">
-        <v>252.04</v>
+        <v>189.03</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>197.29</v>
+        <v>147.97</v>
       </c>
       <c r="K58" t="n">
-        <v>63.23</v>
+        <v>47.42</v>
       </c>
       <c r="L58" t="n">
-        <v>207.18</v>
+        <v>155.38</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>-33.5</v>
+        <v>-25.13</v>
       </c>
       <c r="K59" t="n">
-        <v>-28.59</v>
+        <v>-21.44</v>
       </c>
       <c r="L59" t="n">
-        <v>44.04</v>
+        <v>33.03</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>28</v>
       </c>
       <c r="J60" t="n">
-        <v>-42.34</v>
+        <v>-31.76</v>
       </c>
       <c r="K60" t="n">
-        <v>-38.98</v>
+        <v>-29.24</v>
       </c>
       <c r="L60" t="n">
-        <v>57.55</v>
+        <v>43.17</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>28</v>
       </c>
       <c r="J61" t="n">
-        <v>50.23</v>
+        <v>37.24</v>
       </c>
       <c r="K61" t="n">
-        <v>44.37</v>
+        <v>32.89</v>
       </c>
       <c r="L61" t="n">
-        <v>67.02</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>46.95</v>
+        <v>35.21</v>
       </c>
       <c r="K62" t="n">
-        <v>48.61</v>
+        <v>36.46</v>
       </c>
       <c r="L62" t="n">
-        <v>67.58</v>
+        <v>50.69</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>29</v>
       </c>
       <c r="J63" t="n">
-        <v>33.06</v>
+        <v>11.55</v>
       </c>
       <c r="K63" t="n">
-        <v>-14.53</v>
+        <v>-5.08</v>
       </c>
       <c r="L63" t="n">
-        <v>36.11</v>
+        <v>12.62</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>52.78</v>
+        <v>39.32</v>
       </c>
       <c r="K64" t="n">
-        <v>79.45</v>
+        <v>59.19</v>
       </c>
       <c r="L64" t="n">
-        <v>95.38</v>
+        <v>71.06</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>94.56</v>
+        <v>66.73</v>
       </c>
       <c r="K65" t="n">
-        <v>-67.06</v>
+        <v>-47.33</v>
       </c>
       <c r="L65" t="n">
-        <v>115.92</v>
+        <v>81.81</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>27</v>
       </c>
       <c r="J66" t="n">
-        <v>50.27</v>
+        <v>37.71</v>
       </c>
       <c r="K66" t="n">
-        <v>-39.67</v>
+        <v>-29.75</v>
       </c>
       <c r="L66" t="n">
-        <v>64.04000000000001</v>
+        <v>48.03</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>-118.25</v>
+        <v>-88.69</v>
       </c>
       <c r="K67" t="n">
-        <v>41.01</v>
+        <v>30.76</v>
       </c>
       <c r="L67" t="n">
-        <v>125.16</v>
+        <v>93.87</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>27</v>
       </c>
       <c r="J68" t="n">
-        <v>-95.72</v>
+        <v>-71.79000000000001</v>
       </c>
       <c r="K68" t="n">
-        <v>-57.77</v>
+        <v>-43.33</v>
       </c>
       <c r="L68" t="n">
-        <v>111.8</v>
+        <v>83.84999999999999</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>28</v>
       </c>
       <c r="J69" t="n">
-        <v>-136.12</v>
+        <v>-102.09</v>
       </c>
       <c r="K69" t="n">
-        <v>4.58</v>
+        <v>3.43</v>
       </c>
       <c r="L69" t="n">
-        <v>136.19</v>
+        <v>102.14</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>-28</v>
+        <v>-21</v>
       </c>
       <c r="K70" t="n">
-        <v>176.09</v>
+        <v>132.07</v>
       </c>
       <c r="L70" t="n">
-        <v>178.3</v>
+        <v>133.73</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>20.38</v>
+        <v>15.29</v>
       </c>
       <c r="K71" t="n">
-        <v>-165.41</v>
+        <v>-124.06</v>
       </c>
       <c r="L71" t="n">
-        <v>166.67</v>
+        <v>125</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>28</v>
       </c>
       <c r="J72" t="n">
-        <v>186.96</v>
+        <v>138.18</v>
       </c>
       <c r="K72" t="n">
-        <v>149.4</v>
+        <v>110.43</v>
       </c>
       <c r="L72" t="n">
-        <v>239.32</v>
+        <v>176.89</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>29</v>
       </c>
       <c r="J73" t="n">
-        <v>-208.93</v>
+        <v>-156.7</v>
       </c>
       <c r="K73" t="n">
-        <v>57.39</v>
+        <v>43.04</v>
       </c>
       <c r="L73" t="n">
-        <v>216.67</v>
+        <v>162.5</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>29</v>
       </c>
       <c r="J74" t="n">
-        <v>9.57</v>
+        <v>7.04</v>
       </c>
       <c r="K74" t="n">
-        <v>-35.26</v>
+        <v>-25.95</v>
       </c>
       <c r="L74" t="n">
-        <v>36.54</v>
+        <v>26.89</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>1.79</v>
+        <v>1.33</v>
       </c>
       <c r="K75" t="n">
-        <v>-57.03</v>
+        <v>-42.44</v>
       </c>
       <c r="L75" t="n">
-        <v>57.06</v>
+        <v>42.46</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>41.83</v>
+        <v>28.96</v>
       </c>
       <c r="K76" t="n">
-        <v>-28.77</v>
+        <v>-19.92</v>
       </c>
       <c r="L76" t="n">
-        <v>50.77</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>70.94</v>
+        <v>53.21</v>
       </c>
       <c r="K77" t="n">
-        <v>3.33</v>
+        <v>2.5</v>
       </c>
       <c r="L77" t="n">
-        <v>71.02</v>
+        <v>53.27</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>29</v>
       </c>
       <c r="J78" t="n">
-        <v>-11.12</v>
+        <v>-6.94</v>
       </c>
       <c r="K78" t="n">
-        <v>-39.92</v>
+        <v>-24.91</v>
       </c>
       <c r="L78" t="n">
-        <v>41.44</v>
+        <v>25.86</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>28</v>
       </c>
       <c r="J79" t="n">
-        <v>-101.04</v>
+        <v>-59.14</v>
       </c>
       <c r="K79" t="n">
-        <v>-47.1</v>
+        <v>-27.57</v>
       </c>
       <c r="L79" t="n">
-        <v>111.48</v>
+        <v>65.25</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>88.59</v>
+        <v>66.44</v>
       </c>
       <c r="K80" t="n">
-        <v>-96.5</v>
+        <v>-72.37</v>
       </c>
       <c r="L80" t="n">
-        <v>130.99</v>
+        <v>98.23999999999999</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>-15.54</v>
+        <v>-11.12</v>
       </c>
       <c r="K81" t="n">
-        <v>-108.02</v>
+        <v>-77.29000000000001</v>
       </c>
       <c r="L81" t="n">
-        <v>109.13</v>
+        <v>78.09</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>23</v>
       </c>
       <c r="J82" t="n">
-        <v>119.91</v>
+        <v>89.93000000000001</v>
       </c>
       <c r="K82" t="n">
-        <v>150.84</v>
+        <v>113.13</v>
       </c>
       <c r="L82" t="n">
-        <v>192.7</v>
+        <v>144.52</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>-167.97</v>
+        <v>-125.98</v>
       </c>
       <c r="K83" t="n">
-        <v>-119.21</v>
+        <v>-89.40000000000001</v>
       </c>
       <c r="L83" t="n">
-        <v>205.97</v>
+        <v>154.48</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>-120.59</v>
+        <v>-90.44</v>
       </c>
       <c r="K84" t="n">
-        <v>-35.56</v>
+        <v>-26.67</v>
       </c>
       <c r="L84" t="n">
-        <v>125.72</v>
+        <v>94.29000000000001</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>-92.31</v>
+        <v>-67.67</v>
       </c>
       <c r="K85" t="n">
-        <v>-89.36</v>
+        <v>-65.51000000000001</v>
       </c>
       <c r="L85" t="n">
-        <v>128.48</v>
+        <v>94.19</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>-128.51</v>
+        <v>-94.08</v>
       </c>
       <c r="K86" t="n">
-        <v>151.17</v>
+        <v>110.67</v>
       </c>
       <c r="L86" t="n">
-        <v>198.41</v>
+        <v>145.25</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>-141.37</v>
+        <v>-91.59999999999999</v>
       </c>
       <c r="K87" t="n">
-        <v>-292.45</v>
+        <v>-189.5</v>
       </c>
       <c r="L87" t="n">
-        <v>324.82</v>
+        <v>210.48</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>294.59</v>
+        <v>205.95</v>
       </c>
       <c r="K88" t="n">
-        <v>-311.81</v>
+        <v>-217.99</v>
       </c>
       <c r="L88" t="n">
-        <v>428.96</v>
+        <v>299.89</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-08-25.xlsx
+++ b/output/2024-08-25.xlsx
@@ -640,13 +640,13 @@
         <v>29</v>
       </c>
       <c r="J14" t="n">
-        <v>22.88</v>
+        <v>23.16</v>
       </c>
       <c r="K14" t="n">
-        <v>-25.12</v>
+        <v>-25.42</v>
       </c>
       <c r="L14" t="n">
-        <v>33.98</v>
+        <v>34.39</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>27</v>
       </c>
       <c r="J15" t="n">
-        <v>-15.06</v>
+        <v>-14.56</v>
       </c>
       <c r="K15" t="n">
-        <v>50.14</v>
+        <v>48.45</v>
       </c>
       <c r="L15" t="n">
-        <v>52.36</v>
+        <v>50.59</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>27</v>
       </c>
       <c r="J16" t="n">
-        <v>32.8</v>
+        <v>33.29</v>
       </c>
       <c r="K16" t="n">
-        <v>8.84</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>33.97</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>-30.41</v>
+        <v>-31.64</v>
       </c>
       <c r="K17" t="n">
-        <v>-33.59</v>
+        <v>-34.94</v>
       </c>
       <c r="L17" t="n">
-        <v>45.31</v>
+        <v>47.14</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>24</v>
       </c>
       <c r="J18" t="n">
-        <v>-67.23</v>
+        <v>-65.22</v>
       </c>
       <c r="K18" t="n">
-        <v>-36.57</v>
+        <v>-35.48</v>
       </c>
       <c r="L18" t="n">
-        <v>76.53</v>
+        <v>74.23999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>39.8</v>
+        <v>40.79</v>
       </c>
       <c r="K19" t="n">
-        <v>24.86</v>
+        <v>25.48</v>
       </c>
       <c r="L19" t="n">
-        <v>46.92</v>
+        <v>48.09</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>55.62</v>
+        <v>58.13</v>
       </c>
       <c r="K20" t="n">
-        <v>27.98</v>
+        <v>29.24</v>
       </c>
       <c r="L20" t="n">
-        <v>62.26</v>
+        <v>65.06</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>23</v>
       </c>
       <c r="J21" t="n">
-        <v>57.46</v>
+        <v>60.53</v>
       </c>
       <c r="K21" t="n">
-        <v>-22.97</v>
+        <v>-24.19</v>
       </c>
       <c r="L21" t="n">
-        <v>61.88</v>
+        <v>65.19</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>36.76</v>
+        <v>37.33</v>
       </c>
       <c r="K22" t="n">
-        <v>60.51</v>
+        <v>61.44</v>
       </c>
       <c r="L22" t="n">
-        <v>70.8</v>
+        <v>71.89</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>28</v>
       </c>
       <c r="J23" t="n">
-        <v>-16.09</v>
+        <v>-16.86</v>
       </c>
       <c r="K23" t="n">
-        <v>-73.03</v>
+        <v>-76.56</v>
       </c>
       <c r="L23" t="n">
-        <v>74.78</v>
+        <v>78.39</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>28</v>
       </c>
       <c r="J24" t="n">
-        <v>-74.20999999999999</v>
+        <v>-74.36</v>
       </c>
       <c r="K24" t="n">
-        <v>68.05</v>
+        <v>68.19</v>
       </c>
       <c r="L24" t="n">
-        <v>100.69</v>
+        <v>100.89</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>-140.88</v>
+        <v>-135.82</v>
       </c>
       <c r="K25" t="n">
-        <v>-100.44</v>
+        <v>-96.83</v>
       </c>
       <c r="L25" t="n">
-        <v>173.02</v>
+        <v>166.8</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>29</v>
       </c>
       <c r="J26" t="n">
-        <v>116.81</v>
+        <v>120.08</v>
       </c>
       <c r="K26" t="n">
-        <v>29.73</v>
+        <v>30.56</v>
       </c>
       <c r="L26" t="n">
-        <v>120.53</v>
+        <v>123.91</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>-93.26000000000001</v>
+        <v>-95.56</v>
       </c>
       <c r="K27" t="n">
-        <v>107.78</v>
+        <v>110.45</v>
       </c>
       <c r="L27" t="n">
-        <v>142.52</v>
+        <v>146.05</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>-135.13</v>
+        <v>-135.54</v>
       </c>
       <c r="K28" t="n">
-        <v>-83.8</v>
+        <v>-84.05</v>
       </c>
       <c r="L28" t="n">
-        <v>159.01</v>
+        <v>159.49</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>29</v>
       </c>
       <c r="J29" t="n">
-        <v>23.35</v>
+        <v>23.98</v>
       </c>
       <c r="K29" t="n">
-        <v>19.32</v>
+        <v>19.84</v>
       </c>
       <c r="L29" t="n">
-        <v>30.31</v>
+        <v>31.13</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>47.6</v>
+        <v>46.22</v>
       </c>
       <c r="K30" t="n">
-        <v>-24.78</v>
+        <v>-24.06</v>
       </c>
       <c r="L30" t="n">
-        <v>53.66</v>
+        <v>52.11</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>-46.36</v>
+        <v>-44.78</v>
       </c>
       <c r="K31" t="n">
-        <v>31.58</v>
+        <v>30.5</v>
       </c>
       <c r="L31" t="n">
-        <v>56.1</v>
+        <v>54.18</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>7.15</v>
+        <v>7.39</v>
       </c>
       <c r="K32" t="n">
-        <v>-44.37</v>
+        <v>-45.86</v>
       </c>
       <c r="L32" t="n">
-        <v>44.94</v>
+        <v>46.45</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>-75.47</v>
+        <v>-72.42</v>
       </c>
       <c r="K33" t="n">
-        <v>-26.74</v>
+        <v>-25.67</v>
       </c>
       <c r="L33" t="n">
-        <v>80.06999999999999</v>
+        <v>76.83</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>28</v>
       </c>
       <c r="J34" t="n">
-        <v>65.59999999999999</v>
+        <v>63.51</v>
       </c>
       <c r="K34" t="n">
-        <v>24.37</v>
+        <v>23.59</v>
       </c>
       <c r="L34" t="n">
-        <v>69.98</v>
+        <v>67.75</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>28.07</v>
+        <v>28.32</v>
       </c>
       <c r="K35" t="n">
-        <v>-75.7</v>
+        <v>-76.38</v>
       </c>
       <c r="L35" t="n">
-        <v>80.73</v>
+        <v>81.45999999999999</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>27</v>
       </c>
       <c r="J36" t="n">
-        <v>40.14</v>
+        <v>41.14</v>
       </c>
       <c r="K36" t="n">
-        <v>-49.82</v>
+        <v>-51.07</v>
       </c>
       <c r="L36" t="n">
-        <v>63.98</v>
+        <v>65.58</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>-30.35</v>
+        <v>-29.91</v>
       </c>
       <c r="K37" t="n">
-        <v>87.18000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>92.31</v>
+        <v>90.95999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-130.87</v>
+        <v>-126.81</v>
       </c>
       <c r="K38" t="n">
-        <v>59.95</v>
+        <v>58.09</v>
       </c>
       <c r="L38" t="n">
-        <v>143.95</v>
+        <v>139.49</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>50.71</v>
+        <v>51.68</v>
       </c>
       <c r="K39" t="n">
-        <v>87.45</v>
+        <v>89.11</v>
       </c>
       <c r="L39" t="n">
-        <v>101.09</v>
+        <v>103.01</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>29</v>
       </c>
       <c r="J40" t="n">
-        <v>54.4</v>
+        <v>55.62</v>
       </c>
       <c r="K40" t="n">
-        <v>65.94</v>
+        <v>67.42</v>
       </c>
       <c r="L40" t="n">
-        <v>85.48</v>
+        <v>87.40000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>96.14</v>
+        <v>97.11</v>
       </c>
       <c r="K41" t="n">
-        <v>-104.65</v>
+        <v>-105.7</v>
       </c>
       <c r="L41" t="n">
-        <v>142.11</v>
+        <v>143.54</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>26</v>
       </c>
       <c r="J42" t="n">
-        <v>12.91</v>
+        <v>12.3</v>
       </c>
       <c r="K42" t="n">
-        <v>-255.1</v>
+        <v>-243.03</v>
       </c>
       <c r="L42" t="n">
-        <v>255.43</v>
+        <v>243.34</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>-23.29</v>
+        <v>-25.03</v>
       </c>
       <c r="K43" t="n">
-        <v>-100.52</v>
+        <v>-108.07</v>
       </c>
       <c r="L43" t="n">
-        <v>103.19</v>
+        <v>110.94</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>-8.02</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="K44" t="n">
-        <v>36.59</v>
+        <v>36.98</v>
       </c>
       <c r="L44" t="n">
-        <v>37.46</v>
+        <v>37.86</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>10.03</v>
+        <v>10.8</v>
       </c>
       <c r="K45" t="n">
-        <v>24.64</v>
+        <v>26.52</v>
       </c>
       <c r="L45" t="n">
-        <v>26.61</v>
+        <v>28.63</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>28</v>
       </c>
       <c r="J46" t="n">
-        <v>13.94</v>
+        <v>13.59</v>
       </c>
       <c r="K46" t="n">
-        <v>-48.38</v>
+        <v>-47.17</v>
       </c>
       <c r="L46" t="n">
-        <v>50.35</v>
+        <v>49.09</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>24</v>
       </c>
       <c r="J47" t="n">
-        <v>36.7</v>
+        <v>35.67</v>
       </c>
       <c r="K47" t="n">
-        <v>-69.95</v>
+        <v>-67.98</v>
       </c>
       <c r="L47" t="n">
-        <v>79</v>
+        <v>76.77</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>29</v>
       </c>
       <c r="J48" t="n">
-        <v>-35.53</v>
+        <v>-37.17</v>
       </c>
       <c r="K48" t="n">
-        <v>8.460000000000001</v>
+        <v>8.85</v>
       </c>
       <c r="L48" t="n">
-        <v>36.53</v>
+        <v>38.21</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>42.57</v>
+        <v>43.74</v>
       </c>
       <c r="K49" t="n">
-        <v>-20.94</v>
+        <v>-21.51</v>
       </c>
       <c r="L49" t="n">
-        <v>47.44</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>44.04</v>
+        <v>44.84</v>
       </c>
       <c r="K50" t="n">
-        <v>-62.34</v>
+        <v>-63.48</v>
       </c>
       <c r="L50" t="n">
-        <v>76.33</v>
+        <v>77.72</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>57.34</v>
+        <v>57.09</v>
       </c>
       <c r="K51" t="n">
-        <v>-66.06</v>
+        <v>-65.77</v>
       </c>
       <c r="L51" t="n">
-        <v>87.48</v>
+        <v>87.09</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>-39.68</v>
+        <v>-41.17</v>
       </c>
       <c r="K52" t="n">
-        <v>49.22</v>
+        <v>51.07</v>
       </c>
       <c r="L52" t="n">
-        <v>63.22</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>-100.71</v>
+        <v>-101.82</v>
       </c>
       <c r="K53" t="n">
-        <v>-12.33</v>
+        <v>-12.46</v>
       </c>
       <c r="L53" t="n">
-        <v>101.46</v>
+        <v>102.58</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-12.74</v>
+        <v>-12.63</v>
       </c>
       <c r="K54" t="n">
-        <v>125.88</v>
+        <v>124.81</v>
       </c>
       <c r="L54" t="n">
-        <v>126.53</v>
+        <v>125.44</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>-69</v>
+        <v>-72.11</v>
       </c>
       <c r="K55" t="n">
-        <v>-43.66</v>
+        <v>-45.63</v>
       </c>
       <c r="L55" t="n">
-        <v>81.65000000000001</v>
+        <v>85.34</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>184.6</v>
+        <v>181.57</v>
       </c>
       <c r="K56" t="n">
-        <v>-31.66</v>
+        <v>-31.14</v>
       </c>
       <c r="L56" t="n">
-        <v>187.29</v>
+        <v>184.23</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>-163.8</v>
+        <v>-160.92</v>
       </c>
       <c r="K57" t="n">
-        <v>-94.34999999999999</v>
+        <v>-92.68000000000001</v>
       </c>
       <c r="L57" t="n">
-        <v>189.03</v>
+        <v>185.7</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>147.97</v>
+        <v>148.82</v>
       </c>
       <c r="K58" t="n">
-        <v>47.42</v>
+        <v>47.69</v>
       </c>
       <c r="L58" t="n">
-        <v>155.38</v>
+        <v>156.27</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>-25.13</v>
+        <v>-25.98</v>
       </c>
       <c r="K59" t="n">
-        <v>-21.44</v>
+        <v>-22.16</v>
       </c>
       <c r="L59" t="n">
-        <v>33.03</v>
+        <v>34.15</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>28</v>
       </c>
       <c r="J60" t="n">
-        <v>-31.76</v>
+        <v>-31.35</v>
       </c>
       <c r="K60" t="n">
-        <v>-29.24</v>
+        <v>-28.86</v>
       </c>
       <c r="L60" t="n">
-        <v>43.17</v>
+        <v>42.61</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>28</v>
       </c>
       <c r="J61" t="n">
-        <v>37.24</v>
+        <v>36.43</v>
       </c>
       <c r="K61" t="n">
-        <v>32.89</v>
+        <v>32.18</v>
       </c>
       <c r="L61" t="n">
-        <v>49.69</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>35.21</v>
+        <v>35.72</v>
       </c>
       <c r="K62" t="n">
-        <v>36.46</v>
+        <v>36.98</v>
       </c>
       <c r="L62" t="n">
-        <v>50.69</v>
+        <v>51.42</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>29</v>
       </c>
       <c r="J63" t="n">
-        <v>11.55</v>
+        <v>11.32</v>
       </c>
       <c r="K63" t="n">
-        <v>-5.08</v>
+        <v>-4.98</v>
       </c>
       <c r="L63" t="n">
-        <v>12.62</v>
+        <v>12.37</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>39.32</v>
+        <v>38.59</v>
       </c>
       <c r="K64" t="n">
-        <v>59.19</v>
+        <v>58.09</v>
       </c>
       <c r="L64" t="n">
-        <v>71.06</v>
+        <v>69.73999999999999</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>66.73</v>
+        <v>67.5</v>
       </c>
       <c r="K65" t="n">
-        <v>-47.33</v>
+        <v>-47.87</v>
       </c>
       <c r="L65" t="n">
-        <v>81.81</v>
+        <v>82.75</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>27</v>
       </c>
       <c r="J66" t="n">
-        <v>37.71</v>
+        <v>40.85</v>
       </c>
       <c r="K66" t="n">
-        <v>-29.75</v>
+        <v>-32.23</v>
       </c>
       <c r="L66" t="n">
-        <v>48.03</v>
+        <v>52.04</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>-88.69</v>
+        <v>-87.98999999999999</v>
       </c>
       <c r="K67" t="n">
-        <v>30.76</v>
+        <v>30.52</v>
       </c>
       <c r="L67" t="n">
-        <v>93.87</v>
+        <v>93.14</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>27</v>
       </c>
       <c r="J68" t="n">
-        <v>-71.79000000000001</v>
+        <v>-74.12</v>
       </c>
       <c r="K68" t="n">
-        <v>-43.33</v>
+        <v>-44.74</v>
       </c>
       <c r="L68" t="n">
-        <v>83.84999999999999</v>
+        <v>86.58</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>28</v>
       </c>
       <c r="J69" t="n">
-        <v>-102.09</v>
+        <v>-102.52</v>
       </c>
       <c r="K69" t="n">
-        <v>3.43</v>
+        <v>3.45</v>
       </c>
       <c r="L69" t="n">
-        <v>102.14</v>
+        <v>102.58</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>-21</v>
+        <v>-20.6</v>
       </c>
       <c r="K70" t="n">
-        <v>132.07</v>
+        <v>129.56</v>
       </c>
       <c r="L70" t="n">
-        <v>133.73</v>
+        <v>131.19</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>15.29</v>
+        <v>15.98</v>
       </c>
       <c r="K71" t="n">
-        <v>-124.06</v>
+        <v>-129.7</v>
       </c>
       <c r="L71" t="n">
-        <v>125</v>
+        <v>130.68</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>28</v>
       </c>
       <c r="J72" t="n">
-        <v>138.18</v>
+        <v>136.77</v>
       </c>
       <c r="K72" t="n">
-        <v>110.43</v>
+        <v>109.3</v>
       </c>
       <c r="L72" t="n">
-        <v>176.89</v>
+        <v>175.08</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>29</v>
       </c>
       <c r="J73" t="n">
-        <v>-156.7</v>
+        <v>-155.91</v>
       </c>
       <c r="K73" t="n">
-        <v>43.04</v>
+        <v>42.83</v>
       </c>
       <c r="L73" t="n">
-        <v>162.5</v>
+        <v>161.69</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>29</v>
       </c>
       <c r="J74" t="n">
-        <v>7.04</v>
+        <v>7.4</v>
       </c>
       <c r="K74" t="n">
-        <v>-25.95</v>
+        <v>-27.28</v>
       </c>
       <c r="L74" t="n">
-        <v>26.89</v>
+        <v>28.27</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="K75" t="n">
-        <v>-42.44</v>
+        <v>-42.03</v>
       </c>
       <c r="L75" t="n">
-        <v>42.46</v>
+        <v>42.05</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>28.96</v>
+        <v>29.83</v>
       </c>
       <c r="K76" t="n">
-        <v>-19.92</v>
+        <v>-20.52</v>
       </c>
       <c r="L76" t="n">
-        <v>35.15</v>
+        <v>36.21</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>53.21</v>
+        <v>53.84</v>
       </c>
       <c r="K77" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="L77" t="n">
-        <v>53.27</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>29</v>
       </c>
       <c r="J78" t="n">
-        <v>-6.94</v>
+        <v>-6.77</v>
       </c>
       <c r="K78" t="n">
-        <v>-24.91</v>
+        <v>-24.31</v>
       </c>
       <c r="L78" t="n">
-        <v>25.86</v>
+        <v>25.24</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>28</v>
       </c>
       <c r="J79" t="n">
-        <v>-59.14</v>
+        <v>-58.75</v>
       </c>
       <c r="K79" t="n">
-        <v>-27.57</v>
+        <v>-27.39</v>
       </c>
       <c r="L79" t="n">
-        <v>65.25</v>
+        <v>64.81999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>66.44</v>
+        <v>65.05</v>
       </c>
       <c r="K80" t="n">
-        <v>-72.37</v>
+        <v>-70.86</v>
       </c>
       <c r="L80" t="n">
-        <v>98.23999999999999</v>
+        <v>96.19</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>-11.12</v>
+        <v>-11.25</v>
       </c>
       <c r="K81" t="n">
-        <v>-77.29000000000001</v>
+        <v>-78.23999999999999</v>
       </c>
       <c r="L81" t="n">
-        <v>78.09</v>
+        <v>79.04000000000001</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>23</v>
       </c>
       <c r="J82" t="n">
-        <v>89.93000000000001</v>
+        <v>85.44</v>
       </c>
       <c r="K82" t="n">
-        <v>113.13</v>
+        <v>107.47</v>
       </c>
       <c r="L82" t="n">
-        <v>144.52</v>
+        <v>137.29</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>-125.98</v>
+        <v>-120.68</v>
       </c>
       <c r="K83" t="n">
-        <v>-89.40000000000001</v>
+        <v>-85.64</v>
       </c>
       <c r="L83" t="n">
-        <v>154.48</v>
+        <v>147.98</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>-90.44</v>
+        <v>-87.2</v>
       </c>
       <c r="K84" t="n">
-        <v>-26.67</v>
+        <v>-25.71</v>
       </c>
       <c r="L84" t="n">
-        <v>94.29000000000001</v>
+        <v>90.91</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>-67.67</v>
+        <v>-68.64</v>
       </c>
       <c r="K85" t="n">
-        <v>-65.51000000000001</v>
+        <v>-66.45</v>
       </c>
       <c r="L85" t="n">
-        <v>94.19</v>
+        <v>95.54000000000001</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>-94.08</v>
+        <v>-95.11</v>
       </c>
       <c r="K86" t="n">
-        <v>110.67</v>
+        <v>111.88</v>
       </c>
       <c r="L86" t="n">
-        <v>145.25</v>
+        <v>146.84</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>-91.59999999999999</v>
+        <v>-89.52</v>
       </c>
       <c r="K87" t="n">
-        <v>-189.5</v>
+        <v>-185.19</v>
       </c>
       <c r="L87" t="n">
-        <v>210.48</v>
+        <v>205.7</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>205.95</v>
+        <v>194.39</v>
       </c>
       <c r="K88" t="n">
-        <v>-217.99</v>
+        <v>-205.75</v>
       </c>
       <c r="L88" t="n">
-        <v>299.89</v>
+        <v>283.05</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-08-25.xlsx
+++ b/output/2024-08-25.xlsx
@@ -640,13 +640,13 @@
         <v>29</v>
       </c>
       <c r="J14" t="n">
-        <v>23.16</v>
+        <v>23.47</v>
       </c>
       <c r="K14" t="n">
-        <v>-25.42</v>
+        <v>-25.76</v>
       </c>
       <c r="L14" t="n">
-        <v>34.39</v>
+        <v>34.85</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>27</v>
       </c>
       <c r="J15" t="n">
-        <v>-14.56</v>
+        <v>-13.97</v>
       </c>
       <c r="K15" t="n">
-        <v>48.45</v>
+        <v>46.51</v>
       </c>
       <c r="L15" t="n">
-        <v>50.59</v>
+        <v>48.57</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>27</v>
       </c>
       <c r="J16" t="n">
-        <v>33.29</v>
+        <v>33.85</v>
       </c>
       <c r="K16" t="n">
-        <v>8.970000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>34.48</v>
+        <v>35.05</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>-31.64</v>
+        <v>-33.04</v>
       </c>
       <c r="K17" t="n">
-        <v>-34.94</v>
+        <v>-36.49</v>
       </c>
       <c r="L17" t="n">
-        <v>47.14</v>
+        <v>49.23</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>24</v>
       </c>
       <c r="J18" t="n">
-        <v>-65.22</v>
+        <v>-62.92</v>
       </c>
       <c r="K18" t="n">
-        <v>-35.48</v>
+        <v>-34.23</v>
       </c>
       <c r="L18" t="n">
-        <v>74.23999999999999</v>
+        <v>71.63</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>40.79</v>
+        <v>41.93</v>
       </c>
       <c r="K19" t="n">
-        <v>25.48</v>
+        <v>26.19</v>
       </c>
       <c r="L19" t="n">
-        <v>48.09</v>
+        <v>49.43</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>58.13</v>
+        <v>60.99</v>
       </c>
       <c r="K20" t="n">
-        <v>29.24</v>
+        <v>30.68</v>
       </c>
       <c r="L20" t="n">
-        <v>65.06</v>
+        <v>68.27</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>23</v>
       </c>
       <c r="J21" t="n">
-        <v>60.53</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>-24.19</v>
+        <v>-25.6</v>
       </c>
       <c r="L21" t="n">
-        <v>65.19</v>
+        <v>68.97</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>37.33</v>
+        <v>37.98</v>
       </c>
       <c r="K22" t="n">
-        <v>61.44</v>
+        <v>62.51</v>
       </c>
       <c r="L22" t="n">
-        <v>71.89</v>
+        <v>73.14</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>28</v>
       </c>
       <c r="J23" t="n">
-        <v>-16.86</v>
+        <v>-17.75</v>
       </c>
       <c r="K23" t="n">
-        <v>-76.56</v>
+        <v>-80.59</v>
       </c>
       <c r="L23" t="n">
-        <v>78.39</v>
+        <v>82.53</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>28</v>
       </c>
       <c r="J24" t="n">
-        <v>-74.36</v>
+        <v>-74.53</v>
       </c>
       <c r="K24" t="n">
-        <v>68.19</v>
+        <v>68.34</v>
       </c>
       <c r="L24" t="n">
-        <v>100.89</v>
+        <v>101.12</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>-135.82</v>
+        <v>-130.04</v>
       </c>
       <c r="K25" t="n">
-        <v>-96.83</v>
+        <v>-92.70999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>166.8</v>
+        <v>159.7</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>29</v>
       </c>
       <c r="J26" t="n">
-        <v>120.08</v>
+        <v>123.82</v>
       </c>
       <c r="K26" t="n">
-        <v>30.56</v>
+        <v>31.51</v>
       </c>
       <c r="L26" t="n">
-        <v>123.91</v>
+        <v>127.76</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>-95.56</v>
+        <v>-98.2</v>
       </c>
       <c r="K27" t="n">
-        <v>110.45</v>
+        <v>113.49</v>
       </c>
       <c r="L27" t="n">
-        <v>146.05</v>
+        <v>150.08</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>-135.54</v>
+        <v>-136.01</v>
       </c>
       <c r="K28" t="n">
-        <v>-84.05</v>
+        <v>-84.34</v>
       </c>
       <c r="L28" t="n">
-        <v>159.49</v>
+        <v>160.04</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>29</v>
       </c>
       <c r="J29" t="n">
-        <v>23.98</v>
+        <v>24.7</v>
       </c>
       <c r="K29" t="n">
-        <v>19.84</v>
+        <v>20.43</v>
       </c>
       <c r="L29" t="n">
-        <v>31.13</v>
+        <v>32.06</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>46.22</v>
+        <v>44.64</v>
       </c>
       <c r="K30" t="n">
-        <v>-24.06</v>
+        <v>-23.24</v>
       </c>
       <c r="L30" t="n">
-        <v>52.11</v>
+        <v>50.33</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>-44.78</v>
+        <v>-42.96</v>
       </c>
       <c r="K31" t="n">
-        <v>30.5</v>
+        <v>29.27</v>
       </c>
       <c r="L31" t="n">
-        <v>54.18</v>
+        <v>51.99</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>7.39</v>
+        <v>7.66</v>
       </c>
       <c r="K32" t="n">
-        <v>-45.86</v>
+        <v>-47.56</v>
       </c>
       <c r="L32" t="n">
-        <v>46.45</v>
+        <v>48.18</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>-72.42</v>
+        <v>-68.94</v>
       </c>
       <c r="K33" t="n">
-        <v>-25.67</v>
+        <v>-24.43</v>
       </c>
       <c r="L33" t="n">
-        <v>76.83</v>
+        <v>73.14</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>28</v>
       </c>
       <c r="J34" t="n">
-        <v>63.51</v>
+        <v>61.12</v>
       </c>
       <c r="K34" t="n">
-        <v>23.59</v>
+        <v>22.7</v>
       </c>
       <c r="L34" t="n">
-        <v>67.75</v>
+        <v>65.2</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>28.32</v>
+        <v>28.61</v>
       </c>
       <c r="K35" t="n">
-        <v>-76.38</v>
+        <v>-77.16</v>
       </c>
       <c r="L35" t="n">
-        <v>81.45999999999999</v>
+        <v>82.29000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>27</v>
       </c>
       <c r="J36" t="n">
-        <v>41.14</v>
+        <v>42.29</v>
       </c>
       <c r="K36" t="n">
-        <v>-51.07</v>
+        <v>-52.5</v>
       </c>
       <c r="L36" t="n">
-        <v>65.58</v>
+        <v>67.41</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>-29.91</v>
+        <v>-29.4</v>
       </c>
       <c r="K37" t="n">
-        <v>85.90000000000001</v>
+        <v>84.44</v>
       </c>
       <c r="L37" t="n">
-        <v>90.95999999999999</v>
+        <v>89.41</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-126.81</v>
+        <v>-122.18</v>
       </c>
       <c r="K38" t="n">
-        <v>58.09</v>
+        <v>55.97</v>
       </c>
       <c r="L38" t="n">
-        <v>139.49</v>
+        <v>134.39</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>51.68</v>
+        <v>52.78</v>
       </c>
       <c r="K39" t="n">
-        <v>89.11</v>
+        <v>91.01000000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>103.01</v>
+        <v>105.21</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>29</v>
       </c>
       <c r="J40" t="n">
-        <v>55.62</v>
+        <v>57.01</v>
       </c>
       <c r="K40" t="n">
-        <v>67.42</v>
+        <v>69.11</v>
       </c>
       <c r="L40" t="n">
-        <v>87.40000000000001</v>
+        <v>89.59</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>97.11</v>
+        <v>98.2</v>
       </c>
       <c r="K41" t="n">
-        <v>-105.7</v>
+        <v>-106.9</v>
       </c>
       <c r="L41" t="n">
-        <v>143.54</v>
+        <v>145.16</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>26</v>
       </c>
       <c r="J42" t="n">
-        <v>12.3</v>
+        <v>11.6</v>
       </c>
       <c r="K42" t="n">
-        <v>-243.03</v>
+        <v>-229.23</v>
       </c>
       <c r="L42" t="n">
-        <v>243.34</v>
+        <v>229.52</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>-25.03</v>
+        <v>-27.03</v>
       </c>
       <c r="K43" t="n">
-        <v>-108.07</v>
+        <v>-116.7</v>
       </c>
       <c r="L43" t="n">
-        <v>110.94</v>
+        <v>119.79</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>-8.109999999999999</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>36.98</v>
+        <v>37.44</v>
       </c>
       <c r="L44" t="n">
-        <v>37.86</v>
+        <v>38.33</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>10.8</v>
+        <v>11.67</v>
       </c>
       <c r="K45" t="n">
-        <v>26.52</v>
+        <v>28.66</v>
       </c>
       <c r="L45" t="n">
-        <v>28.63</v>
+        <v>30.94</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>28</v>
       </c>
       <c r="J46" t="n">
-        <v>13.59</v>
+        <v>13.19</v>
       </c>
       <c r="K46" t="n">
-        <v>-47.17</v>
+        <v>-45.79</v>
       </c>
       <c r="L46" t="n">
-        <v>49.09</v>
+        <v>47.65</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>24</v>
       </c>
       <c r="J47" t="n">
-        <v>35.67</v>
+        <v>34.48</v>
       </c>
       <c r="K47" t="n">
-        <v>-67.98</v>
+        <v>-65.72</v>
       </c>
       <c r="L47" t="n">
-        <v>76.77</v>
+        <v>74.22</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>29</v>
       </c>
       <c r="J48" t="n">
-        <v>-37.17</v>
+        <v>-39.05</v>
       </c>
       <c r="K48" t="n">
-        <v>8.85</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="L48" t="n">
-        <v>38.21</v>
+        <v>40.14</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>43.74</v>
+        <v>45.07</v>
       </c>
       <c r="K49" t="n">
-        <v>-21.51</v>
+        <v>-22.16</v>
       </c>
       <c r="L49" t="n">
-        <v>48.74</v>
+        <v>50.23</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>44.84</v>
+        <v>45.76</v>
       </c>
       <c r="K50" t="n">
-        <v>-63.48</v>
+        <v>-64.77</v>
       </c>
       <c r="L50" t="n">
-        <v>77.72</v>
+        <v>79.3</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>57.09</v>
+        <v>56.79</v>
       </c>
       <c r="K51" t="n">
-        <v>-65.77</v>
+        <v>-65.43000000000001</v>
       </c>
       <c r="L51" t="n">
-        <v>87.09</v>
+        <v>86.64</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>-41.17</v>
+        <v>-42.88</v>
       </c>
       <c r="K52" t="n">
-        <v>51.07</v>
+        <v>53.18</v>
       </c>
       <c r="L52" t="n">
-        <v>65.59999999999999</v>
+        <v>68.31</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>-101.82</v>
+        <v>-103.08</v>
       </c>
       <c r="K53" t="n">
-        <v>-12.46</v>
+        <v>-12.62</v>
       </c>
       <c r="L53" t="n">
-        <v>102.58</v>
+        <v>103.85</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-12.63</v>
+        <v>-12.5</v>
       </c>
       <c r="K54" t="n">
-        <v>124.81</v>
+        <v>123.57</v>
       </c>
       <c r="L54" t="n">
-        <v>125.44</v>
+        <v>124.2</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>-72.11</v>
+        <v>-75.67</v>
       </c>
       <c r="K55" t="n">
-        <v>-45.63</v>
+        <v>-47.88</v>
       </c>
       <c r="L55" t="n">
-        <v>85.34</v>
+        <v>89.55</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>181.57</v>
+        <v>178.12</v>
       </c>
       <c r="K56" t="n">
-        <v>-31.14</v>
+        <v>-30.55</v>
       </c>
       <c r="L56" t="n">
-        <v>184.23</v>
+        <v>180.72</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>-160.92</v>
+        <v>-157.62</v>
       </c>
       <c r="K57" t="n">
-        <v>-92.68000000000001</v>
+        <v>-90.79000000000001</v>
       </c>
       <c r="L57" t="n">
-        <v>185.7</v>
+        <v>181.9</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>148.82</v>
+        <v>149.79</v>
       </c>
       <c r="K58" t="n">
-        <v>47.69</v>
+        <v>48</v>
       </c>
       <c r="L58" t="n">
-        <v>156.27</v>
+        <v>157.29</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>-25.98</v>
+        <v>-26.95</v>
       </c>
       <c r="K59" t="n">
-        <v>-22.16</v>
+        <v>-22.99</v>
       </c>
       <c r="L59" t="n">
-        <v>34.15</v>
+        <v>35.42</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>28</v>
       </c>
       <c r="J60" t="n">
-        <v>-31.35</v>
+        <v>-30.88</v>
       </c>
       <c r="K60" t="n">
-        <v>-28.86</v>
+        <v>-28.43</v>
       </c>
       <c r="L60" t="n">
-        <v>42.61</v>
+        <v>41.98</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>28</v>
       </c>
       <c r="J61" t="n">
-        <v>36.43</v>
+        <v>35.5</v>
       </c>
       <c r="K61" t="n">
-        <v>32.18</v>
+        <v>31.36</v>
       </c>
       <c r="L61" t="n">
-        <v>48.6</v>
+        <v>47.36</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>35.72</v>
+        <v>36.3</v>
       </c>
       <c r="K62" t="n">
-        <v>36.98</v>
+        <v>37.58</v>
       </c>
       <c r="L62" t="n">
-        <v>51.42</v>
+        <v>52.25</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>29</v>
       </c>
       <c r="J63" t="n">
-        <v>11.32</v>
+        <v>12.24</v>
       </c>
       <c r="K63" t="n">
-        <v>-4.98</v>
+        <v>-5.38</v>
       </c>
       <c r="L63" t="n">
-        <v>12.37</v>
+        <v>13.37</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>38.59</v>
+        <v>37.75</v>
       </c>
       <c r="K64" t="n">
-        <v>58.09</v>
+        <v>56.83</v>
       </c>
       <c r="L64" t="n">
-        <v>69.73999999999999</v>
+        <v>68.23</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>67.5</v>
+        <v>68.37</v>
       </c>
       <c r="K65" t="n">
-        <v>-47.87</v>
+        <v>-48.49</v>
       </c>
       <c r="L65" t="n">
-        <v>82.75</v>
+        <v>83.81999999999999</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>27</v>
       </c>
       <c r="J66" t="n">
-        <v>40.85</v>
+        <v>44.45</v>
       </c>
       <c r="K66" t="n">
-        <v>-32.23</v>
+        <v>-35.07</v>
       </c>
       <c r="L66" t="n">
-        <v>52.04</v>
+        <v>56.61</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>-87.98999999999999</v>
+        <v>-87.2</v>
       </c>
       <c r="K67" t="n">
-        <v>30.52</v>
+        <v>30.24</v>
       </c>
       <c r="L67" t="n">
-        <v>93.14</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>27</v>
       </c>
       <c r="J68" t="n">
-        <v>-74.12</v>
+        <v>-76.79000000000001</v>
       </c>
       <c r="K68" t="n">
-        <v>-44.74</v>
+        <v>-46.35</v>
       </c>
       <c r="L68" t="n">
-        <v>86.58</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>28</v>
       </c>
       <c r="J69" t="n">
-        <v>-102.52</v>
+        <v>-103.02</v>
       </c>
       <c r="K69" t="n">
-        <v>3.45</v>
+        <v>3.47</v>
       </c>
       <c r="L69" t="n">
-        <v>102.58</v>
+        <v>103.08</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>-20.6</v>
+        <v>-20.15</v>
       </c>
       <c r="K70" t="n">
-        <v>129.56</v>
+        <v>126.7</v>
       </c>
       <c r="L70" t="n">
-        <v>131.19</v>
+        <v>128.29</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>15.98</v>
+        <v>16.77</v>
       </c>
       <c r="K71" t="n">
-        <v>-129.7</v>
+        <v>-136.14</v>
       </c>
       <c r="L71" t="n">
-        <v>130.68</v>
+        <v>137.17</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>28</v>
       </c>
       <c r="J72" t="n">
-        <v>136.77</v>
+        <v>135.16</v>
       </c>
       <c r="K72" t="n">
-        <v>109.3</v>
+        <v>108.01</v>
       </c>
       <c r="L72" t="n">
-        <v>175.08</v>
+        <v>173.01</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>29</v>
       </c>
       <c r="J73" t="n">
-        <v>-155.91</v>
+        <v>-155.02</v>
       </c>
       <c r="K73" t="n">
-        <v>42.83</v>
+        <v>42.58</v>
       </c>
       <c r="L73" t="n">
-        <v>161.69</v>
+        <v>160.76</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>29</v>
       </c>
       <c r="J74" t="n">
-        <v>7.4</v>
+        <v>7.81</v>
       </c>
       <c r="K74" t="n">
-        <v>-27.28</v>
+        <v>-28.8</v>
       </c>
       <c r="L74" t="n">
-        <v>28.27</v>
+        <v>29.84</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="K75" t="n">
-        <v>-42.03</v>
+        <v>-41.57</v>
       </c>
       <c r="L75" t="n">
-        <v>42.05</v>
+        <v>41.59</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>29.83</v>
+        <v>30.83</v>
       </c>
       <c r="K76" t="n">
-        <v>-20.52</v>
+        <v>-21.21</v>
       </c>
       <c r="L76" t="n">
-        <v>36.21</v>
+        <v>37.42</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>53.84</v>
+        <v>54.56</v>
       </c>
       <c r="K77" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="L77" t="n">
-        <v>53.9</v>
+        <v>54.62</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>29</v>
       </c>
       <c r="J78" t="n">
-        <v>-6.77</v>
+        <v>-7.43</v>
       </c>
       <c r="K78" t="n">
-        <v>-24.31</v>
+        <v>-26.67</v>
       </c>
       <c r="L78" t="n">
-        <v>25.24</v>
+        <v>27.68</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>28</v>
       </c>
       <c r="J79" t="n">
-        <v>-58.75</v>
+        <v>-58.31</v>
       </c>
       <c r="K79" t="n">
-        <v>-27.39</v>
+        <v>-27.18</v>
       </c>
       <c r="L79" t="n">
-        <v>64.81999999999999</v>
+        <v>64.34</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>65.05</v>
+        <v>63.47</v>
       </c>
       <c r="K80" t="n">
-        <v>-70.86</v>
+        <v>-69.13</v>
       </c>
       <c r="L80" t="n">
-        <v>96.19</v>
+        <v>93.84999999999999</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>-11.25</v>
+        <v>-11.41</v>
       </c>
       <c r="K81" t="n">
-        <v>-78.23999999999999</v>
+        <v>-79.31</v>
       </c>
       <c r="L81" t="n">
-        <v>79.04000000000001</v>
+        <v>80.13</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>23</v>
       </c>
       <c r="J82" t="n">
-        <v>85.44</v>
+        <v>80.29000000000001</v>
       </c>
       <c r="K82" t="n">
-        <v>107.47</v>
+        <v>101.01</v>
       </c>
       <c r="L82" t="n">
-        <v>137.29</v>
+        <v>129.03</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>-120.68</v>
+        <v>-114.62</v>
       </c>
       <c r="K83" t="n">
-        <v>-85.64</v>
+        <v>-81.34999999999999</v>
       </c>
       <c r="L83" t="n">
-        <v>147.98</v>
+        <v>140.56</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>-87.2</v>
+        <v>-90.38</v>
       </c>
       <c r="K84" t="n">
-        <v>-25.71</v>
+        <v>-26.65</v>
       </c>
       <c r="L84" t="n">
-        <v>90.91</v>
+        <v>94.23</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>-68.64</v>
+        <v>-69.75</v>
       </c>
       <c r="K85" t="n">
-        <v>-66.45</v>
+        <v>-67.52</v>
       </c>
       <c r="L85" t="n">
-        <v>95.54000000000001</v>
+        <v>97.08</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>-95.11</v>
+        <v>-96.28</v>
       </c>
       <c r="K86" t="n">
-        <v>111.88</v>
+        <v>113.26</v>
       </c>
       <c r="L86" t="n">
-        <v>146.84</v>
+        <v>148.66</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>-89.52</v>
+        <v>-87.14</v>
       </c>
       <c r="K87" t="n">
-        <v>-185.19</v>
+        <v>-180.27</v>
       </c>
       <c r="L87" t="n">
-        <v>205.7</v>
+        <v>200.23</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>194.39</v>
+        <v>181.18</v>
       </c>
       <c r="K88" t="n">
-        <v>-205.75</v>
+        <v>-191.77</v>
       </c>
       <c r="L88" t="n">
-        <v>283.05</v>
+        <v>263.82</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-08-25.xlsx
+++ b/output/2024-08-25.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.54</v>
+        <v>1.35</v>
       </c>
       <c r="F14" t="n">
-        <v>5.26</v>
+        <v>1.65</v>
       </c>
       <c r="G14" t="n">
-        <v>228.5</v>
+        <v>240.2</v>
       </c>
       <c r="H14" t="n">
-        <v>12.1</v>
+        <v>11.6</v>
       </c>
       <c r="I14" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J14" t="n">
-        <v>23.47</v>
+        <v>-13.67</v>
       </c>
       <c r="K14" t="n">
-        <v>-25.76</v>
+        <v>-23.13</v>
       </c>
       <c r="L14" t="n">
-        <v>34.85</v>
+        <v>26.87</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:07:25</t>
+          <t>06:07:16</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1.35</v>
+        <v>1.84</v>
       </c>
       <c r="F15" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="G15" t="n">
-        <v>240.2</v>
+        <v>231.6</v>
       </c>
       <c r="H15" t="n">
-        <v>11.6</v>
+        <v>13.5</v>
       </c>
       <c r="I15" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J15" t="n">
-        <v>-13.97</v>
+        <v>34.67</v>
       </c>
       <c r="K15" t="n">
-        <v>46.51</v>
+        <v>9.16</v>
       </c>
       <c r="L15" t="n">
-        <v>48.57</v>
+        <v>35.86</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:08:54</t>
+          <t>06:08:35</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="F16" t="n">
-        <v>5.51</v>
+        <v>5.41</v>
       </c>
       <c r="G16" t="n">
-        <v>229.5</v>
+        <v>241.1</v>
       </c>
       <c r="H16" t="n">
-        <v>9.4</v>
+        <v>12.6</v>
       </c>
       <c r="I16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>33.85</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>9.119999999999999</v>
+        <v>-33.1</v>
       </c>
       <c r="L16" t="n">
-        <v>35.05</v>
+        <v>33.11</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:14:10</t>
+          <t>06:14:26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1.65</v>
+        <v>1.42</v>
       </c>
       <c r="F17" t="n">
-        <v>5.45</v>
+        <v>5.88</v>
       </c>
       <c r="G17" t="n">
-        <v>241.1</v>
+        <v>230.9</v>
       </c>
       <c r="H17" t="n">
-        <v>12.6</v>
+        <v>14</v>
       </c>
       <c r="I17" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J17" t="n">
-        <v>-33.04</v>
+        <v>-62.4</v>
       </c>
       <c r="K17" t="n">
-        <v>-36.49</v>
+        <v>-34.06</v>
       </c>
       <c r="L17" t="n">
-        <v>49.23</v>
+        <v>71.09</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:15:15</t>
+          <t>06:16:11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.55</v>
+        <v>1.27</v>
       </c>
       <c r="F18" t="n">
-        <v>5.47</v>
+        <v>2.1</v>
       </c>
       <c r="G18" t="n">
-        <v>230.4</v>
+        <v>219.8</v>
       </c>
       <c r="H18" t="n">
-        <v>10.8</v>
+        <v>11.5</v>
       </c>
       <c r="I18" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>-62.92</v>
+        <v>-40.54</v>
       </c>
       <c r="K18" t="n">
-        <v>-34.23</v>
+        <v>25.99</v>
       </c>
       <c r="L18" t="n">
-        <v>71.63</v>
+        <v>48.16</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:17:40</t>
+          <t>06:18:44</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="F19" t="n">
-        <v>5.24</v>
+        <v>4.27</v>
       </c>
       <c r="G19" t="n">
-        <v>219.8</v>
+        <v>223.3</v>
       </c>
       <c r="H19" t="n">
-        <v>11.5</v>
+        <v>11.7</v>
       </c>
       <c r="I19" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J19" t="n">
-        <v>41.93</v>
+        <v>40.14</v>
       </c>
       <c r="K19" t="n">
-        <v>26.19</v>
+        <v>20.03</v>
       </c>
       <c r="L19" t="n">
-        <v>49.43</v>
+        <v>44.86</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:22:59</t>
+          <t>06:23:02</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.55</v>
+        <v>1.74</v>
       </c>
       <c r="F20" t="n">
-        <v>5.1</v>
+        <v>4.11</v>
       </c>
       <c r="G20" t="n">
-        <v>225.7</v>
+        <v>230.7</v>
       </c>
       <c r="H20" t="n">
-        <v>5.3</v>
+        <v>17.7</v>
       </c>
       <c r="I20" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J20" t="n">
-        <v>60.99</v>
+        <v>92.48</v>
       </c>
       <c r="K20" t="n">
-        <v>30.68</v>
+        <v>26.74</v>
       </c>
       <c r="L20" t="n">
-        <v>68.27</v>
+        <v>96.26000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:24:34</t>
+          <t>06:24:23</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1.74</v>
+        <v>1.49</v>
       </c>
       <c r="F21" t="n">
-        <v>5.3</v>
+        <v>6.21</v>
       </c>
       <c r="G21" t="n">
-        <v>230.7</v>
+        <v>234.8</v>
       </c>
       <c r="H21" t="n">
-        <v>17.7</v>
+        <v>13.6</v>
       </c>
       <c r="I21" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J21" t="n">
-        <v>64.04000000000001</v>
+        <v>41.74</v>
       </c>
       <c r="K21" t="n">
-        <v>-25.6</v>
+        <v>73.05</v>
       </c>
       <c r="L21" t="n">
-        <v>68.97</v>
+        <v>84.14</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:25:57</t>
+          <t>06:26:32</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>1.41</v>
+        <v>1.61</v>
       </c>
       <c r="F22" t="n">
-        <v>5.67</v>
+        <v>3.49</v>
       </c>
       <c r="G22" t="n">
-        <v>229.6</v>
+        <v>219.5</v>
       </c>
       <c r="H22" t="n">
-        <v>14.3</v>
+        <v>20.7</v>
       </c>
       <c r="I22" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J22" t="n">
-        <v>37.98</v>
+        <v>-75.84999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>62.51</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>73.14</v>
+        <v>76.44</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:30:45</t>
+          <t>06:31:24</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="F23" t="n">
-        <v>5.52</v>
+        <v>5.07</v>
       </c>
       <c r="G23" t="n">
-        <v>219.5</v>
+        <v>240.5</v>
       </c>
       <c r="H23" t="n">
-        <v>20.7</v>
+        <v>13.4</v>
       </c>
       <c r="I23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J23" t="n">
-        <v>-17.75</v>
+        <v>-85.23999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>-80.59</v>
+        <v>68.11</v>
       </c>
       <c r="L23" t="n">
-        <v>82.53</v>
+        <v>109.11</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:32:47</t>
+          <t>06:33:08</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.56</v>
+        <v>2.3</v>
       </c>
       <c r="F24" t="n">
-        <v>5.96</v>
+        <v>5.51</v>
       </c>
       <c r="G24" t="n">
-        <v>229.2</v>
+        <v>224.3</v>
       </c>
       <c r="H24" t="n">
-        <v>9.699999999999999</v>
+        <v>11.4</v>
       </c>
       <c r="I24" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J24" t="n">
-        <v>-74.53</v>
+        <v>72.23</v>
       </c>
       <c r="K24" t="n">
-        <v>68.34</v>
+        <v>-115.41</v>
       </c>
       <c r="L24" t="n">
-        <v>101.12</v>
+        <v>136.15</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:34:31</t>
+          <t>06:34:50</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.3</v>
+        <v>1.34</v>
       </c>
       <c r="F25" t="n">
-        <v>5.26</v>
+        <v>6.21</v>
       </c>
       <c r="G25" t="n">
-        <v>224.3</v>
+        <v>216.5</v>
       </c>
       <c r="H25" t="n">
-        <v>11.4</v>
+        <v>12.2</v>
       </c>
       <c r="I25" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J25" t="n">
-        <v>-130.04</v>
+        <v>107.36</v>
       </c>
       <c r="K25" t="n">
-        <v>-92.70999999999999</v>
+        <v>19.28</v>
       </c>
       <c r="L25" t="n">
-        <v>159.7</v>
+        <v>109.08</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:39:28</t>
+          <t>06:39:14</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="F26" t="n">
-        <v>4.75</v>
+        <v>4.08</v>
       </c>
       <c r="G26" t="n">
-        <v>226.8</v>
+        <v>221.5</v>
       </c>
       <c r="H26" t="n">
-        <v>11</v>
+        <v>14.1</v>
       </c>
       <c r="I26" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J26" t="n">
-        <v>123.82</v>
+        <v>99.97</v>
       </c>
       <c r="K26" t="n">
-        <v>31.51</v>
+        <v>-95.98</v>
       </c>
       <c r="L26" t="n">
-        <v>127.76</v>
+        <v>138.58</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:40:31</t>
+          <t>06:41:06</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="F27" t="n">
-        <v>5.66</v>
+        <v>6.21</v>
       </c>
       <c r="G27" t="n">
-        <v>221.5</v>
+        <v>235.6</v>
       </c>
       <c r="H27" t="n">
-        <v>14.1</v>
+        <v>9.1</v>
       </c>
       <c r="I27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>-98.2</v>
+        <v>-164.68</v>
       </c>
       <c r="K27" t="n">
-        <v>113.49</v>
+        <v>-100.27</v>
       </c>
       <c r="L27" t="n">
-        <v>150.08</v>
+        <v>192.8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:41:28</t>
+          <t>06:43:25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="F28" t="n">
-        <v>5.71</v>
+        <v>3.82</v>
       </c>
       <c r="G28" t="n">
-        <v>220.7</v>
+        <v>236.1</v>
       </c>
       <c r="H28" t="n">
-        <v>21.6</v>
+        <v>12.7</v>
       </c>
       <c r="I28" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J28" t="n">
-        <v>-136.01</v>
+        <v>-134.33</v>
       </c>
       <c r="K28" t="n">
-        <v>-84.34</v>
+        <v>63.43</v>
       </c>
       <c r="L28" t="n">
-        <v>160.04</v>
+        <v>148.55</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:53:26</t>
+          <t>06:54:50</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="F29" t="n">
-        <v>4.64</v>
+        <v>6.21</v>
       </c>
       <c r="G29" t="n">
-        <v>236.1</v>
+        <v>221.3</v>
       </c>
       <c r="H29" t="n">
-        <v>12.7</v>
+        <v>13.3</v>
       </c>
       <c r="I29" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>24.7</v>
+        <v>47.36</v>
       </c>
       <c r="K29" t="n">
-        <v>20.43</v>
+        <v>-25.01</v>
       </c>
       <c r="L29" t="n">
-        <v>32.06</v>
+        <v>53.56</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06:55:19</t>
+          <t>06:55:50</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="F30" t="n">
-        <v>5</v>
+        <v>5.18</v>
       </c>
       <c r="G30" t="n">
-        <v>229</v>
+        <v>232.9</v>
       </c>
       <c r="H30" t="n">
-        <v>18.8</v>
+        <v>6.5</v>
       </c>
       <c r="I30" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J30" t="n">
-        <v>44.64</v>
+        <v>-30.41</v>
       </c>
       <c r="K30" t="n">
-        <v>-23.24</v>
+        <v>-41.11</v>
       </c>
       <c r="L30" t="n">
-        <v>50.33</v>
+        <v>51.13</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06:57:38</t>
+          <t>06:57:49</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>1.59</v>
+        <v>1.79</v>
       </c>
       <c r="F31" t="n">
-        <v>5.01</v>
+        <v>6.21</v>
       </c>
       <c r="G31" t="n">
-        <v>232.9</v>
+        <v>231.8</v>
       </c>
       <c r="H31" t="n">
-        <v>6.5</v>
+        <v>14.1</v>
       </c>
       <c r="I31" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J31" t="n">
-        <v>-42.96</v>
+        <v>5.37</v>
       </c>
       <c r="K31" t="n">
-        <v>29.27</v>
+        <v>-34.68</v>
       </c>
       <c r="L31" t="n">
-        <v>51.99</v>
+        <v>35.1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:02:03</t>
+          <t>07:02:05</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="F32" t="n">
-        <v>5.52</v>
+        <v>4.27</v>
       </c>
       <c r="G32" t="n">
-        <v>230.7</v>
+        <v>238.2</v>
       </c>
       <c r="H32" t="n">
-        <v>15.8</v>
+        <v>15.2</v>
       </c>
       <c r="I32" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J32" t="n">
-        <v>7.66</v>
+        <v>-26.83</v>
       </c>
       <c r="K32" t="n">
-        <v>-47.56</v>
+        <v>-70.15000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>48.18</v>
+        <v>75.09999999999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:03:44</t>
+          <t>07:03:39</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="F33" t="n">
-        <v>5.54</v>
+        <v>3.16</v>
       </c>
       <c r="G33" t="n">
-        <v>238.2</v>
+        <v>244.3</v>
       </c>
       <c r="H33" t="n">
-        <v>15.2</v>
+        <v>13.8</v>
       </c>
       <c r="I33" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>-68.94</v>
+        <v>62.91</v>
       </c>
       <c r="K33" t="n">
-        <v>-24.43</v>
+        <v>23.45</v>
       </c>
       <c r="L33" t="n">
-        <v>73.14</v>
+        <v>67.13</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:05:57</t>
+          <t>07:06:00</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>1.37</v>
+        <v>1.79</v>
       </c>
       <c r="F34" t="n">
-        <v>6.14</v>
+        <v>3.54</v>
       </c>
       <c r="G34" t="n">
-        <v>230.1</v>
+        <v>229.3</v>
       </c>
       <c r="H34" t="n">
-        <v>14.5</v>
+        <v>11.7</v>
       </c>
       <c r="I34" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J34" t="n">
-        <v>61.12</v>
+        <v>-49.9</v>
       </c>
       <c r="K34" t="n">
-        <v>22.7</v>
+        <v>18.69</v>
       </c>
       <c r="L34" t="n">
-        <v>65.2</v>
+        <v>53.28</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:10:32</t>
+          <t>07:11:15</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>1.79</v>
+        <v>1.43</v>
       </c>
       <c r="F35" t="n">
-        <v>5.15</v>
+        <v>2.33</v>
       </c>
       <c r="G35" t="n">
-        <v>229.3</v>
+        <v>227.6</v>
       </c>
       <c r="H35" t="n">
-        <v>11.7</v>
+        <v>9.5</v>
       </c>
       <c r="I35" t="n">
         <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>28.61</v>
+        <v>38.74</v>
       </c>
       <c r="K35" t="n">
-        <v>-77.16</v>
+        <v>-54.76</v>
       </c>
       <c r="L35" t="n">
-        <v>82.29000000000001</v>
+        <v>67.08</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:13:03</t>
+          <t>07:13:40</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="F36" t="n">
-        <v>5.31</v>
+        <v>5.66</v>
       </c>
       <c r="G36" t="n">
-        <v>221.5</v>
+        <v>232.2</v>
       </c>
       <c r="H36" t="n">
-        <v>12.6</v>
+        <v>17.1</v>
       </c>
       <c r="I36" t="n">
         <v>27</v>
       </c>
       <c r="J36" t="n">
-        <v>42.29</v>
+        <v>96.37</v>
       </c>
       <c r="K36" t="n">
-        <v>-52.5</v>
+        <v>-31.07</v>
       </c>
       <c r="L36" t="n">
-        <v>67.41</v>
+        <v>101.26</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:14:57</t>
+          <t>07:14:54</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>1.39</v>
+        <v>1.87</v>
       </c>
       <c r="F37" t="n">
-        <v>5.88</v>
+        <v>6.21</v>
       </c>
       <c r="G37" t="n">
-        <v>232.2</v>
+        <v>221.7</v>
       </c>
       <c r="H37" t="n">
-        <v>17.1</v>
+        <v>5.6</v>
       </c>
       <c r="I37" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J37" t="n">
-        <v>-29.4</v>
+        <v>-93.88</v>
       </c>
       <c r="K37" t="n">
-        <v>84.44</v>
+        <v>40.08</v>
       </c>
       <c r="L37" t="n">
-        <v>89.41</v>
+        <v>102.08</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:18:51</t>
+          <t>07:19:35</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1.57</v>
+        <v>1.98</v>
       </c>
       <c r="F38" t="n">
-        <v>5.01</v>
+        <v>6.21</v>
       </c>
       <c r="G38" t="n">
-        <v>213.6</v>
+        <v>231.1</v>
       </c>
       <c r="H38" t="n">
-        <v>16.3</v>
+        <v>19.4</v>
       </c>
       <c r="I38" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J38" t="n">
-        <v>-122.18</v>
+        <v>-62.27</v>
       </c>
       <c r="K38" t="n">
-        <v>55.97</v>
+        <v>62.51</v>
       </c>
       <c r="L38" t="n">
-        <v>134.39</v>
+        <v>88.23</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:20:58</t>
+          <t>07:21:28</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="F39" t="n">
-        <v>5.39</v>
+        <v>6.21</v>
       </c>
       <c r="G39" t="n">
-        <v>231.1</v>
+        <v>236.6</v>
       </c>
       <c r="H39" t="n">
-        <v>19.4</v>
+        <v>7.1</v>
       </c>
       <c r="I39" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J39" t="n">
-        <v>52.78</v>
+        <v>58.18</v>
       </c>
       <c r="K39" t="n">
-        <v>91.01000000000001</v>
+        <v>81.87</v>
       </c>
       <c r="L39" t="n">
-        <v>105.21</v>
+        <v>100.44</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:22:34</t>
+          <t>07:22:28</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>1.71</v>
+        <v>1.43</v>
       </c>
       <c r="F40" t="n">
-        <v>5.76</v>
+        <v>6.21</v>
       </c>
       <c r="G40" t="n">
-        <v>216.7</v>
+        <v>219.6</v>
       </c>
       <c r="H40" t="n">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="I40" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>57.01</v>
+        <v>-64.65000000000001</v>
       </c>
       <c r="K40" t="n">
-        <v>69.11</v>
+        <v>-151.65</v>
       </c>
       <c r="L40" t="n">
-        <v>89.59</v>
+        <v>164.85</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:26:33</t>
+          <t>07:26:46</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1.44</v>
+        <v>1.72</v>
       </c>
       <c r="F41" t="n">
-        <v>5.37</v>
+        <v>6.1</v>
       </c>
       <c r="G41" t="n">
-        <v>246.4</v>
+        <v>230.9</v>
       </c>
       <c r="H41" t="n">
-        <v>17.3</v>
+        <v>16.3</v>
       </c>
       <c r="I41" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J41" t="n">
-        <v>98.2</v>
+        <v>49.54</v>
       </c>
       <c r="K41" t="n">
-        <v>-106.9</v>
+        <v>-125.15</v>
       </c>
       <c r="L41" t="n">
-        <v>145.16</v>
+        <v>134.6</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:27:24</t>
+          <t>07:28:40</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.3</v>
+        <v>1.88</v>
       </c>
       <c r="F42" t="n">
-        <v>5.07</v>
+        <v>6.21</v>
       </c>
       <c r="G42" t="n">
-        <v>232</v>
+        <v>223.1</v>
       </c>
       <c r="H42" t="n">
-        <v>9.800000000000001</v>
+        <v>10.7</v>
       </c>
       <c r="I42" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>11.6</v>
+        <v>-80.31999999999999</v>
       </c>
       <c r="K42" t="n">
-        <v>-229.23</v>
+        <v>163.45</v>
       </c>
       <c r="L42" t="n">
-        <v>229.52</v>
+        <v>182.12</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:28:42</t>
+          <t>07:31:04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="F43" t="n">
-        <v>5.12</v>
+        <v>3.54</v>
       </c>
       <c r="G43" t="n">
-        <v>235.4</v>
+        <v>227.6</v>
       </c>
       <c r="H43" t="n">
-        <v>15.1</v>
+        <v>12.8</v>
       </c>
       <c r="I43" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J43" t="n">
-        <v>-27.03</v>
+        <v>-85.31999999999999</v>
       </c>
       <c r="K43" t="n">
-        <v>-116.7</v>
+        <v>-187</v>
       </c>
       <c r="L43" t="n">
-        <v>119.79</v>
+        <v>205.55</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:37:11</t>
+          <t>07:41:54</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1.88</v>
+        <v>1.51</v>
       </c>
       <c r="F44" t="n">
-        <v>5.79</v>
+        <v>4.37</v>
       </c>
       <c r="G44" t="n">
-        <v>222.8</v>
+        <v>237.5</v>
       </c>
       <c r="H44" t="n">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
       <c r="I44" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>-8.210000000000001</v>
+        <v>22.41</v>
       </c>
       <c r="K44" t="n">
-        <v>37.44</v>
+        <v>24.61</v>
       </c>
       <c r="L44" t="n">
-        <v>38.33</v>
+        <v>33.29</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:39:06</t>
+          <t>07:43:10</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="F45" t="n">
-        <v>4.78</v>
+        <v>6.21</v>
       </c>
       <c r="G45" t="n">
-        <v>227.4</v>
+        <v>233.5</v>
       </c>
       <c r="H45" t="n">
-        <v>14.5</v>
+        <v>16.4</v>
       </c>
       <c r="I45" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J45" t="n">
-        <v>11.67</v>
+        <v>-1.25</v>
       </c>
       <c r="K45" t="n">
-        <v>28.66</v>
+        <v>-40.7</v>
       </c>
       <c r="L45" t="n">
-        <v>30.94</v>
+        <v>40.72</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:41:30</t>
+          <t>07:45:11</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="F46" t="n">
-        <v>5.86</v>
+        <v>4.22</v>
       </c>
       <c r="G46" t="n">
-        <v>236.7</v>
+        <v>231.4</v>
       </c>
       <c r="H46" t="n">
-        <v>14.7</v>
+        <v>13.3</v>
       </c>
       <c r="I46" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>13.19</v>
+        <v>-37.19</v>
       </c>
       <c r="K46" t="n">
-        <v>-45.79</v>
+        <v>-48.83</v>
       </c>
       <c r="L46" t="n">
-        <v>47.65</v>
+        <v>61.38</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:45:18</t>
+          <t>07:50:31</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="F47" t="n">
-        <v>5.38</v>
+        <v>5.74</v>
       </c>
       <c r="G47" t="n">
-        <v>221.8</v>
+        <v>224.4</v>
       </c>
       <c r="H47" t="n">
-        <v>18</v>
+        <v>18.4</v>
       </c>
       <c r="I47" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J47" t="n">
-        <v>34.48</v>
+        <v>27.79</v>
       </c>
       <c r="K47" t="n">
-        <v>-65.72</v>
+        <v>-53.85</v>
       </c>
       <c r="L47" t="n">
-        <v>74.22</v>
+        <v>60.6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:46:57</t>
+          <t>07:51:38</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>1.28</v>
+        <v>1.83</v>
       </c>
       <c r="F48" t="n">
-        <v>5.64</v>
+        <v>4.75</v>
       </c>
       <c r="G48" t="n">
-        <v>230.7</v>
+        <v>228.3</v>
       </c>
       <c r="H48" t="n">
-        <v>3.4</v>
+        <v>14.1</v>
       </c>
       <c r="I48" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>-39.05</v>
+        <v>-42.13</v>
       </c>
       <c r="K48" t="n">
-        <v>9.300000000000001</v>
+        <v>21</v>
       </c>
       <c r="L48" t="n">
-        <v>40.14</v>
+        <v>47.08</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:49:13</t>
+          <t>07:52:57</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="F49" t="n">
-        <v>5.46</v>
+        <v>5.42</v>
       </c>
       <c r="G49" t="n">
-        <v>224.6</v>
+        <v>234.1</v>
       </c>
       <c r="H49" t="n">
-        <v>14.6</v>
+        <v>16.7</v>
       </c>
       <c r="I49" t="n">
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>45.07</v>
+        <v>11.75</v>
       </c>
       <c r="K49" t="n">
-        <v>-22.16</v>
+        <v>-51.17</v>
       </c>
       <c r="L49" t="n">
-        <v>50.23</v>
+        <v>52.51</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07:54:26</t>
+          <t>07:57:19</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>1.72</v>
+        <v>1.41</v>
       </c>
       <c r="F50" t="n">
-        <v>5.04</v>
+        <v>4.48</v>
       </c>
       <c r="G50" t="n">
-        <v>230.8</v>
+        <v>230.6</v>
       </c>
       <c r="H50" t="n">
-        <v>9.699999999999999</v>
+        <v>15.6</v>
       </c>
       <c r="I50" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J50" t="n">
-        <v>45.76</v>
+        <v>-73.04000000000001</v>
       </c>
       <c r="K50" t="n">
-        <v>-64.77</v>
+        <v>-30.09</v>
       </c>
       <c r="L50" t="n">
-        <v>79.3</v>
+        <v>78.98999999999999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07:55:59</t>
+          <t>07:59:39</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>1.72</v>
+        <v>1.97</v>
       </c>
       <c r="F51" t="n">
-        <v>5.61</v>
+        <v>5.53</v>
       </c>
       <c r="G51" t="n">
-        <v>229</v>
+        <v>225.9</v>
       </c>
       <c r="H51" t="n">
-        <v>11.1</v>
+        <v>12.7</v>
       </c>
       <c r="I51" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>56.79</v>
+        <v>-83.58</v>
       </c>
       <c r="K51" t="n">
-        <v>-65.43000000000001</v>
+        <v>14.69</v>
       </c>
       <c r="L51" t="n">
-        <v>86.64</v>
+        <v>84.86</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07:58:16</t>
+          <t>08:01:46</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="F52" t="n">
-        <v>4.97</v>
+        <v>6.21</v>
       </c>
       <c r="G52" t="n">
-        <v>225.8</v>
+        <v>235</v>
       </c>
       <c r="H52" t="n">
-        <v>5.8</v>
+        <v>23.2</v>
       </c>
       <c r="I52" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>-42.88</v>
+        <v>-39.73</v>
       </c>
       <c r="K52" t="n">
-        <v>53.18</v>
+        <v>25.87</v>
       </c>
       <c r="L52" t="n">
-        <v>68.31</v>
+        <v>47.41</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:03:38</t>
+          <t>08:05:41</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="F53" t="n">
-        <v>6.37</v>
+        <v>1.91</v>
       </c>
       <c r="G53" t="n">
-        <v>235.3</v>
+        <v>228.5</v>
       </c>
       <c r="H53" t="n">
-        <v>13.5</v>
+        <v>11.6</v>
       </c>
       <c r="I53" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J53" t="n">
-        <v>-103.08</v>
+        <v>-95.47</v>
       </c>
       <c r="K53" t="n">
-        <v>-12.62</v>
+        <v>11.11</v>
       </c>
       <c r="L53" t="n">
-        <v>103.85</v>
+        <v>96.11</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:04:55</t>
+          <t>08:07:11</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>1.73</v>
+        <v>3.11</v>
       </c>
       <c r="F54" t="n">
-        <v>5.62</v>
+        <v>6.21</v>
       </c>
       <c r="G54" t="n">
-        <v>211.2</v>
+        <v>225.2</v>
       </c>
       <c r="H54" t="n">
-        <v>15.4</v>
+        <v>12.7</v>
       </c>
       <c r="I54" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J54" t="n">
-        <v>-12.5</v>
+        <v>-52.23</v>
       </c>
       <c r="K54" t="n">
-        <v>123.57</v>
+        <v>-121.03</v>
       </c>
       <c r="L54" t="n">
-        <v>124.2</v>
+        <v>131.81</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:07:14</t>
+          <t>08:08:10</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="F55" t="n">
-        <v>5.94</v>
+        <v>6.21</v>
       </c>
       <c r="G55" t="n">
-        <v>216.5</v>
+        <v>227.7</v>
       </c>
       <c r="H55" t="n">
-        <v>14.2</v>
+        <v>20</v>
       </c>
       <c r="I55" t="n">
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>-75.67</v>
+        <v>-106.1</v>
       </c>
       <c r="K55" t="n">
-        <v>-47.88</v>
+        <v>137.13</v>
       </c>
       <c r="L55" t="n">
-        <v>89.55</v>
+        <v>173.39</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:11:18</t>
+          <t>08:13:31</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>1.64</v>
+        <v>1.82</v>
       </c>
       <c r="F56" t="n">
-        <v>5.67</v>
+        <v>6.21</v>
       </c>
       <c r="G56" t="n">
-        <v>224.6</v>
+        <v>218.6</v>
       </c>
       <c r="H56" t="n">
-        <v>14.2</v>
+        <v>18.9</v>
       </c>
       <c r="I56" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J56" t="n">
-        <v>178.12</v>
+        <v>-40.72</v>
       </c>
       <c r="K56" t="n">
-        <v>-30.55</v>
+        <v>-171.98</v>
       </c>
       <c r="L56" t="n">
-        <v>180.72</v>
+        <v>176.73</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:13:27</t>
+          <t>08:14:54</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="F57" t="n">
-        <v>6.08</v>
+        <v>2.89</v>
       </c>
       <c r="G57" t="n">
-        <v>223.9</v>
+        <v>232.6</v>
       </c>
       <c r="H57" t="n">
-        <v>16.1</v>
+        <v>18.2</v>
       </c>
       <c r="I57" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>-157.62</v>
+        <v>-115.83</v>
       </c>
       <c r="K57" t="n">
-        <v>-90.79000000000001</v>
+        <v>89.75</v>
       </c>
       <c r="L57" t="n">
-        <v>181.9</v>
+        <v>146.54</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:15:27</t>
+          <t>08:16:31</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>1.69</v>
+        <v>1.51</v>
       </c>
       <c r="F58" t="n">
-        <v>4.85</v>
+        <v>5.01</v>
       </c>
       <c r="G58" t="n">
-        <v>235.1</v>
+        <v>224.7</v>
       </c>
       <c r="H58" t="n">
-        <v>13.1</v>
+        <v>18</v>
       </c>
       <c r="I58" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J58" t="n">
-        <v>149.79</v>
+        <v>-188.37</v>
       </c>
       <c r="K58" t="n">
-        <v>48</v>
+        <v>36.88</v>
       </c>
       <c r="L58" t="n">
-        <v>157.29</v>
+        <v>191.95</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:25:48</t>
+          <t>08:27:37</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="F59" t="n">
-        <v>5.41</v>
+        <v>3.97</v>
       </c>
       <c r="G59" t="n">
-        <v>231.3</v>
+        <v>221.3</v>
       </c>
       <c r="H59" t="n">
-        <v>8.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="I59" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>-26.95</v>
+        <v>-7.23</v>
       </c>
       <c r="K59" t="n">
-        <v>-22.99</v>
+        <v>37.7</v>
       </c>
       <c r="L59" t="n">
-        <v>35.42</v>
+        <v>38.38</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:27:10</t>
+          <t>08:29:20</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>1.51</v>
+        <v>2.5</v>
       </c>
       <c r="F60" t="n">
-        <v>5.09</v>
+        <v>6.21</v>
       </c>
       <c r="G60" t="n">
-        <v>222.5</v>
+        <v>238.6</v>
       </c>
       <c r="H60" t="n">
-        <v>11.8</v>
+        <v>18.7</v>
       </c>
       <c r="I60" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J60" t="n">
-        <v>-30.88</v>
+        <v>-42.28</v>
       </c>
       <c r="K60" t="n">
-        <v>-28.43</v>
+        <v>31.01</v>
       </c>
       <c r="L60" t="n">
-        <v>41.98</v>
+        <v>52.43</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:28:47</t>
+          <t>08:30:26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>1.88</v>
+        <v>1.97</v>
       </c>
       <c r="F61" t="n">
-        <v>5.46</v>
+        <v>6.21</v>
       </c>
       <c r="G61" t="n">
-        <v>229.4</v>
+        <v>230.6</v>
       </c>
       <c r="H61" t="n">
-        <v>12.1</v>
+        <v>16.5</v>
       </c>
       <c r="I61" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J61" t="n">
-        <v>35.5</v>
+        <v>3.85</v>
       </c>
       <c r="K61" t="n">
-        <v>31.36</v>
+        <v>-39.38</v>
       </c>
       <c r="L61" t="n">
-        <v>47.36</v>
+        <v>39.57</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:33:26</t>
+          <t>08:34:13</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="F62" t="n">
-        <v>5.87</v>
+        <v>2.28</v>
       </c>
       <c r="G62" t="n">
-        <v>240.4</v>
+        <v>229.1</v>
       </c>
       <c r="H62" t="n">
-        <v>16.5</v>
+        <v>14.1</v>
       </c>
       <c r="I62" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J62" t="n">
-        <v>36.3</v>
+        <v>39.72</v>
       </c>
       <c r="K62" t="n">
-        <v>37.58</v>
+        <v>41.9</v>
       </c>
       <c r="L62" t="n">
-        <v>52.25</v>
+        <v>57.74</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:35:08</t>
+          <t>08:35:33</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>1.76</v>
+        <v>1.98</v>
       </c>
       <c r="F63" t="n">
-        <v>5.12</v>
+        <v>3.8</v>
       </c>
       <c r="G63" t="n">
-        <v>223.9</v>
+        <v>241.8</v>
       </c>
       <c r="H63" t="n">
-        <v>10.3</v>
+        <v>19</v>
       </c>
       <c r="I63" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>12.24</v>
+        <v>-72.11</v>
       </c>
       <c r="K63" t="n">
-        <v>-5.38</v>
+        <v>12.09</v>
       </c>
       <c r="L63" t="n">
-        <v>13.37</v>
+        <v>73.12</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:36:50</t>
+          <t>08:36:44</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="F64" t="n">
-        <v>5.1</v>
+        <v>6.21</v>
       </c>
       <c r="G64" t="n">
-        <v>240.7</v>
+        <v>224.7</v>
       </c>
       <c r="H64" t="n">
-        <v>18.8</v>
+        <v>17.1</v>
       </c>
       <c r="I64" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J64" t="n">
-        <v>37.75</v>
+        <v>28.66</v>
       </c>
       <c r="K64" t="n">
-        <v>56.83</v>
+        <v>-47.14</v>
       </c>
       <c r="L64" t="n">
-        <v>68.23</v>
+        <v>55.17</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:41:56</t>
+          <t>08:39:39</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="F65" t="n">
-        <v>5.9</v>
+        <v>6.21</v>
       </c>
       <c r="G65" t="n">
-        <v>233.8</v>
+        <v>222</v>
       </c>
       <c r="H65" t="n">
-        <v>15</v>
+        <v>12.7</v>
       </c>
       <c r="I65" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J65" t="n">
-        <v>68.37</v>
+        <v>-53.98</v>
       </c>
       <c r="K65" t="n">
-        <v>-48.49</v>
+        <v>-53.24</v>
       </c>
       <c r="L65" t="n">
-        <v>83.81999999999999</v>
+        <v>75.81999999999999</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:44:03</t>
+          <t>08:40:36</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>1.57</v>
+        <v>1.94</v>
       </c>
       <c r="F66" t="n">
-        <v>4.72</v>
+        <v>6.21</v>
       </c>
       <c r="G66" t="n">
-        <v>241.2</v>
+        <v>233.2</v>
       </c>
       <c r="H66" t="n">
-        <v>10.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>44.45</v>
+        <v>113.01</v>
       </c>
       <c r="K66" t="n">
-        <v>-35.07</v>
+        <v>-12.01</v>
       </c>
       <c r="L66" t="n">
-        <v>56.61</v>
+        <v>113.65</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:46:38</t>
+          <t>08:42:00</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>1.59</v>
+        <v>1.27</v>
       </c>
       <c r="F67" t="n">
-        <v>5.09</v>
+        <v>2.54</v>
       </c>
       <c r="G67" t="n">
-        <v>238.3</v>
+        <v>224.1</v>
       </c>
       <c r="H67" t="n">
-        <v>11.4</v>
+        <v>12</v>
       </c>
       <c r="I67" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J67" t="n">
-        <v>-87.2</v>
+        <v>-67.13</v>
       </c>
       <c r="K67" t="n">
-        <v>30.24</v>
+        <v>42.37</v>
       </c>
       <c r="L67" t="n">
-        <v>92.3</v>
+        <v>79.39</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:49:54</t>
+          <t>08:45:10</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>1.37</v>
+        <v>2.39</v>
       </c>
       <c r="F68" t="n">
-        <v>5.11</v>
+        <v>5.8</v>
       </c>
       <c r="G68" t="n">
-        <v>207</v>
+        <v>231.2</v>
       </c>
       <c r="H68" t="n">
-        <v>12.9</v>
+        <v>13.8</v>
       </c>
       <c r="I68" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J68" t="n">
-        <v>-76.79000000000001</v>
+        <v>57.64</v>
       </c>
       <c r="K68" t="n">
-        <v>-46.35</v>
+        <v>43.56</v>
       </c>
       <c r="L68" t="n">
-        <v>89.7</v>
+        <v>72.23999999999999</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:50:52</t>
+          <t>08:46:26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="F69" t="n">
-        <v>5.3</v>
+        <v>4.84</v>
       </c>
       <c r="G69" t="n">
-        <v>239</v>
+        <v>245.2</v>
       </c>
       <c r="H69" t="n">
-        <v>16.8</v>
+        <v>15.2</v>
       </c>
       <c r="I69" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J69" t="n">
-        <v>-103.02</v>
+        <v>9</v>
       </c>
       <c r="K69" t="n">
-        <v>3.47</v>
+        <v>-90.62</v>
       </c>
       <c r="L69" t="n">
-        <v>103.08</v>
+        <v>91.06999999999999</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:52:24</t>
+          <t>08:47:32</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="F70" t="n">
-        <v>4.98</v>
+        <v>5.73</v>
       </c>
       <c r="G70" t="n">
-        <v>231.9</v>
+        <v>236.1</v>
       </c>
       <c r="H70" t="n">
-        <v>15.1</v>
+        <v>11.1</v>
       </c>
       <c r="I70" t="n">
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>-20.15</v>
+        <v>66.7</v>
       </c>
       <c r="K70" t="n">
-        <v>126.7</v>
+        <v>-102.27</v>
       </c>
       <c r="L70" t="n">
-        <v>128.29</v>
+        <v>122.1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:56:18</t>
+          <t>08:52:20</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="F71" t="n">
-        <v>5.12</v>
+        <v>6.21</v>
       </c>
       <c r="G71" t="n">
-        <v>223.6</v>
+        <v>228.1</v>
       </c>
       <c r="H71" t="n">
-        <v>14.4</v>
+        <v>13.2</v>
       </c>
       <c r="I71" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>16.77</v>
+        <v>-107.21</v>
       </c>
       <c r="K71" t="n">
-        <v>-136.14</v>
+        <v>116.68</v>
       </c>
       <c r="L71" t="n">
-        <v>137.17</v>
+        <v>158.45</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:57:19</t>
+          <t>08:54:26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="F72" t="n">
-        <v>5.8</v>
+        <v>3.32</v>
       </c>
       <c r="G72" t="n">
-        <v>221.6</v>
+        <v>235</v>
       </c>
       <c r="H72" t="n">
-        <v>16.9</v>
+        <v>15.1</v>
       </c>
       <c r="I72" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J72" t="n">
-        <v>135.16</v>
+        <v>130.48</v>
       </c>
       <c r="K72" t="n">
-        <v>108.01</v>
+        <v>33.98</v>
       </c>
       <c r="L72" t="n">
-        <v>173.01</v>
+        <v>134.83</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08:58:39</t>
+          <t>08:55:30</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="F73" t="n">
-        <v>5.25</v>
+        <v>5.8</v>
       </c>
       <c r="G73" t="n">
-        <v>235.4</v>
+        <v>230</v>
       </c>
       <c r="H73" t="n">
-        <v>12.3</v>
+        <v>15.4</v>
       </c>
       <c r="I73" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>-155.02</v>
+        <v>-51.47</v>
       </c>
       <c r="K73" t="n">
-        <v>42.58</v>
+        <v>175.95</v>
       </c>
       <c r="L73" t="n">
-        <v>160.76</v>
+        <v>183.32</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:08:30</t>
+          <t>09:09:05</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="F74" t="n">
-        <v>5.09</v>
+        <v>6.21</v>
       </c>
       <c r="G74" t="n">
-        <v>232.5</v>
+        <v>243.2</v>
       </c>
       <c r="H74" t="n">
-        <v>18.1</v>
+        <v>7.8</v>
       </c>
       <c r="I74" t="n">
         <v>29</v>
       </c>
       <c r="J74" t="n">
-        <v>7.81</v>
+        <v>17.1</v>
       </c>
       <c r="K74" t="n">
-        <v>-28.8</v>
+        <v>-53.65</v>
       </c>
       <c r="L74" t="n">
-        <v>29.84</v>
+        <v>56.31</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:10:36</t>
+          <t>09:10:59</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="F75" t="n">
-        <v>5.95</v>
+        <v>6.21</v>
       </c>
       <c r="G75" t="n">
-        <v>240.7</v>
+        <v>234.4</v>
       </c>
       <c r="H75" t="n">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="I75" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J75" t="n">
-        <v>1.31</v>
+        <v>-31.34</v>
       </c>
       <c r="K75" t="n">
-        <v>-41.57</v>
+        <v>9.51</v>
       </c>
       <c r="L75" t="n">
-        <v>41.59</v>
+        <v>32.75</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:11:40</t>
+          <t>09:13:22</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="F76" t="n">
-        <v>5.42</v>
+        <v>6.21</v>
       </c>
       <c r="G76" t="n">
-        <v>211.2</v>
+        <v>241.4</v>
       </c>
       <c r="H76" t="n">
-        <v>16.5</v>
+        <v>13.8</v>
       </c>
       <c r="I76" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J76" t="n">
-        <v>30.83</v>
+        <v>43.31</v>
       </c>
       <c r="K76" t="n">
-        <v>-21.21</v>
+        <v>46.34</v>
       </c>
       <c r="L76" t="n">
-        <v>37.42</v>
+        <v>63.43</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:17:43</t>
+          <t>09:16:46</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="F77" t="n">
-        <v>5.94</v>
+        <v>6.21</v>
       </c>
       <c r="G77" t="n">
-        <v>230.9</v>
+        <v>229</v>
       </c>
       <c r="H77" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="I77" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J77" t="n">
-        <v>54.56</v>
+        <v>13.6</v>
       </c>
       <c r="K77" t="n">
-        <v>2.56</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="L77" t="n">
-        <v>54.62</v>
+        <v>70.51000000000001</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:19:24</t>
+          <t>09:18:36</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.05</v>
+        <v>1.81</v>
       </c>
       <c r="F78" t="n">
-        <v>5.58</v>
+        <v>6.21</v>
       </c>
       <c r="G78" t="n">
-        <v>246.6</v>
+        <v>224.9</v>
       </c>
       <c r="H78" t="n">
-        <v>21.6</v>
+        <v>8.6</v>
       </c>
       <c r="I78" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>-7.43</v>
+        <v>16.77</v>
       </c>
       <c r="K78" t="n">
-        <v>-26.67</v>
+        <v>-64.31</v>
       </c>
       <c r="L78" t="n">
-        <v>27.68</v>
+        <v>66.45999999999999</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:21:01</t>
+          <t>09:19:45</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.81</v>
+        <v>1.67</v>
       </c>
       <c r="F79" t="n">
-        <v>4.8</v>
+        <v>6.21</v>
       </c>
       <c r="G79" t="n">
-        <v>230.2</v>
+        <v>237.4</v>
       </c>
       <c r="H79" t="n">
-        <v>21.4</v>
+        <v>8.6</v>
       </c>
       <c r="I79" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J79" t="n">
-        <v>-58.31</v>
+        <v>-23.2</v>
       </c>
       <c r="K79" t="n">
-        <v>-27.18</v>
+        <v>-67.01000000000001</v>
       </c>
       <c r="L79" t="n">
-        <v>64.34</v>
+        <v>70.91</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:24:59</t>
+          <t>09:23:34</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="F80" t="n">
-        <v>4.81</v>
+        <v>6.21</v>
       </c>
       <c r="G80" t="n">
-        <v>223.4</v>
+        <v>221.3</v>
       </c>
       <c r="H80" t="n">
-        <v>7.7</v>
+        <v>13</v>
       </c>
       <c r="I80" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>63.47</v>
+        <v>-90.03</v>
       </c>
       <c r="K80" t="n">
-        <v>-69.13</v>
+        <v>29.06</v>
       </c>
       <c r="L80" t="n">
-        <v>93.84999999999999</v>
+        <v>94.59999999999999</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:27:03</t>
+          <t>09:24:58</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>1.98</v>
+        <v>1.63</v>
       </c>
       <c r="F81" t="n">
-        <v>5.16</v>
+        <v>6.21</v>
       </c>
       <c r="G81" t="n">
-        <v>220.8</v>
+        <v>221.1</v>
       </c>
       <c r="H81" t="n">
-        <v>5.6</v>
+        <v>22.3</v>
       </c>
       <c r="I81" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J81" t="n">
-        <v>-11.41</v>
+        <v>31.79</v>
       </c>
       <c r="K81" t="n">
-        <v>-79.31</v>
+        <v>77.31</v>
       </c>
       <c r="L81" t="n">
-        <v>80.13</v>
+        <v>83.59</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:29:04</t>
+          <t>09:26:03</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>1.83</v>
+        <v>2.26</v>
       </c>
       <c r="F82" t="n">
-        <v>5.07</v>
+        <v>3.97</v>
       </c>
       <c r="G82" t="n">
-        <v>221.6</v>
+        <v>224.9</v>
       </c>
       <c r="H82" t="n">
-        <v>15.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I82" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>80.29000000000001</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="K82" t="n">
-        <v>101.01</v>
+        <v>18.86</v>
       </c>
       <c r="L82" t="n">
-        <v>129.03</v>
+        <v>69.67</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:33:30</t>
+          <t>09:30:58</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>1.63</v>
+        <v>2.59</v>
       </c>
       <c r="F83" t="n">
-        <v>5.43</v>
+        <v>6.21</v>
       </c>
       <c r="G83" t="n">
-        <v>212.1</v>
+        <v>228.2</v>
       </c>
       <c r="H83" t="n">
-        <v>18.2</v>
+        <v>17.6</v>
       </c>
       <c r="I83" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J83" t="n">
-        <v>-114.62</v>
+        <v>34.65</v>
       </c>
       <c r="K83" t="n">
-        <v>-81.34999999999999</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="L83" t="n">
-        <v>140.56</v>
+        <v>84.3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:34:52</t>
+          <t>09:32:38</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>1.72</v>
+        <v>2.02</v>
       </c>
       <c r="F84" t="n">
-        <v>5.78</v>
+        <v>5.61</v>
       </c>
       <c r="G84" t="n">
-        <v>232.2</v>
+        <v>226.1</v>
       </c>
       <c r="H84" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="I84" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J84" t="n">
-        <v>-90.38</v>
+        <v>72.28</v>
       </c>
       <c r="K84" t="n">
-        <v>-26.65</v>
+        <v>-99.45999999999999</v>
       </c>
       <c r="L84" t="n">
-        <v>94.23</v>
+        <v>122.95</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:36:22</t>
+          <t>09:35:18</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>1.94</v>
+        <v>2.17</v>
       </c>
       <c r="F85" t="n">
-        <v>5.59</v>
+        <v>6.21</v>
       </c>
       <c r="G85" t="n">
-        <v>232.1</v>
+        <v>227.3</v>
       </c>
       <c r="H85" t="n">
-        <v>9.800000000000001</v>
+        <v>14.6</v>
       </c>
       <c r="I85" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J85" t="n">
-        <v>-69.75</v>
+        <v>-57.75</v>
       </c>
       <c r="K85" t="n">
-        <v>-67.52</v>
+        <v>-81.68000000000001</v>
       </c>
       <c r="L85" t="n">
-        <v>97.08</v>
+        <v>100.03</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:41:07</t>
+          <t>09:40:59</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>1.95</v>
+        <v>2.13</v>
       </c>
       <c r="F86" t="n">
-        <v>4.85</v>
+        <v>5.99</v>
       </c>
       <c r="G86" t="n">
-        <v>239.4</v>
+        <v>244.3</v>
       </c>
       <c r="H86" t="n">
-        <v>11.7</v>
+        <v>7.5</v>
       </c>
       <c r="I86" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>-96.28</v>
+        <v>200.51</v>
       </c>
       <c r="K86" t="n">
-        <v>113.26</v>
+        <v>29.31</v>
       </c>
       <c r="L86" t="n">
-        <v>148.66</v>
+        <v>202.64</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:43:25</t>
+          <t>09:43:16</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.51</v>
+        <v>3</v>
       </c>
       <c r="F87" t="n">
-        <v>6.13</v>
+        <v>6.04</v>
       </c>
       <c r="G87" t="n">
-        <v>224.8</v>
+        <v>227.7</v>
       </c>
       <c r="H87" t="n">
-        <v>12.1</v>
+        <v>12.4</v>
       </c>
       <c r="I87" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>-87.14</v>
+        <v>-134.62</v>
       </c>
       <c r="K87" t="n">
-        <v>-180.27</v>
+        <v>-19.42</v>
       </c>
       <c r="L87" t="n">
-        <v>200.23</v>
+        <v>136.01</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:44:24</t>
+          <t>09:44:29</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.15</v>
+        <v>1.82</v>
       </c>
       <c r="F88" t="n">
-        <v>5.46</v>
+        <v>6.21</v>
       </c>
       <c r="G88" t="n">
-        <v>232.6</v>
+        <v>225.1</v>
       </c>
       <c r="H88" t="n">
-        <v>21.7</v>
+        <v>16.4</v>
       </c>
       <c r="I88" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>181.18</v>
+        <v>161.39</v>
       </c>
       <c r="K88" t="n">
-        <v>-191.77</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="L88" t="n">
-        <v>263.82</v>
+        <v>185.73</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-08-25.xlsx
+++ b/output/2024-08-25.xlsx
@@ -640,13 +640,13 @@
         <v>30</v>
       </c>
       <c r="J14" t="n">
-        <v>-13.67</v>
+        <v>-11.81</v>
       </c>
       <c r="K14" t="n">
-        <v>-23.13</v>
+        <v>-19.97</v>
       </c>
       <c r="L14" t="n">
-        <v>26.87</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>29</v>
       </c>
       <c r="J15" t="n">
-        <v>34.67</v>
+        <v>30.82</v>
       </c>
       <c r="K15" t="n">
-        <v>9.16</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>35.86</v>
+        <v>31.88</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.66</v>
       </c>
       <c r="K16" t="n">
-        <v>-33.1</v>
+        <v>-31.72</v>
       </c>
       <c r="L16" t="n">
-        <v>33.11</v>
+        <v>31.73</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>29</v>
       </c>
       <c r="J17" t="n">
-        <v>-62.4</v>
+        <v>-55.46</v>
       </c>
       <c r="K17" t="n">
-        <v>-34.06</v>
+        <v>-30.28</v>
       </c>
       <c r="L17" t="n">
-        <v>71.09</v>
+        <v>63.19</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>-40.54</v>
+        <v>-37.02</v>
       </c>
       <c r="K18" t="n">
-        <v>25.99</v>
+        <v>23.73</v>
       </c>
       <c r="L18" t="n">
-        <v>48.16</v>
+        <v>43.97</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>28</v>
       </c>
       <c r="J19" t="n">
-        <v>40.14</v>
+        <v>36.65</v>
       </c>
       <c r="K19" t="n">
-        <v>20.03</v>
+        <v>18.29</v>
       </c>
       <c r="L19" t="n">
-        <v>44.86</v>
+        <v>40.96</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>26</v>
       </c>
       <c r="J20" t="n">
-        <v>92.48</v>
+        <v>88.62</v>
       </c>
       <c r="K20" t="n">
-        <v>26.74</v>
+        <v>25.62</v>
       </c>
       <c r="L20" t="n">
-        <v>96.26000000000001</v>
+        <v>92.25</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>26</v>
       </c>
       <c r="J21" t="n">
-        <v>41.74</v>
+        <v>40</v>
       </c>
       <c r="K21" t="n">
-        <v>73.05</v>
+        <v>70.01000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>84.14</v>
+        <v>80.63</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>30</v>
       </c>
       <c r="J22" t="n">
-        <v>-75.84999999999999</v>
+        <v>-65.5</v>
       </c>
       <c r="K22" t="n">
-        <v>-9.460000000000001</v>
+        <v>-8.17</v>
       </c>
       <c r="L22" t="n">
-        <v>76.44</v>
+        <v>66.01000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>29</v>
       </c>
       <c r="J23" t="n">
-        <v>-85.23999999999999</v>
+        <v>-75.77</v>
       </c>
       <c r="K23" t="n">
-        <v>68.11</v>
+        <v>60.54</v>
       </c>
       <c r="L23" t="n">
-        <v>109.11</v>
+        <v>96.98</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>30</v>
       </c>
       <c r="J24" t="n">
-        <v>72.23</v>
+        <v>62.38</v>
       </c>
       <c r="K24" t="n">
-        <v>-115.41</v>
+        <v>-99.68000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>136.15</v>
+        <v>117.59</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>26</v>
       </c>
       <c r="J25" t="n">
-        <v>107.36</v>
+        <v>102.89</v>
       </c>
       <c r="K25" t="n">
-        <v>19.28</v>
+        <v>18.47</v>
       </c>
       <c r="L25" t="n">
-        <v>109.08</v>
+        <v>104.53</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>30</v>
       </c>
       <c r="J26" t="n">
-        <v>99.97</v>
+        <v>86.33</v>
       </c>
       <c r="K26" t="n">
-        <v>-95.98</v>
+        <v>-82.89</v>
       </c>
       <c r="L26" t="n">
-        <v>138.58</v>
+        <v>119.69</v>
       </c>
     </row>
     <row r="27">
@@ -1228,13 +1228,13 @@
         <v>30</v>
       </c>
       <c r="J28" t="n">
-        <v>-134.33</v>
+        <v>-116.01</v>
       </c>
       <c r="K28" t="n">
-        <v>63.43</v>
+        <v>54.78</v>
       </c>
       <c r="L28" t="n">
-        <v>148.55</v>
+        <v>128.3</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>47.36</v>
+        <v>45.39</v>
       </c>
       <c r="K29" t="n">
-        <v>-25.01</v>
+        <v>-23.96</v>
       </c>
       <c r="L29" t="n">
-        <v>53.56</v>
+        <v>51.33</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>28</v>
       </c>
       <c r="J30" t="n">
-        <v>-30.41</v>
+        <v>-27.76</v>
       </c>
       <c r="K30" t="n">
-        <v>-41.11</v>
+        <v>-37.54</v>
       </c>
       <c r="L30" t="n">
-        <v>51.13</v>
+        <v>46.69</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>30</v>
       </c>
       <c r="J31" t="n">
-        <v>5.37</v>
+        <v>4.64</v>
       </c>
       <c r="K31" t="n">
-        <v>-34.68</v>
+        <v>-29.95</v>
       </c>
       <c r="L31" t="n">
-        <v>35.1</v>
+        <v>30.31</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>26</v>
       </c>
       <c r="J32" t="n">
-        <v>-26.83</v>
+        <v>-25.71</v>
       </c>
       <c r="K32" t="n">
-        <v>-70.15000000000001</v>
+        <v>-67.23</v>
       </c>
       <c r="L32" t="n">
-        <v>75.09999999999999</v>
+        <v>71.98</v>
       </c>
     </row>
     <row r="33">
@@ -1480,13 +1480,13 @@
         <v>25</v>
       </c>
       <c r="J34" t="n">
-        <v>-49.9</v>
+        <v>-48.88</v>
       </c>
       <c r="K34" t="n">
-        <v>18.69</v>
+        <v>18.31</v>
       </c>
       <c r="L34" t="n">
-        <v>53.28</v>
+        <v>52.19</v>
       </c>
     </row>
     <row r="35">
@@ -1564,13 +1564,13 @@
         <v>27</v>
       </c>
       <c r="J36" t="n">
-        <v>96.37</v>
+        <v>90.22</v>
       </c>
       <c r="K36" t="n">
-        <v>-31.07</v>
+        <v>-29.08</v>
       </c>
       <c r="L36" t="n">
-        <v>101.26</v>
+        <v>94.79000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>29</v>
       </c>
       <c r="J37" t="n">
-        <v>-93.88</v>
+        <v>-83.45</v>
       </c>
       <c r="K37" t="n">
-        <v>40.08</v>
+        <v>35.62</v>
       </c>
       <c r="L37" t="n">
-        <v>102.08</v>
+        <v>90.73</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>29</v>
       </c>
       <c r="J38" t="n">
-        <v>-62.27</v>
+        <v>-55.35</v>
       </c>
       <c r="K38" t="n">
-        <v>62.51</v>
+        <v>55.57</v>
       </c>
       <c r="L38" t="n">
-        <v>88.23</v>
+        <v>78.43000000000001</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>26</v>
       </c>
       <c r="J39" t="n">
-        <v>58.18</v>
+        <v>55.76</v>
       </c>
       <c r="K39" t="n">
-        <v>81.87</v>
+        <v>78.45999999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>100.44</v>
+        <v>96.25</v>
       </c>
     </row>
     <row r="40">
@@ -1774,13 +1774,13 @@
         <v>27</v>
       </c>
       <c r="J41" t="n">
-        <v>49.54</v>
+        <v>46.38</v>
       </c>
       <c r="K41" t="n">
-        <v>-125.15</v>
+        <v>-117.16</v>
       </c>
       <c r="L41" t="n">
-        <v>134.6</v>
+        <v>126.01</v>
       </c>
     </row>
     <row r="42">
@@ -1858,13 +1858,13 @@
         <v>29</v>
       </c>
       <c r="J43" t="n">
-        <v>-85.31999999999999</v>
+        <v>-75.84</v>
       </c>
       <c r="K43" t="n">
-        <v>-187</v>
+        <v>-166.22</v>
       </c>
       <c r="L43" t="n">
-        <v>205.55</v>
+        <v>182.71</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>22.41</v>
+        <v>21.96</v>
       </c>
       <c r="K44" t="n">
-        <v>24.61</v>
+        <v>24.11</v>
       </c>
       <c r="L44" t="n">
-        <v>33.29</v>
+        <v>32.61</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>28</v>
       </c>
       <c r="J45" t="n">
-        <v>-1.25</v>
+        <v>-1.15</v>
       </c>
       <c r="K45" t="n">
-        <v>-40.7</v>
+        <v>-37.16</v>
       </c>
       <c r="L45" t="n">
-        <v>40.72</v>
+        <v>37.18</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>-37.19</v>
+        <v>-36.44</v>
       </c>
       <c r="K46" t="n">
-        <v>-48.83</v>
+        <v>-47.84</v>
       </c>
       <c r="L46" t="n">
-        <v>61.38</v>
+        <v>60.13</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>29</v>
       </c>
       <c r="J47" t="n">
-        <v>27.79</v>
+        <v>24.7</v>
       </c>
       <c r="K47" t="n">
-        <v>-53.85</v>
+        <v>-47.87</v>
       </c>
       <c r="L47" t="n">
-        <v>60.6</v>
+        <v>53.86</v>
       </c>
     </row>
     <row r="48">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>11.75</v>
+        <v>11</v>
       </c>
       <c r="K49" t="n">
-        <v>-51.17</v>
+        <v>-47.91</v>
       </c>
       <c r="L49" t="n">
-        <v>52.51</v>
+        <v>49.15</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>28</v>
       </c>
       <c r="J50" t="n">
-        <v>-73.04000000000001</v>
+        <v>-66.69</v>
       </c>
       <c r="K50" t="n">
-        <v>-30.09</v>
+        <v>-27.47</v>
       </c>
       <c r="L50" t="n">
-        <v>78.98999999999999</v>
+        <v>72.13</v>
       </c>
     </row>
     <row r="51">
@@ -2236,13 +2236,13 @@
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>-39.73</v>
+        <v>-38.92</v>
       </c>
       <c r="K52" t="n">
-        <v>25.87</v>
+        <v>25.34</v>
       </c>
       <c r="L52" t="n">
-        <v>47.41</v>
+        <v>46.44</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>29</v>
       </c>
       <c r="J53" t="n">
-        <v>-95.47</v>
+        <v>-84.86</v>
       </c>
       <c r="K53" t="n">
-        <v>11.11</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="L53" t="n">
-        <v>96.11</v>
+        <v>85.43000000000001</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>29</v>
       </c>
       <c r="J54" t="n">
-        <v>-52.23</v>
+        <v>-46.42</v>
       </c>
       <c r="K54" t="n">
-        <v>-121.03</v>
+        <v>-107.58</v>
       </c>
       <c r="L54" t="n">
-        <v>131.81</v>
+        <v>117.17</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>-106.1</v>
+        <v>-103.94</v>
       </c>
       <c r="K55" t="n">
-        <v>137.13</v>
+        <v>134.33</v>
       </c>
       <c r="L55" t="n">
-        <v>173.39</v>
+        <v>169.85</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>28</v>
       </c>
       <c r="J56" t="n">
-        <v>-40.72</v>
+        <v>-37.18</v>
       </c>
       <c r="K56" t="n">
-        <v>-171.98</v>
+        <v>-157.02</v>
       </c>
       <c r="L56" t="n">
-        <v>176.73</v>
+        <v>161.36</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>-115.83</v>
+        <v>-111.01</v>
       </c>
       <c r="K57" t="n">
-        <v>89.75</v>
+        <v>86.01000000000001</v>
       </c>
       <c r="L57" t="n">
-        <v>146.54</v>
+        <v>140.43</v>
       </c>
     </row>
     <row r="58">
@@ -2572,13 +2572,13 @@
         <v>25</v>
       </c>
       <c r="J60" t="n">
-        <v>-42.28</v>
+        <v>-41.41</v>
       </c>
       <c r="K60" t="n">
-        <v>31.01</v>
+        <v>30.38</v>
       </c>
       <c r="L60" t="n">
-        <v>52.43</v>
+        <v>51.36</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>27</v>
       </c>
       <c r="J61" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="K61" t="n">
-        <v>-39.38</v>
+        <v>-36.87</v>
       </c>
       <c r="L61" t="n">
-        <v>39.57</v>
+        <v>37.05</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>28</v>
       </c>
       <c r="J62" t="n">
-        <v>39.72</v>
+        <v>36.27</v>
       </c>
       <c r="K62" t="n">
-        <v>41.9</v>
+        <v>38.26</v>
       </c>
       <c r="L62" t="n">
-        <v>57.74</v>
+        <v>52.72</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>-72.11</v>
+        <v>-70.64</v>
       </c>
       <c r="K63" t="n">
-        <v>12.09</v>
+        <v>11.85</v>
       </c>
       <c r="L63" t="n">
-        <v>73.12</v>
+        <v>71.62</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>29</v>
       </c>
       <c r="J64" t="n">
-        <v>28.66</v>
+        <v>25.48</v>
       </c>
       <c r="K64" t="n">
-        <v>-47.14</v>
+        <v>-41.9</v>
       </c>
       <c r="L64" t="n">
-        <v>55.17</v>
+        <v>49.04</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>29</v>
       </c>
       <c r="J65" t="n">
-        <v>-53.98</v>
+        <v>-47.98</v>
       </c>
       <c r="K65" t="n">
-        <v>-53.24</v>
+        <v>-47.32</v>
       </c>
       <c r="L65" t="n">
-        <v>75.81999999999999</v>
+        <v>67.39</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>113.01</v>
+        <v>110.71</v>
       </c>
       <c r="K66" t="n">
-        <v>-12.01</v>
+        <v>-11.77</v>
       </c>
       <c r="L66" t="n">
-        <v>113.65</v>
+        <v>111.33</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>26</v>
       </c>
       <c r="J67" t="n">
-        <v>-67.13</v>
+        <v>-64.34</v>
       </c>
       <c r="K67" t="n">
-        <v>42.37</v>
+        <v>40.61</v>
       </c>
       <c r="L67" t="n">
-        <v>79.39</v>
+        <v>76.08</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>28</v>
       </c>
       <c r="J68" t="n">
-        <v>57.64</v>
+        <v>52.62</v>
       </c>
       <c r="K68" t="n">
-        <v>43.56</v>
+        <v>39.77</v>
       </c>
       <c r="L68" t="n">
-        <v>72.23999999999999</v>
+        <v>65.95999999999999</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>30</v>
       </c>
       <c r="J69" t="n">
-        <v>9</v>
+        <v>7.77</v>
       </c>
       <c r="K69" t="n">
-        <v>-90.62</v>
+        <v>-78.26000000000001</v>
       </c>
       <c r="L69" t="n">
-        <v>91.06999999999999</v>
+        <v>78.65000000000001</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>66.7</v>
+        <v>65.34</v>
       </c>
       <c r="K70" t="n">
-        <v>-102.27</v>
+        <v>-100.18</v>
       </c>
       <c r="L70" t="n">
-        <v>122.1</v>
+        <v>119.61</v>
       </c>
     </row>
     <row r="71">
@@ -3076,13 +3076,13 @@
         <v>29</v>
       </c>
       <c r="J72" t="n">
-        <v>130.48</v>
+        <v>115.98</v>
       </c>
       <c r="K72" t="n">
-        <v>33.98</v>
+        <v>30.21</v>
       </c>
       <c r="L72" t="n">
-        <v>134.83</v>
+        <v>119.85</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>-51.47</v>
+        <v>-49.33</v>
       </c>
       <c r="K73" t="n">
-        <v>175.95</v>
+        <v>168.62</v>
       </c>
       <c r="L73" t="n">
-        <v>183.32</v>
+        <v>175.68</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>29</v>
       </c>
       <c r="J74" t="n">
-        <v>17.1</v>
+        <v>15.2</v>
       </c>
       <c r="K74" t="n">
-        <v>-53.65</v>
+        <v>-47.69</v>
       </c>
       <c r="L74" t="n">
-        <v>56.31</v>
+        <v>50.05</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>30</v>
       </c>
       <c r="J75" t="n">
-        <v>-31.34</v>
+        <v>-27.06</v>
       </c>
       <c r="K75" t="n">
-        <v>9.51</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="L75" t="n">
-        <v>32.75</v>
+        <v>28.28</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>29</v>
       </c>
       <c r="J76" t="n">
-        <v>43.31</v>
+        <v>38.5</v>
       </c>
       <c r="K76" t="n">
-        <v>46.34</v>
+        <v>41.2</v>
       </c>
       <c r="L76" t="n">
-        <v>63.43</v>
+        <v>56.39</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>29</v>
       </c>
       <c r="J77" t="n">
-        <v>13.6</v>
+        <v>12.09</v>
       </c>
       <c r="K77" t="n">
-        <v>69.18000000000001</v>
+        <v>61.5</v>
       </c>
       <c r="L77" t="n">
-        <v>70.51000000000001</v>
+        <v>62.67</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>16.77</v>
+        <v>16.07</v>
       </c>
       <c r="K78" t="n">
-        <v>-64.31</v>
+        <v>-61.63</v>
       </c>
       <c r="L78" t="n">
-        <v>66.45999999999999</v>
+        <v>63.7</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>30</v>
       </c>
       <c r="J79" t="n">
-        <v>-23.2</v>
+        <v>-20.04</v>
       </c>
       <c r="K79" t="n">
-        <v>-67.01000000000001</v>
+        <v>-57.87</v>
       </c>
       <c r="L79" t="n">
-        <v>70.91</v>
+        <v>61.24</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>-90.03</v>
+        <v>-86.27</v>
       </c>
       <c r="K80" t="n">
-        <v>29.06</v>
+        <v>27.85</v>
       </c>
       <c r="L80" t="n">
-        <v>94.59999999999999</v>
+        <v>90.66</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>29</v>
       </c>
       <c r="J81" t="n">
-        <v>31.79</v>
+        <v>28.26</v>
       </c>
       <c r="K81" t="n">
-        <v>77.31</v>
+        <v>68.72</v>
       </c>
       <c r="L81" t="n">
-        <v>83.59</v>
+        <v>74.3</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>67.06999999999999</v>
+        <v>61.24</v>
       </c>
       <c r="K82" t="n">
-        <v>18.86</v>
+        <v>17.22</v>
       </c>
       <c r="L82" t="n">
-        <v>69.67</v>
+        <v>63.61</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>28</v>
       </c>
       <c r="J83" t="n">
-        <v>34.65</v>
+        <v>31.64</v>
       </c>
       <c r="K83" t="n">
-        <v>76.84999999999999</v>
+        <v>70.16</v>
       </c>
       <c r="L83" t="n">
-        <v>84.3</v>
+        <v>76.97</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>30</v>
       </c>
       <c r="J84" t="n">
-        <v>72.28</v>
+        <v>62.42</v>
       </c>
       <c r="K84" t="n">
-        <v>-99.45999999999999</v>
+        <v>-85.90000000000001</v>
       </c>
       <c r="L84" t="n">
-        <v>122.95</v>
+        <v>106.18</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>28</v>
       </c>
       <c r="J85" t="n">
-        <v>-57.75</v>
+        <v>-52.73</v>
       </c>
       <c r="K85" t="n">
-        <v>-81.68000000000001</v>
+        <v>-74.56999999999999</v>
       </c>
       <c r="L85" t="n">
-        <v>100.03</v>
+        <v>91.33</v>
       </c>
     </row>
     <row r="86">
@@ -3706,13 +3706,13 @@
         <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>-134.62</v>
+        <v>-131.87</v>
       </c>
       <c r="K87" t="n">
-        <v>-19.42</v>
+        <v>-19.02</v>
       </c>
       <c r="L87" t="n">
-        <v>136.01</v>
+        <v>133.23</v>
       </c>
     </row>
     <row r="88">

--- a/output/2024-08-25.xlsx
+++ b/output/2024-08-25.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="F14" t="n">
-        <v>1.65</v>
+        <v>4.92</v>
       </c>
       <c r="G14" t="n">
-        <v>240.2</v>
+        <v>232.3</v>
       </c>
       <c r="H14" t="n">
-        <v>11.6</v>
+        <v>28.9</v>
       </c>
       <c r="I14" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>-11.81</v>
+        <v>28.33</v>
       </c>
       <c r="K14" t="n">
-        <v>-19.97</v>
+        <v>-13.22</v>
       </c>
       <c r="L14" t="n">
-        <v>23.2</v>
+        <v>31.26</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:07:16</t>
+          <t>06:07:41</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="F15" t="n">
-        <v>4.6</v>
+        <v>6.21</v>
       </c>
       <c r="G15" t="n">
-        <v>231.6</v>
+        <v>243.5</v>
       </c>
       <c r="H15" t="n">
-        <v>13.5</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>30.82</v>
+        <v>29.96</v>
       </c>
       <c r="K15" t="n">
-        <v>8.140000000000001</v>
+        <v>18.26</v>
       </c>
       <c r="L15" t="n">
-        <v>31.88</v>
+        <v>35.09</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:08:35</t>
+          <t>06:09:14</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.64</v>
+        <v>1.48</v>
       </c>
       <c r="F16" t="n">
-        <v>5.41</v>
+        <v>1.78</v>
       </c>
       <c r="G16" t="n">
-        <v>241.1</v>
+        <v>231.7</v>
       </c>
       <c r="H16" t="n">
-        <v>12.6</v>
+        <v>46.8</v>
       </c>
       <c r="I16" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.66</v>
+        <v>30.86</v>
       </c>
       <c r="K16" t="n">
-        <v>-31.72</v>
+        <v>-4.35</v>
       </c>
       <c r="L16" t="n">
-        <v>31.73</v>
+        <v>31.17</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:14:26</t>
+          <t>06:12:36</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="F17" t="n">
-        <v>5.88</v>
+        <v>6.21</v>
       </c>
       <c r="G17" t="n">
-        <v>230.9</v>
+        <v>224.4</v>
       </c>
       <c r="H17" t="n">
-        <v>14</v>
+        <v>45.1</v>
       </c>
       <c r="I17" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>-55.46</v>
+        <v>42.47</v>
       </c>
       <c r="K17" t="n">
-        <v>-30.28</v>
+        <v>-18.15</v>
       </c>
       <c r="L17" t="n">
-        <v>63.19</v>
+        <v>46.18</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:16:11</t>
+          <t>06:14:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.27</v>
+        <v>1.66</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1</v>
+        <v>5.93</v>
       </c>
       <c r="G18" t="n">
-        <v>219.8</v>
+        <v>218.7</v>
       </c>
       <c r="H18" t="n">
-        <v>11.5</v>
+        <v>55.7</v>
       </c>
       <c r="I18" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>-37.02</v>
+        <v>-22.69</v>
       </c>
       <c r="K18" t="n">
-        <v>23.73</v>
+        <v>-39.07</v>
       </c>
       <c r="L18" t="n">
-        <v>43.97</v>
+        <v>45.18</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:18:44</t>
+          <t>06:16:22</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="F19" t="n">
-        <v>4.27</v>
+        <v>2.87</v>
       </c>
       <c r="G19" t="n">
-        <v>223.3</v>
+        <v>229.2</v>
       </c>
       <c r="H19" t="n">
-        <v>11.7</v>
+        <v>36.9</v>
       </c>
       <c r="I19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J19" t="n">
-        <v>36.65</v>
+        <v>29.06</v>
       </c>
       <c r="K19" t="n">
-        <v>18.29</v>
+        <v>100.36</v>
       </c>
       <c r="L19" t="n">
-        <v>40.96</v>
+        <v>104.48</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:23:02</t>
+          <t>06:21:13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.74</v>
+        <v>1.59</v>
       </c>
       <c r="F20" t="n">
-        <v>4.11</v>
+        <v>3.52</v>
       </c>
       <c r="G20" t="n">
-        <v>230.7</v>
+        <v>213</v>
       </c>
       <c r="H20" t="n">
-        <v>17.7</v>
+        <v>31.8</v>
       </c>
       <c r="I20" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J20" t="n">
-        <v>88.62</v>
+        <v>59.78</v>
       </c>
       <c r="K20" t="n">
-        <v>25.62</v>
+        <v>-62</v>
       </c>
       <c r="L20" t="n">
-        <v>92.25</v>
+        <v>86.13</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:24:23</t>
+          <t>06:23:51</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1.49</v>
+        <v>1.76</v>
       </c>
       <c r="F21" t="n">
-        <v>6.21</v>
+        <v>5.3</v>
       </c>
       <c r="G21" t="n">
-        <v>234.8</v>
+        <v>221.6</v>
       </c>
       <c r="H21" t="n">
-        <v>13.6</v>
+        <v>59.4</v>
       </c>
       <c r="I21" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J21" t="n">
-        <v>40</v>
+        <v>-52.99</v>
       </c>
       <c r="K21" t="n">
-        <v>70.01000000000001</v>
+        <v>78.55</v>
       </c>
       <c r="L21" t="n">
-        <v>80.63</v>
+        <v>94.75</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:26:32</t>
+          <t>06:25:22</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="F22" t="n">
-        <v>3.49</v>
+        <v>4.52</v>
       </c>
       <c r="G22" t="n">
-        <v>219.5</v>
+        <v>217.7</v>
       </c>
       <c r="H22" t="n">
-        <v>20.7</v>
+        <v>20.3</v>
       </c>
       <c r="I22" t="n">
         <v>30</v>
       </c>
       <c r="J22" t="n">
-        <v>-65.5</v>
+        <v>-67.04000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>-8.17</v>
+        <v>46.66</v>
       </c>
       <c r="L22" t="n">
-        <v>66.01000000000001</v>
+        <v>81.67</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:31:24</t>
+          <t>06:30:20</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="F23" t="n">
-        <v>5.07</v>
+        <v>3.08</v>
       </c>
       <c r="G23" t="n">
-        <v>240.5</v>
+        <v>239.6</v>
       </c>
       <c r="H23" t="n">
-        <v>13.4</v>
+        <v>36.2</v>
       </c>
       <c r="I23" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J23" t="n">
-        <v>-75.77</v>
+        <v>103.75</v>
       </c>
       <c r="K23" t="n">
-        <v>60.54</v>
+        <v>-0.68</v>
       </c>
       <c r="L23" t="n">
-        <v>96.98</v>
+        <v>103.75</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:33:08</t>
+          <t>06:32:50</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.3</v>
+        <v>1.53</v>
       </c>
       <c r="F24" t="n">
-        <v>5.51</v>
+        <v>6.21</v>
       </c>
       <c r="G24" t="n">
-        <v>224.3</v>
+        <v>230.7</v>
       </c>
       <c r="H24" t="n">
-        <v>11.4</v>
+        <v>22</v>
       </c>
       <c r="I24" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J24" t="n">
-        <v>62.38</v>
+        <v>123.39</v>
       </c>
       <c r="K24" t="n">
-        <v>-99.68000000000001</v>
+        <v>30.88</v>
       </c>
       <c r="L24" t="n">
-        <v>117.59</v>
+        <v>127.19</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:34:50</t>
+          <t>06:34:28</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>1.34</v>
+        <v>1.81</v>
       </c>
       <c r="F25" t="n">
-        <v>6.21</v>
+        <v>5.79</v>
       </c>
       <c r="G25" t="n">
-        <v>216.5</v>
+        <v>233.4</v>
       </c>
       <c r="H25" t="n">
-        <v>12.2</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J25" t="n">
-        <v>102.89</v>
+        <v>-29.37</v>
       </c>
       <c r="K25" t="n">
-        <v>18.47</v>
+        <v>126.74</v>
       </c>
       <c r="L25" t="n">
-        <v>104.53</v>
+        <v>130.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:39:14</t>
+          <t>06:39:57</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="F26" t="n">
-        <v>4.08</v>
+        <v>6.21</v>
       </c>
       <c r="G26" t="n">
-        <v>221.5</v>
+        <v>216.1</v>
       </c>
       <c r="H26" t="n">
-        <v>14.1</v>
+        <v>39.7</v>
       </c>
       <c r="I26" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J26" t="n">
-        <v>86.33</v>
+        <v>-136.76</v>
       </c>
       <c r="K26" t="n">
-        <v>-82.89</v>
+        <v>-38.35</v>
       </c>
       <c r="L26" t="n">
-        <v>119.69</v>
+        <v>142.03</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:41:06</t>
+          <t>06:42:20</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.68</v>
+        <v>1.49</v>
       </c>
       <c r="F27" t="n">
-        <v>6.21</v>
+        <v>5.16</v>
       </c>
       <c r="G27" t="n">
-        <v>235.6</v>
+        <v>223.5</v>
       </c>
       <c r="H27" t="n">
-        <v>9.1</v>
+        <v>52.3</v>
       </c>
       <c r="I27" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>-164.68</v>
+        <v>177.65</v>
       </c>
       <c r="K27" t="n">
-        <v>-100.27</v>
+        <v>-26.76</v>
       </c>
       <c r="L27" t="n">
-        <v>192.8</v>
+        <v>179.65</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:43:25</t>
+          <t>06:44:44</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>1.46</v>
+        <v>1.63</v>
       </c>
       <c r="F28" t="n">
-        <v>3.82</v>
+        <v>6.04</v>
       </c>
       <c r="G28" t="n">
-        <v>236.1</v>
+        <v>220.8</v>
       </c>
       <c r="H28" t="n">
-        <v>12.7</v>
+        <v>29.8</v>
       </c>
       <c r="I28" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>-116.01</v>
+        <v>-54.75</v>
       </c>
       <c r="K28" t="n">
-        <v>54.78</v>
+        <v>119.83</v>
       </c>
       <c r="L28" t="n">
-        <v>128.3</v>
+        <v>131.75</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:54:50</t>
+          <t>06:53:23</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="F29" t="n">
-        <v>6.21</v>
+        <v>6.06</v>
       </c>
       <c r="G29" t="n">
-        <v>221.3</v>
+        <v>235.3</v>
       </c>
       <c r="H29" t="n">
-        <v>13.3</v>
+        <v>66.5</v>
       </c>
       <c r="I29" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J29" t="n">
-        <v>45.39</v>
+        <v>-9.98</v>
       </c>
       <c r="K29" t="n">
-        <v>-23.96</v>
+        <v>28.97</v>
       </c>
       <c r="L29" t="n">
-        <v>51.33</v>
+        <v>30.64</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06:55:50</t>
+          <t>06:54:33</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>1.59</v>
+        <v>1.71</v>
       </c>
       <c r="F30" t="n">
-        <v>5.18</v>
+        <v>2.01</v>
       </c>
       <c r="G30" t="n">
-        <v>232.9</v>
+        <v>243.5</v>
       </c>
       <c r="H30" t="n">
-        <v>6.5</v>
+        <v>51.1</v>
       </c>
       <c r="I30" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J30" t="n">
-        <v>-27.76</v>
+        <v>-13.54</v>
       </c>
       <c r="K30" t="n">
-        <v>-37.54</v>
+        <v>27.17</v>
       </c>
       <c r="L30" t="n">
-        <v>46.69</v>
+        <v>30.35</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06:57:49</t>
+          <t>06:55:21</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>1.79</v>
+        <v>1.64</v>
       </c>
       <c r="F31" t="n">
-        <v>6.21</v>
+        <v>3.9</v>
       </c>
       <c r="G31" t="n">
-        <v>231.8</v>
+        <v>224.5</v>
       </c>
       <c r="H31" t="n">
-        <v>14.1</v>
+        <v>51.1</v>
       </c>
       <c r="I31" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J31" t="n">
-        <v>4.64</v>
+        <v>-22.42</v>
       </c>
       <c r="K31" t="n">
-        <v>-29.95</v>
+        <v>-9.07</v>
       </c>
       <c r="L31" t="n">
-        <v>30.31</v>
+        <v>24.19</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:02:05</t>
+          <t>07:00:03</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="F32" t="n">
-        <v>4.27</v>
+        <v>2.78</v>
       </c>
       <c r="G32" t="n">
-        <v>238.2</v>
+        <v>232.2</v>
       </c>
       <c r="H32" t="n">
-        <v>15.2</v>
+        <v>29.6</v>
       </c>
       <c r="I32" t="n">
         <v>26</v>
       </c>
       <c r="J32" t="n">
-        <v>-25.71</v>
+        <v>-47.48</v>
       </c>
       <c r="K32" t="n">
-        <v>-67.23</v>
+        <v>2.45</v>
       </c>
       <c r="L32" t="n">
-        <v>71.98</v>
+        <v>47.54</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:03:39</t>
+          <t>07:01:41</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="F33" t="n">
-        <v>3.16</v>
+        <v>3.99</v>
       </c>
       <c r="G33" t="n">
-        <v>244.3</v>
+        <v>248.4</v>
       </c>
       <c r="H33" t="n">
-        <v>13.8</v>
+        <v>50.3</v>
       </c>
       <c r="I33" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J33" t="n">
-        <v>62.91</v>
+        <v>-35.66</v>
       </c>
       <c r="K33" t="n">
-        <v>23.45</v>
+        <v>18.4</v>
       </c>
       <c r="L33" t="n">
-        <v>67.13</v>
+        <v>40.12</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:06:00</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="F34" t="n">
-        <v>3.54</v>
+        <v>4.82</v>
       </c>
       <c r="G34" t="n">
-        <v>229.3</v>
+        <v>222.1</v>
       </c>
       <c r="H34" t="n">
-        <v>11.7</v>
+        <v>31</v>
       </c>
       <c r="I34" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J34" t="n">
-        <v>-48.88</v>
+        <v>56.35</v>
       </c>
       <c r="K34" t="n">
-        <v>18.31</v>
+        <v>12.59</v>
       </c>
       <c r="L34" t="n">
-        <v>52.19</v>
+        <v>57.74</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:11:15</t>
+          <t>07:09:32</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="F35" t="n">
-        <v>2.33</v>
+        <v>4.05</v>
       </c>
       <c r="G35" t="n">
-        <v>227.6</v>
+        <v>237.7</v>
       </c>
       <c r="H35" t="n">
-        <v>9.5</v>
+        <v>49.1</v>
       </c>
       <c r="I35" t="n">
         <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>38.74</v>
+        <v>-61.52</v>
       </c>
       <c r="K35" t="n">
-        <v>-54.76</v>
+        <v>45.34</v>
       </c>
       <c r="L35" t="n">
-        <v>67.08</v>
+        <v>76.42</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:13:40</t>
+          <t>07:11:06</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="F36" t="n">
-        <v>5.66</v>
+        <v>4.18</v>
       </c>
       <c r="G36" t="n">
-        <v>232.2</v>
+        <v>232.6</v>
       </c>
       <c r="H36" t="n">
-        <v>17.1</v>
+        <v>46.1</v>
       </c>
       <c r="I36" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>90.22</v>
+        <v>-20.13</v>
       </c>
       <c r="K36" t="n">
-        <v>-29.08</v>
+        <v>-64.09</v>
       </c>
       <c r="L36" t="n">
-        <v>94.79000000000001</v>
+        <v>67.18000000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:14:54</t>
+          <t>07:11:36</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>1.87</v>
+        <v>1.58</v>
       </c>
       <c r="F37" t="n">
-        <v>6.21</v>
+        <v>5.69</v>
       </c>
       <c r="G37" t="n">
-        <v>221.7</v>
+        <v>212.1</v>
       </c>
       <c r="H37" t="n">
-        <v>5.6</v>
+        <v>25.1</v>
       </c>
       <c r="I37" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J37" t="n">
-        <v>-83.45</v>
+        <v>-15.74</v>
       </c>
       <c r="K37" t="n">
-        <v>35.62</v>
+        <v>-16.9</v>
       </c>
       <c r="L37" t="n">
-        <v>90.73</v>
+        <v>23.09</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:19:35</t>
+          <t>07:16:20</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1.98</v>
+        <v>1.66</v>
       </c>
       <c r="F38" t="n">
-        <v>6.21</v>
+        <v>5.3</v>
       </c>
       <c r="G38" t="n">
-        <v>231.1</v>
+        <v>231.9</v>
       </c>
       <c r="H38" t="n">
-        <v>19.4</v>
+        <v>58.7</v>
       </c>
       <c r="I38" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J38" t="n">
-        <v>-55.35</v>
+        <v>-46.25</v>
       </c>
       <c r="K38" t="n">
-        <v>55.57</v>
+        <v>112.91</v>
       </c>
       <c r="L38" t="n">
-        <v>78.43000000000001</v>
+        <v>122.01</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:21:28</t>
+          <t>07:18:06</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="F39" t="n">
-        <v>6.21</v>
+        <v>3.62</v>
       </c>
       <c r="G39" t="n">
-        <v>236.6</v>
+        <v>229.5</v>
       </c>
       <c r="H39" t="n">
-        <v>7.1</v>
+        <v>55.2</v>
       </c>
       <c r="I39" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>55.76</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="K39" t="n">
-        <v>78.45999999999999</v>
+        <v>-104.42</v>
       </c>
       <c r="L39" t="n">
-        <v>96.25</v>
+        <v>131.1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:22:28</t>
+          <t>07:20:18</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>1.43</v>
+        <v>2.31</v>
       </c>
       <c r="F40" t="n">
         <v>6.21</v>
       </c>
       <c r="G40" t="n">
-        <v>219.6</v>
+        <v>233.8</v>
       </c>
       <c r="H40" t="n">
-        <v>13.2</v>
+        <v>60.4</v>
       </c>
       <c r="I40" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>-64.65000000000001</v>
+        <v>99.76000000000001</v>
       </c>
       <c r="K40" t="n">
-        <v>-151.65</v>
+        <v>102.23</v>
       </c>
       <c r="L40" t="n">
-        <v>164.85</v>
+        <v>142.84</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:26:46</t>
+          <t>07:25:12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="F41" t="n">
-        <v>6.1</v>
+        <v>5.04</v>
       </c>
       <c r="G41" t="n">
-        <v>230.9</v>
+        <v>227.2</v>
       </c>
       <c r="H41" t="n">
-        <v>16.3</v>
+        <v>8.1</v>
       </c>
       <c r="I41" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>46.38</v>
+        <v>43.04</v>
       </c>
       <c r="K41" t="n">
-        <v>-117.16</v>
+        <v>-111.52</v>
       </c>
       <c r="L41" t="n">
-        <v>126.01</v>
+        <v>119.54</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:28:40</t>
+          <t>07:27:15</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.88</v>
+        <v>1.54</v>
       </c>
       <c r="F42" t="n">
-        <v>6.21</v>
+        <v>5.09</v>
       </c>
       <c r="G42" t="n">
-        <v>223.1</v>
+        <v>244.2</v>
       </c>
       <c r="H42" t="n">
-        <v>10.7</v>
+        <v>54.4</v>
       </c>
       <c r="I42" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>-80.31999999999999</v>
+        <v>-155.46</v>
       </c>
       <c r="K42" t="n">
-        <v>163.45</v>
+        <v>25.79</v>
       </c>
       <c r="L42" t="n">
-        <v>182.12</v>
+        <v>157.58</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:31:04</t>
+          <t>07:28:25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="F43" t="n">
-        <v>3.54</v>
+        <v>3.82</v>
       </c>
       <c r="G43" t="n">
-        <v>227.6</v>
+        <v>230.3</v>
       </c>
       <c r="H43" t="n">
-        <v>12.8</v>
+        <v>40.4</v>
       </c>
       <c r="I43" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>-75.84</v>
+        <v>-80.09999999999999</v>
       </c>
       <c r="K43" t="n">
-        <v>-166.22</v>
+        <v>-117.82</v>
       </c>
       <c r="L43" t="n">
-        <v>182.71</v>
+        <v>142.47</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:41:54</t>
+          <t>07:37:15</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1.51</v>
+        <v>1.72</v>
       </c>
       <c r="F44" t="n">
-        <v>4.37</v>
+        <v>6.21</v>
       </c>
       <c r="G44" t="n">
-        <v>237.5</v>
+        <v>212.7</v>
       </c>
       <c r="H44" t="n">
-        <v>7.3</v>
+        <v>40.8</v>
       </c>
       <c r="I44" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J44" t="n">
-        <v>21.96</v>
+        <v>14.95</v>
       </c>
       <c r="K44" t="n">
-        <v>24.11</v>
+        <v>-30.1</v>
       </c>
       <c r="L44" t="n">
-        <v>32.61</v>
+        <v>33.6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:43:10</t>
+          <t>07:39:29</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="F45" t="n">
-        <v>6.21</v>
+        <v>5.42</v>
       </c>
       <c r="G45" t="n">
-        <v>233.5</v>
+        <v>229.3</v>
       </c>
       <c r="H45" t="n">
-        <v>16.4</v>
+        <v>16.8</v>
       </c>
       <c r="I45" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J45" t="n">
-        <v>-1.15</v>
+        <v>-23.52</v>
       </c>
       <c r="K45" t="n">
-        <v>-37.16</v>
+        <v>-13.42</v>
       </c>
       <c r="L45" t="n">
-        <v>37.18</v>
+        <v>27.07</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:45:11</t>
+          <t>07:40:44</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>1.88</v>
+        <v>1.6</v>
       </c>
       <c r="F46" t="n">
-        <v>4.22</v>
+        <v>6.21</v>
       </c>
       <c r="G46" t="n">
-        <v>231.4</v>
+        <v>224.2</v>
       </c>
       <c r="H46" t="n">
-        <v>13.3</v>
+        <v>21.7</v>
       </c>
       <c r="I46" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J46" t="n">
-        <v>-36.44</v>
+        <v>28.35</v>
       </c>
       <c r="K46" t="n">
-        <v>-47.84</v>
+        <v>-20.31</v>
       </c>
       <c r="L46" t="n">
-        <v>60.13</v>
+        <v>34.88</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:50:31</t>
+          <t>07:44:02</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>1.68</v>
+        <v>1.32</v>
       </c>
       <c r="F47" t="n">
-        <v>5.74</v>
+        <v>3.15</v>
       </c>
       <c r="G47" t="n">
-        <v>224.4</v>
+        <v>216.7</v>
       </c>
       <c r="H47" t="n">
-        <v>18.4</v>
+        <v>60.2</v>
       </c>
       <c r="I47" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J47" t="n">
-        <v>24.7</v>
+        <v>32.45</v>
       </c>
       <c r="K47" t="n">
-        <v>-47.87</v>
+        <v>-31.77</v>
       </c>
       <c r="L47" t="n">
-        <v>53.86</v>
+        <v>45.41</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:51:38</t>
+          <t>07:45:38</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="F48" t="n">
-        <v>4.75</v>
+        <v>5.44</v>
       </c>
       <c r="G48" t="n">
-        <v>228.3</v>
+        <v>230.2</v>
       </c>
       <c r="H48" t="n">
-        <v>14.1</v>
+        <v>53.8</v>
       </c>
       <c r="I48" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J48" t="n">
-        <v>-42.13</v>
+        <v>-56.95</v>
       </c>
       <c r="K48" t="n">
-        <v>21</v>
+        <v>-11.96</v>
       </c>
       <c r="L48" t="n">
-        <v>47.08</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:52:57</t>
+          <t>07:47:00</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="F49" t="n">
-        <v>5.42</v>
+        <v>5.24</v>
       </c>
       <c r="G49" t="n">
-        <v>234.1</v>
+        <v>220.9</v>
       </c>
       <c r="H49" t="n">
-        <v>16.7</v>
+        <v>41.3</v>
       </c>
       <c r="I49" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>11</v>
+        <v>-65.36</v>
       </c>
       <c r="K49" t="n">
-        <v>-47.91</v>
+        <v>6.96</v>
       </c>
       <c r="L49" t="n">
-        <v>49.15</v>
+        <v>65.73</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07:57:19</t>
+          <t>07:52:00</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>1.41</v>
+        <v>1.72</v>
       </c>
       <c r="F50" t="n">
-        <v>4.48</v>
+        <v>6.12</v>
       </c>
       <c r="G50" t="n">
-        <v>230.6</v>
+        <v>239</v>
       </c>
       <c r="H50" t="n">
-        <v>15.6</v>
+        <v>79.2</v>
       </c>
       <c r="I50" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J50" t="n">
-        <v>-66.69</v>
+        <v>-79.48999999999999</v>
       </c>
       <c r="K50" t="n">
-        <v>-27.47</v>
+        <v>32.01</v>
       </c>
       <c r="L50" t="n">
-        <v>72.13</v>
+        <v>85.69</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07:59:39</t>
+          <t>07:54:34</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>1.97</v>
+        <v>1.71</v>
       </c>
       <c r="F51" t="n">
-        <v>5.53</v>
+        <v>6.21</v>
       </c>
       <c r="G51" t="n">
-        <v>225.9</v>
+        <v>229.9</v>
       </c>
       <c r="H51" t="n">
-        <v>12.7</v>
+        <v>36.5</v>
       </c>
       <c r="I51" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J51" t="n">
-        <v>-83.58</v>
+        <v>-18.54</v>
       </c>
       <c r="K51" t="n">
-        <v>14.69</v>
+        <v>56.69</v>
       </c>
       <c r="L51" t="n">
-        <v>84.86</v>
+        <v>59.64</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:01:46</t>
+          <t>07:56:11</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>1.76</v>
+        <v>1.93</v>
       </c>
       <c r="F52" t="n">
-        <v>6.21</v>
+        <v>4.11</v>
       </c>
       <c r="G52" t="n">
-        <v>235</v>
+        <v>238.4</v>
       </c>
       <c r="H52" t="n">
-        <v>23.2</v>
+        <v>36.6</v>
       </c>
       <c r="I52" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J52" t="n">
-        <v>-38.92</v>
+        <v>1.2</v>
       </c>
       <c r="K52" t="n">
-        <v>25.34</v>
+        <v>102.76</v>
       </c>
       <c r="L52" t="n">
-        <v>46.44</v>
+        <v>102.77</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:05:41</t>
+          <t>08:01:00</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="F53" t="n">
-        <v>1.91</v>
+        <v>5.68</v>
       </c>
       <c r="G53" t="n">
-        <v>228.5</v>
+        <v>233.4</v>
       </c>
       <c r="H53" t="n">
-        <v>11.6</v>
+        <v>33.6</v>
       </c>
       <c r="I53" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>-84.86</v>
+        <v>-25.57</v>
       </c>
       <c r="K53" t="n">
-        <v>9.880000000000001</v>
+        <v>-98.81</v>
       </c>
       <c r="L53" t="n">
-        <v>85.43000000000001</v>
+        <v>102.07</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:07:11</t>
+          <t>08:03:03</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.11</v>
+        <v>1.63</v>
       </c>
       <c r="F54" t="n">
-        <v>6.21</v>
+        <v>2.92</v>
       </c>
       <c r="G54" t="n">
-        <v>225.2</v>
+        <v>220.4</v>
       </c>
       <c r="H54" t="n">
-        <v>12.7</v>
+        <v>66</v>
       </c>
       <c r="I54" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J54" t="n">
-        <v>-46.42</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="K54" t="n">
-        <v>-107.58</v>
+        <v>138.9</v>
       </c>
       <c r="L54" t="n">
-        <v>117.17</v>
+        <v>153.68</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:08:10</t>
+          <t>08:05:01</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="F55" t="n">
         <v>6.21</v>
       </c>
       <c r="G55" t="n">
-        <v>227.7</v>
+        <v>231.8</v>
       </c>
       <c r="H55" t="n">
-        <v>20</v>
+        <v>40.2</v>
       </c>
       <c r="I55" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J55" t="n">
-        <v>-103.94</v>
+        <v>-89.29000000000001</v>
       </c>
       <c r="K55" t="n">
-        <v>134.33</v>
+        <v>51.88</v>
       </c>
       <c r="L55" t="n">
-        <v>169.85</v>
+        <v>103.26</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:13:31</t>
+          <t>08:09:18</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>1.82</v>
+        <v>1.52</v>
       </c>
       <c r="F56" t="n">
-        <v>6.21</v>
+        <v>4.25</v>
       </c>
       <c r="G56" t="n">
-        <v>218.6</v>
+        <v>229.3</v>
       </c>
       <c r="H56" t="n">
-        <v>18.9</v>
+        <v>100</v>
       </c>
       <c r="I56" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J56" t="n">
-        <v>-37.18</v>
+        <v>76</v>
       </c>
       <c r="K56" t="n">
-        <v>-157.02</v>
+        <v>-97.56</v>
       </c>
       <c r="L56" t="n">
-        <v>161.36</v>
+        <v>123.67</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:14:54</t>
+          <t>08:11:07</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>1.69</v>
+        <v>2.02</v>
       </c>
       <c r="F57" t="n">
-        <v>2.89</v>
+        <v>6.21</v>
       </c>
       <c r="G57" t="n">
-        <v>232.6</v>
+        <v>231</v>
       </c>
       <c r="H57" t="n">
-        <v>18.2</v>
+        <v>36.8</v>
       </c>
       <c r="I57" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J57" t="n">
-        <v>-111.01</v>
+        <v>-190.74</v>
       </c>
       <c r="K57" t="n">
-        <v>86.01000000000001</v>
+        <v>10.16</v>
       </c>
       <c r="L57" t="n">
-        <v>140.43</v>
+        <v>191.01</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:16:31</t>
+          <t>08:13:07</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>1.51</v>
+        <v>1.66</v>
       </c>
       <c r="F58" t="n">
-        <v>5.01</v>
+        <v>6.21</v>
       </c>
       <c r="G58" t="n">
-        <v>224.7</v>
+        <v>215.8</v>
       </c>
       <c r="H58" t="n">
-        <v>18</v>
+        <v>18.7</v>
       </c>
       <c r="I58" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J58" t="n">
-        <v>-188.37</v>
+        <v>191.99</v>
       </c>
       <c r="K58" t="n">
-        <v>36.88</v>
+        <v>37.02</v>
       </c>
       <c r="L58" t="n">
-        <v>191.95</v>
+        <v>195.53</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:27:37</t>
+          <t>08:23:25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="F59" t="n">
-        <v>3.97</v>
+        <v>6.21</v>
       </c>
       <c r="G59" t="n">
-        <v>221.3</v>
+        <v>249.1</v>
       </c>
       <c r="H59" t="n">
-        <v>9.1</v>
+        <v>14.2</v>
       </c>
       <c r="I59" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J59" t="n">
-        <v>-7.23</v>
+        <v>-29.6</v>
       </c>
       <c r="K59" t="n">
-        <v>37.7</v>
+        <v>26.86</v>
       </c>
       <c r="L59" t="n">
-        <v>38.38</v>
+        <v>39.97</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:29:20</t>
+          <t>08:24:14</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="F60" t="n">
-        <v>6.21</v>
+        <v>6.07</v>
       </c>
       <c r="G60" t="n">
-        <v>238.6</v>
+        <v>226.2</v>
       </c>
       <c r="H60" t="n">
-        <v>18.7</v>
+        <v>43.3</v>
       </c>
       <c r="I60" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J60" t="n">
-        <v>-41.41</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="K60" t="n">
-        <v>30.38</v>
+        <v>-36.57</v>
       </c>
       <c r="L60" t="n">
-        <v>51.36</v>
+        <v>37.44</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:30:26</t>
+          <t>08:25:16</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>1.97</v>
+        <v>1.69</v>
       </c>
       <c r="F61" t="n">
         <v>6.21</v>
       </c>
       <c r="G61" t="n">
-        <v>230.6</v>
+        <v>223.2</v>
       </c>
       <c r="H61" t="n">
-        <v>16.5</v>
+        <v>81.2</v>
       </c>
       <c r="I61" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J61" t="n">
-        <v>3.6</v>
+        <v>22.11</v>
       </c>
       <c r="K61" t="n">
-        <v>-36.87</v>
+        <v>22.55</v>
       </c>
       <c r="L61" t="n">
-        <v>37.05</v>
+        <v>31.58</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:34:13</t>
+          <t>08:29:38</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="F62" t="n">
-        <v>2.28</v>
+        <v>6.21</v>
       </c>
       <c r="G62" t="n">
-        <v>229.1</v>
+        <v>237.4</v>
       </c>
       <c r="H62" t="n">
-        <v>14.1</v>
+        <v>27.5</v>
       </c>
       <c r="I62" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>36.27</v>
+        <v>41.09</v>
       </c>
       <c r="K62" t="n">
-        <v>38.26</v>
+        <v>-10.28</v>
       </c>
       <c r="L62" t="n">
-        <v>52.72</v>
+        <v>42.36</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:35:33</t>
+          <t>08:32:14</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="F63" t="n">
-        <v>3.8</v>
+        <v>3.69</v>
       </c>
       <c r="G63" t="n">
-        <v>241.8</v>
+        <v>228.3</v>
       </c>
       <c r="H63" t="n">
-        <v>19</v>
+        <v>51.9</v>
       </c>
       <c r="I63" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J63" t="n">
-        <v>-70.64</v>
+        <v>-17.2</v>
       </c>
       <c r="K63" t="n">
-        <v>11.85</v>
+        <v>-51.7</v>
       </c>
       <c r="L63" t="n">
-        <v>71.62</v>
+        <v>54.48</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:36:44</t>
+          <t>08:34:02</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="F64" t="n">
-        <v>6.21</v>
+        <v>3.49</v>
       </c>
       <c r="G64" t="n">
-        <v>224.7</v>
+        <v>230.7</v>
       </c>
       <c r="H64" t="n">
-        <v>17.1</v>
+        <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J64" t="n">
-        <v>25.48</v>
+        <v>-47.64</v>
       </c>
       <c r="K64" t="n">
-        <v>-41.9</v>
+        <v>-27.42</v>
       </c>
       <c r="L64" t="n">
-        <v>49.04</v>
+        <v>54.97</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:39:39</t>
+          <t>08:37:55</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="F65" t="n">
-        <v>6.21</v>
+        <v>3.32</v>
       </c>
       <c r="G65" t="n">
-        <v>222</v>
+        <v>229.3</v>
       </c>
       <c r="H65" t="n">
-        <v>12.7</v>
+        <v>33.9</v>
       </c>
       <c r="I65" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J65" t="n">
-        <v>-47.98</v>
+        <v>72.12</v>
       </c>
       <c r="K65" t="n">
-        <v>-47.32</v>
+        <v>29.41</v>
       </c>
       <c r="L65" t="n">
-        <v>67.39</v>
+        <v>77.89</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:40:36</t>
+          <t>08:39:37</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="F66" t="n">
-        <v>6.21</v>
+        <v>4.86</v>
       </c>
       <c r="G66" t="n">
-        <v>233.2</v>
+        <v>225.5</v>
       </c>
       <c r="H66" t="n">
-        <v>8.300000000000001</v>
+        <v>32.9</v>
       </c>
       <c r="I66" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>110.71</v>
+        <v>-69.52</v>
       </c>
       <c r="K66" t="n">
-        <v>-11.77</v>
+        <v>-18.09</v>
       </c>
       <c r="L66" t="n">
-        <v>111.33</v>
+        <v>71.83</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:42:00</t>
+          <t>08:41:14</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>1.27</v>
+        <v>1.8</v>
       </c>
       <c r="F67" t="n">
-        <v>2.54</v>
+        <v>5.48</v>
       </c>
       <c r="G67" t="n">
-        <v>224.1</v>
+        <v>234.9</v>
       </c>
       <c r="H67" t="n">
-        <v>12</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="I67" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J67" t="n">
-        <v>-64.34</v>
+        <v>0.27</v>
       </c>
       <c r="K67" t="n">
-        <v>40.61</v>
+        <v>-86.09</v>
       </c>
       <c r="L67" t="n">
-        <v>76.08</v>
+        <v>86.09</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:45:10</t>
+          <t>08:44:29</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.39</v>
+        <v>1.96</v>
       </c>
       <c r="F68" t="n">
-        <v>5.8</v>
+        <v>6.18</v>
       </c>
       <c r="G68" t="n">
-        <v>231.2</v>
+        <v>228.1</v>
       </c>
       <c r="H68" t="n">
-        <v>13.8</v>
+        <v>76.2</v>
       </c>
       <c r="I68" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J68" t="n">
-        <v>52.62</v>
+        <v>-53.24</v>
       </c>
       <c r="K68" t="n">
-        <v>39.77</v>
+        <v>-146.72</v>
       </c>
       <c r="L68" t="n">
-        <v>65.95999999999999</v>
+        <v>156.08</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:46:26</t>
+          <t>08:45:51</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="F69" t="n">
-        <v>4.84</v>
+        <v>3.2</v>
       </c>
       <c r="G69" t="n">
-        <v>245.2</v>
+        <v>225.1</v>
       </c>
       <c r="H69" t="n">
-        <v>15.2</v>
+        <v>30.2</v>
       </c>
       <c r="I69" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J69" t="n">
-        <v>7.77</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="K69" t="n">
-        <v>-78.26000000000001</v>
+        <v>75.66</v>
       </c>
       <c r="L69" t="n">
-        <v>78.65000000000001</v>
+        <v>116.13</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:47:32</t>
+          <t>08:47:49</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="F70" t="n">
-        <v>5.73</v>
+        <v>4.87</v>
       </c>
       <c r="G70" t="n">
-        <v>236.1</v>
+        <v>246.6</v>
       </c>
       <c r="H70" t="n">
-        <v>11.1</v>
+        <v>29.7</v>
       </c>
       <c r="I70" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J70" t="n">
-        <v>65.34</v>
+        <v>98.25</v>
       </c>
       <c r="K70" t="n">
-        <v>-100.18</v>
+        <v>28.12</v>
       </c>
       <c r="L70" t="n">
-        <v>119.61</v>
+        <v>102.19</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:52:20</t>
+          <t>08:51:51</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>1.93</v>
+        <v>1.77</v>
       </c>
       <c r="F71" t="n">
         <v>6.21</v>
       </c>
       <c r="G71" t="n">
-        <v>228.1</v>
+        <v>226.8</v>
       </c>
       <c r="H71" t="n">
-        <v>13.2</v>
+        <v>38.3</v>
       </c>
       <c r="I71" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J71" t="n">
-        <v>-107.21</v>
+        <v>124.42</v>
       </c>
       <c r="K71" t="n">
-        <v>116.68</v>
+        <v>-68.97</v>
       </c>
       <c r="L71" t="n">
-        <v>158.45</v>
+        <v>142.26</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:54:26</t>
+          <t>08:54:05</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="F72" t="n">
-        <v>3.32</v>
+        <v>6.21</v>
       </c>
       <c r="G72" t="n">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="H72" t="n">
-        <v>15.1</v>
+        <v>57.4</v>
       </c>
       <c r="I72" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J72" t="n">
-        <v>115.98</v>
+        <v>-98.58</v>
       </c>
       <c r="K72" t="n">
-        <v>30.21</v>
+        <v>-132</v>
       </c>
       <c r="L72" t="n">
-        <v>119.85</v>
+        <v>164.75</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08:55:30</t>
+          <t>08:55:34</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="F73" t="n">
-        <v>5.8</v>
+        <v>1.99</v>
       </c>
       <c r="G73" t="n">
-        <v>230</v>
+        <v>225.2</v>
       </c>
       <c r="H73" t="n">
-        <v>15.4</v>
+        <v>58.5</v>
       </c>
       <c r="I73" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J73" t="n">
-        <v>-49.33</v>
+        <v>-140.81</v>
       </c>
       <c r="K73" t="n">
-        <v>168.62</v>
+        <v>-82.56</v>
       </c>
       <c r="L73" t="n">
-        <v>175.68</v>
+        <v>163.23</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:09:05</t>
+          <t>09:07:24</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.02</v>
+        <v>1.64</v>
       </c>
       <c r="F74" t="n">
-        <v>6.21</v>
+        <v>4.97</v>
       </c>
       <c r="G74" t="n">
-        <v>243.2</v>
+        <v>220.7</v>
       </c>
       <c r="H74" t="n">
-        <v>7.8</v>
+        <v>64.2</v>
       </c>
       <c r="I74" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J74" t="n">
-        <v>15.2</v>
+        <v>31.36</v>
       </c>
       <c r="K74" t="n">
-        <v>-47.69</v>
+        <v>13.7</v>
       </c>
       <c r="L74" t="n">
-        <v>50.05</v>
+        <v>34.22</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:10:59</t>
+          <t>09:09:51</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="F75" t="n">
         <v>6.21</v>
       </c>
       <c r="G75" t="n">
-        <v>234.4</v>
+        <v>231.9</v>
       </c>
       <c r="H75" t="n">
-        <v>12.6</v>
+        <v>14.8</v>
       </c>
       <c r="I75" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J75" t="n">
-        <v>-27.06</v>
+        <v>-34.87</v>
       </c>
       <c r="K75" t="n">
-        <v>8.210000000000001</v>
+        <v>-4.31</v>
       </c>
       <c r="L75" t="n">
-        <v>28.28</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:13:22</t>
+          <t>09:11:56</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.02</v>
+        <v>1.79</v>
       </c>
       <c r="F76" t="n">
-        <v>6.21</v>
+        <v>2.09</v>
       </c>
       <c r="G76" t="n">
-        <v>241.4</v>
+        <v>232.1</v>
       </c>
       <c r="H76" t="n">
-        <v>13.8</v>
+        <v>27.8</v>
       </c>
       <c r="I76" t="n">
         <v>29</v>
       </c>
       <c r="J76" t="n">
-        <v>38.5</v>
+        <v>-15.75</v>
       </c>
       <c r="K76" t="n">
-        <v>41.2</v>
+        <v>30.42</v>
       </c>
       <c r="L76" t="n">
-        <v>56.39</v>
+        <v>34.26</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:16:46</t>
+          <t>09:17:20</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="F77" t="n">
-        <v>6.21</v>
+        <v>5.61</v>
       </c>
       <c r="G77" t="n">
-        <v>229</v>
+        <v>224.1</v>
       </c>
       <c r="H77" t="n">
-        <v>11.1</v>
+        <v>20.4</v>
       </c>
       <c r="I77" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>12.09</v>
+        <v>-55.01</v>
       </c>
       <c r="K77" t="n">
-        <v>61.5</v>
+        <v>13.36</v>
       </c>
       <c r="L77" t="n">
-        <v>62.67</v>
+        <v>56.61</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:18:36</t>
+          <t>09:19:17</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>1.81</v>
+        <v>1.58</v>
       </c>
       <c r="F78" t="n">
-        <v>6.21</v>
+        <v>2.37</v>
       </c>
       <c r="G78" t="n">
-        <v>224.9</v>
+        <v>235.8</v>
       </c>
       <c r="H78" t="n">
-        <v>8.6</v>
+        <v>55.6</v>
       </c>
       <c r="I78" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J78" t="n">
-        <v>16.07</v>
+        <v>-15.2</v>
       </c>
       <c r="K78" t="n">
-        <v>-61.63</v>
+        <v>-52.53</v>
       </c>
       <c r="L78" t="n">
-        <v>63.7</v>
+        <v>54.69</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:19:45</t>
+          <t>09:20:22</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="F79" t="n">
         <v>6.21</v>
       </c>
       <c r="G79" t="n">
-        <v>237.4</v>
+        <v>233.9</v>
       </c>
       <c r="H79" t="n">
-        <v>8.6</v>
+        <v>69.8</v>
       </c>
       <c r="I79" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J79" t="n">
-        <v>-20.04</v>
+        <v>21.23</v>
       </c>
       <c r="K79" t="n">
-        <v>-57.87</v>
+        <v>-42.21</v>
       </c>
       <c r="L79" t="n">
-        <v>61.24</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:23:34</t>
+          <t>09:26:39</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="F80" t="n">
-        <v>6.21</v>
+        <v>5.48</v>
       </c>
       <c r="G80" t="n">
-        <v>221.3</v>
+        <v>219</v>
       </c>
       <c r="H80" t="n">
-        <v>13</v>
+        <v>71.7</v>
       </c>
       <c r="I80" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J80" t="n">
-        <v>-86.27</v>
+        <v>-93.34999999999999</v>
       </c>
       <c r="K80" t="n">
-        <v>27.85</v>
+        <v>7.88</v>
       </c>
       <c r="L80" t="n">
-        <v>90.66</v>
+        <v>93.68000000000001</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:24:58</t>
+          <t>09:27:48</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>1.63</v>
+        <v>1.96</v>
       </c>
       <c r="F81" t="n">
         <v>6.21</v>
       </c>
       <c r="G81" t="n">
-        <v>221.1</v>
+        <v>238.5</v>
       </c>
       <c r="H81" t="n">
-        <v>22.3</v>
+        <v>37.4</v>
       </c>
       <c r="I81" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>28.26</v>
+        <v>-41.6</v>
       </c>
       <c r="K81" t="n">
-        <v>68.72</v>
+        <v>-91.48999999999999</v>
       </c>
       <c r="L81" t="n">
-        <v>74.3</v>
+        <v>100.5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:26:03</t>
+          <t>09:29:04</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.26</v>
+        <v>1.88</v>
       </c>
       <c r="F82" t="n">
-        <v>3.97</v>
+        <v>6.21</v>
       </c>
       <c r="G82" t="n">
-        <v>224.9</v>
+        <v>237</v>
       </c>
       <c r="H82" t="n">
-        <v>8.199999999999999</v>
+        <v>34.8</v>
       </c>
       <c r="I82" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>61.24</v>
+        <v>36.69</v>
       </c>
       <c r="K82" t="n">
-        <v>17.22</v>
+        <v>-76.22</v>
       </c>
       <c r="L82" t="n">
-        <v>63.61</v>
+        <v>84.59</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:30:58</t>
+          <t>09:33:47</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.59</v>
+        <v>1.66</v>
       </c>
       <c r="F83" t="n">
         <v>6.21</v>
       </c>
       <c r="G83" t="n">
-        <v>228.2</v>
+        <v>232</v>
       </c>
       <c r="H83" t="n">
-        <v>17.6</v>
+        <v>54.3</v>
       </c>
       <c r="I83" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>31.64</v>
+        <v>-3.04</v>
       </c>
       <c r="K83" t="n">
-        <v>70.16</v>
+        <v>-108.54</v>
       </c>
       <c r="L83" t="n">
-        <v>76.97</v>
+        <v>108.58</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:32:38</t>
+          <t>09:35:56</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="F84" t="n">
-        <v>5.61</v>
+        <v>6.21</v>
       </c>
       <c r="G84" t="n">
-        <v>226.1</v>
+        <v>222.8</v>
       </c>
       <c r="H84" t="n">
-        <v>16.5</v>
+        <v>36.4</v>
       </c>
       <c r="I84" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J84" t="n">
-        <v>62.42</v>
+        <v>-116.91</v>
       </c>
       <c r="K84" t="n">
-        <v>-85.90000000000001</v>
+        <v>70.89</v>
       </c>
       <c r="L84" t="n">
-        <v>106.18</v>
+        <v>136.73</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:35:18</t>
+          <t>09:37:39</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.17</v>
+        <v>1.9</v>
       </c>
       <c r="F85" t="n">
-        <v>6.21</v>
+        <v>4.38</v>
       </c>
       <c r="G85" t="n">
-        <v>227.3</v>
+        <v>226.1</v>
       </c>
       <c r="H85" t="n">
-        <v>14.6</v>
+        <v>40.1</v>
       </c>
       <c r="I85" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>-52.73</v>
+        <v>-36.46</v>
       </c>
       <c r="K85" t="n">
-        <v>-74.56999999999999</v>
+        <v>109.53</v>
       </c>
       <c r="L85" t="n">
-        <v>91.33</v>
+        <v>115.43</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:40:59</t>
+          <t>09:42:19</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="F86" t="n">
-        <v>5.99</v>
+        <v>5.93</v>
       </c>
       <c r="G86" t="n">
-        <v>244.3</v>
+        <v>231.2</v>
       </c>
       <c r="H86" t="n">
-        <v>7.5</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="I86" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>200.51</v>
+        <v>-150.98</v>
       </c>
       <c r="K86" t="n">
-        <v>29.31</v>
+        <v>-62.25</v>
       </c>
       <c r="L86" t="n">
-        <v>202.64</v>
+        <v>163.31</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:43:16</t>
+          <t>09:43:29</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="F87" t="n">
-        <v>6.04</v>
+        <v>6.21</v>
       </c>
       <c r="G87" t="n">
-        <v>227.7</v>
+        <v>231.4</v>
       </c>
       <c r="H87" t="n">
-        <v>12.4</v>
+        <v>25.8</v>
       </c>
       <c r="I87" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J87" t="n">
-        <v>-131.87</v>
+        <v>-153.25</v>
       </c>
       <c r="K87" t="n">
-        <v>-19.02</v>
+        <v>-45.01</v>
       </c>
       <c r="L87" t="n">
-        <v>133.23</v>
+        <v>159.72</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:44:29</t>
+          <t>09:44:27</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="F88" t="n">
         <v>6.21</v>
       </c>
       <c r="G88" t="n">
-        <v>225.1</v>
+        <v>231.6</v>
       </c>
       <c r="H88" t="n">
-        <v>16.4</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I88" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J88" t="n">
-        <v>161.39</v>
+        <v>-160.08</v>
       </c>
       <c r="K88" t="n">
-        <v>91.90000000000001</v>
+        <v>-65.25</v>
       </c>
       <c r="L88" t="n">
-        <v>185.73</v>
+        <v>172.87</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-08-25.xlsx
+++ b/output/2024-08-25.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="F14" t="n">
-        <v>4.92</v>
+        <v>6.21</v>
       </c>
       <c r="G14" t="n">
-        <v>232.3</v>
+        <v>237</v>
       </c>
       <c r="H14" t="n">
-        <v>28.9</v>
+        <v>25.8</v>
       </c>
       <c r="I14" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>28.33</v>
+        <v>-11.39</v>
       </c>
       <c r="K14" t="n">
-        <v>-13.22</v>
+        <v>-0.11</v>
       </c>
       <c r="L14" t="n">
-        <v>31.26</v>
+        <v>11.39</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:07:41</t>
+          <t>06:07:28</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>1.32</v>
       </c>
       <c r="F15" t="n">
         <v>6.21</v>
       </c>
       <c r="G15" t="n">
-        <v>243.5</v>
+        <v>236.2</v>
       </c>
       <c r="H15" t="n">
-        <v>84.40000000000001</v>
+        <v>44.7</v>
       </c>
       <c r="I15" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J15" t="n">
-        <v>29.96</v>
+        <v>-6.71</v>
       </c>
       <c r="K15" t="n">
-        <v>18.26</v>
+        <v>26.43</v>
       </c>
       <c r="L15" t="n">
-        <v>35.09</v>
+        <v>27.27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:09:14</t>
+          <t>06:09:36</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="F16" t="n">
-        <v>1.78</v>
+        <v>3.28</v>
       </c>
       <c r="G16" t="n">
-        <v>231.7</v>
+        <v>233.1</v>
       </c>
       <c r="H16" t="n">
-        <v>46.8</v>
+        <v>27.2</v>
       </c>
       <c r="I16" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>30.86</v>
+        <v>14.44</v>
       </c>
       <c r="K16" t="n">
-        <v>-4.35</v>
+        <v>-33.37</v>
       </c>
       <c r="L16" t="n">
-        <v>31.17</v>
+        <v>36.36</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:12:36</t>
+          <t>06:13:06</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1.49</v>
+        <v>1.76</v>
       </c>
       <c r="F17" t="n">
-        <v>6.21</v>
+        <v>3.21</v>
       </c>
       <c r="G17" t="n">
-        <v>224.4</v>
+        <v>227.8</v>
       </c>
       <c r="H17" t="n">
-        <v>45.1</v>
+        <v>46.2</v>
       </c>
       <c r="I17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>42.47</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>-18.15</v>
+        <v>44.39</v>
       </c>
       <c r="L17" t="n">
-        <v>46.18</v>
+        <v>45.22</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:14:00</t>
+          <t>06:14:24</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.66</v>
+        <v>2.64</v>
       </c>
       <c r="F18" t="n">
-        <v>5.93</v>
+        <v>6.21</v>
       </c>
       <c r="G18" t="n">
-        <v>218.7</v>
+        <v>218</v>
       </c>
       <c r="H18" t="n">
-        <v>55.7</v>
+        <v>51</v>
       </c>
       <c r="I18" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>-22.69</v>
+        <v>-18.73</v>
       </c>
       <c r="K18" t="n">
-        <v>-39.07</v>
+        <v>-66.44</v>
       </c>
       <c r="L18" t="n">
-        <v>45.18</v>
+        <v>69.03</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:16:22</t>
+          <t>06:15:57</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="F19" t="n">
-        <v>2.87</v>
+        <v>3.79</v>
       </c>
       <c r="G19" t="n">
-        <v>229.2</v>
+        <v>227.9</v>
       </c>
       <c r="H19" t="n">
-        <v>36.9</v>
+        <v>39.7</v>
       </c>
       <c r="I19" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="J19" t="n">
-        <v>29.06</v>
+        <v>40.47</v>
       </c>
       <c r="K19" t="n">
-        <v>100.36</v>
+        <v>23.5</v>
       </c>
       <c r="L19" t="n">
-        <v>104.48</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:21:13</t>
+          <t>06:20:23</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="F20" t="n">
-        <v>3.52</v>
+        <v>6.21</v>
       </c>
       <c r="G20" t="n">
-        <v>213</v>
+        <v>219.6</v>
       </c>
       <c r="H20" t="n">
-        <v>31.8</v>
+        <v>48.1</v>
       </c>
       <c r="I20" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>59.78</v>
+        <v>72.8</v>
       </c>
       <c r="K20" t="n">
-        <v>-62</v>
+        <v>7.61</v>
       </c>
       <c r="L20" t="n">
-        <v>86.13</v>
+        <v>73.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:23:51</t>
+          <t>06:22:01</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1.76</v>
+        <v>1.48</v>
       </c>
       <c r="F21" t="n">
-        <v>5.3</v>
+        <v>6.21</v>
       </c>
       <c r="G21" t="n">
-        <v>221.6</v>
+        <v>233.2</v>
       </c>
       <c r="H21" t="n">
-        <v>59.4</v>
+        <v>44.3</v>
       </c>
       <c r="I21" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J21" t="n">
-        <v>-52.99</v>
+        <v>-31.21</v>
       </c>
       <c r="K21" t="n">
-        <v>78.55</v>
+        <v>-48.26</v>
       </c>
       <c r="L21" t="n">
-        <v>94.75</v>
+        <v>57.48</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:25:22</t>
+          <t>06:22:53</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>1.65</v>
+        <v>1.16</v>
       </c>
       <c r="F22" t="n">
-        <v>4.52</v>
+        <v>1.84</v>
       </c>
       <c r="G22" t="n">
-        <v>217.7</v>
+        <v>227.8</v>
       </c>
       <c r="H22" t="n">
-        <v>20.3</v>
+        <v>53.5</v>
       </c>
       <c r="I22" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="J22" t="n">
-        <v>-67.04000000000001</v>
+        <v>-53.59</v>
       </c>
       <c r="K22" t="n">
-        <v>46.66</v>
+        <v>17.28</v>
       </c>
       <c r="L22" t="n">
-        <v>81.67</v>
+        <v>56.3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:30:20</t>
+          <t>06:27:26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="F23" t="n">
-        <v>3.08</v>
+        <v>2.23</v>
       </c>
       <c r="G23" t="n">
-        <v>239.6</v>
+        <v>225.8</v>
       </c>
       <c r="H23" t="n">
-        <v>36.2</v>
+        <v>42.9</v>
       </c>
       <c r="I23" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="J23" t="n">
-        <v>103.75</v>
+        <v>127.73</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.68</v>
+        <v>-82.29000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>103.75</v>
+        <v>151.94</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:32:50</t>
+          <t>06:29:04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="F24" t="n">
-        <v>6.21</v>
+        <v>2.74</v>
       </c>
       <c r="G24" t="n">
-        <v>230.7</v>
+        <v>219.4</v>
       </c>
       <c r="H24" t="n">
-        <v>22</v>
+        <v>30.2</v>
       </c>
       <c r="I24" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="J24" t="n">
-        <v>123.39</v>
+        <v>24.64</v>
       </c>
       <c r="K24" t="n">
-        <v>30.88</v>
+        <v>-97.68000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>127.19</v>
+        <v>100.74</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:34:28</t>
+          <t>06:31:08</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>1.81</v>
+        <v>1.29</v>
       </c>
       <c r="F25" t="n">
-        <v>5.79</v>
+        <v>1.59</v>
       </c>
       <c r="G25" t="n">
-        <v>233.4</v>
+        <v>229</v>
       </c>
       <c r="H25" t="n">
-        <v>72.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="I25" t="n">
         <v>28</v>
       </c>
       <c r="J25" t="n">
-        <v>-29.37</v>
+        <v>79.02</v>
       </c>
       <c r="K25" t="n">
-        <v>126.74</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>130.1</v>
+        <v>102.16</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:39:57</t>
+          <t>06:36:48</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="F26" t="n">
         <v>6.21</v>
       </c>
       <c r="G26" t="n">
-        <v>216.1</v>
+        <v>220.2</v>
       </c>
       <c r="H26" t="n">
-        <v>39.7</v>
+        <v>44.3</v>
       </c>
       <c r="I26" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>-136.76</v>
+        <v>-125.44</v>
       </c>
       <c r="K26" t="n">
-        <v>-38.35</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>142.03</v>
+        <v>125.71</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:42:20</t>
+          <t>06:38:21</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.49</v>
+        <v>1.64</v>
       </c>
       <c r="F27" t="n">
-        <v>5.16</v>
+        <v>6.21</v>
       </c>
       <c r="G27" t="n">
-        <v>223.5</v>
+        <v>234.3</v>
       </c>
       <c r="H27" t="n">
-        <v>52.3</v>
+        <v>37.8</v>
       </c>
       <c r="I27" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J27" t="n">
-        <v>177.65</v>
+        <v>-88.12</v>
       </c>
       <c r="K27" t="n">
-        <v>-26.76</v>
+        <v>-89.44</v>
       </c>
       <c r="L27" t="n">
-        <v>179.65</v>
+        <v>125.55</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:44:44</t>
+          <t>06:40:03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="F28" t="n">
-        <v>6.04</v>
+        <v>6.21</v>
       </c>
       <c r="G28" t="n">
-        <v>220.8</v>
+        <v>230</v>
       </c>
       <c r="H28" t="n">
-        <v>29.8</v>
+        <v>23.2</v>
       </c>
       <c r="I28" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J28" t="n">
-        <v>-54.75</v>
+        <v>151.87</v>
       </c>
       <c r="K28" t="n">
-        <v>119.83</v>
+        <v>-29.31</v>
       </c>
       <c r="L28" t="n">
-        <v>131.75</v>
+        <v>154.68</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:53:23</t>
+          <t>06:48:32</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="F29" t="n">
-        <v>6.06</v>
+        <v>3.66</v>
       </c>
       <c r="G29" t="n">
-        <v>235.3</v>
+        <v>222.3</v>
       </c>
       <c r="H29" t="n">
-        <v>66.5</v>
+        <v>54.5</v>
       </c>
       <c r="I29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>-9.98</v>
+        <v>-40.66</v>
       </c>
       <c r="K29" t="n">
-        <v>28.97</v>
+        <v>18.83</v>
       </c>
       <c r="L29" t="n">
-        <v>30.64</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06:54:33</t>
+          <t>06:50:25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="F30" t="n">
-        <v>2.01</v>
+        <v>4.64</v>
       </c>
       <c r="G30" t="n">
-        <v>243.5</v>
+        <v>226</v>
       </c>
       <c r="H30" t="n">
-        <v>51.1</v>
+        <v>55.4</v>
       </c>
       <c r="I30" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-13.54</v>
+        <v>-34.53</v>
       </c>
       <c r="K30" t="n">
-        <v>27.17</v>
+        <v>25.98</v>
       </c>
       <c r="L30" t="n">
-        <v>30.35</v>
+        <v>43.21</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06:55:21</t>
+          <t>06:51:37</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="F31" t="n">
-        <v>3.9</v>
+        <v>5.01</v>
       </c>
       <c r="G31" t="n">
-        <v>224.5</v>
+        <v>229.4</v>
       </c>
       <c r="H31" t="n">
-        <v>51.1</v>
+        <v>50.5</v>
       </c>
       <c r="I31" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>-22.42</v>
+        <v>-39.89</v>
       </c>
       <c r="K31" t="n">
-        <v>-9.07</v>
+        <v>5.3</v>
       </c>
       <c r="L31" t="n">
-        <v>24.19</v>
+        <v>40.24</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:00:03</t>
+          <t>06:55:54</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1.64</v>
+        <v>1.41</v>
       </c>
       <c r="F32" t="n">
-        <v>2.78</v>
+        <v>4.09</v>
       </c>
       <c r="G32" t="n">
-        <v>232.2</v>
+        <v>218.6</v>
       </c>
       <c r="H32" t="n">
-        <v>29.6</v>
+        <v>53.3</v>
       </c>
       <c r="I32" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>-47.48</v>
+        <v>-38.53</v>
       </c>
       <c r="K32" t="n">
-        <v>2.45</v>
+        <v>-20.4</v>
       </c>
       <c r="L32" t="n">
-        <v>47.54</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:01:41</t>
+          <t>06:56:51</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1.53</v>
+        <v>1.87</v>
       </c>
       <c r="F33" t="n">
-        <v>3.99</v>
+        <v>4.47</v>
       </c>
       <c r="G33" t="n">
-        <v>248.4</v>
+        <v>231.1</v>
       </c>
       <c r="H33" t="n">
-        <v>50.3</v>
+        <v>60.6</v>
       </c>
       <c r="I33" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>-35.66</v>
+        <v>43.23</v>
       </c>
       <c r="K33" t="n">
-        <v>18.4</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>40.12</v>
+        <v>44.33</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>06:58:18</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="F34" t="n">
-        <v>4.82</v>
+        <v>6.21</v>
       </c>
       <c r="G34" t="n">
-        <v>222.1</v>
+        <v>232.5</v>
       </c>
       <c r="H34" t="n">
-        <v>31</v>
+        <v>95.3</v>
       </c>
       <c r="I34" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="J34" t="n">
-        <v>56.35</v>
+        <v>51.06</v>
       </c>
       <c r="K34" t="n">
-        <v>12.59</v>
+        <v>3.87</v>
       </c>
       <c r="L34" t="n">
-        <v>57.74</v>
+        <v>51.21</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:09:32</t>
+          <t>07:02:22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="F35" t="n">
-        <v>4.05</v>
+        <v>5.73</v>
       </c>
       <c r="G35" t="n">
-        <v>237.7</v>
+        <v>239.1</v>
       </c>
       <c r="H35" t="n">
-        <v>49.1</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J35" t="n">
-        <v>-61.52</v>
+        <v>80.37</v>
       </c>
       <c r="K35" t="n">
-        <v>45.34</v>
+        <v>-87.77</v>
       </c>
       <c r="L35" t="n">
-        <v>76.42</v>
+        <v>119.01</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:11:06</t>
+          <t>07:03:23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="F36" t="n">
-        <v>4.18</v>
+        <v>6.21</v>
       </c>
       <c r="G36" t="n">
-        <v>232.6</v>
+        <v>235.2</v>
       </c>
       <c r="H36" t="n">
-        <v>46.1</v>
+        <v>32.6</v>
       </c>
       <c r="I36" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J36" t="n">
-        <v>-20.13</v>
+        <v>27.48</v>
       </c>
       <c r="K36" t="n">
-        <v>-64.09</v>
+        <v>58.43</v>
       </c>
       <c r="L36" t="n">
-        <v>67.18000000000001</v>
+        <v>64.56999999999999</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:11:36</t>
+          <t>07:05:39</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="F37" t="n">
-        <v>5.69</v>
+        <v>4.24</v>
       </c>
       <c r="G37" t="n">
-        <v>212.1</v>
+        <v>237.4</v>
       </c>
       <c r="H37" t="n">
-        <v>25.1</v>
+        <v>39.4</v>
       </c>
       <c r="I37" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>-15.74</v>
+        <v>48</v>
       </c>
       <c r="K37" t="n">
-        <v>-16.9</v>
+        <v>51.12</v>
       </c>
       <c r="L37" t="n">
-        <v>23.09</v>
+        <v>70.12</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:16:20</t>
+          <t>07:11:09</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1.66</v>
+        <v>1.48</v>
       </c>
       <c r="F38" t="n">
-        <v>5.3</v>
+        <v>1.78</v>
       </c>
       <c r="G38" t="n">
-        <v>231.9</v>
+        <v>229</v>
       </c>
       <c r="H38" t="n">
-        <v>58.7</v>
+        <v>45.8</v>
       </c>
       <c r="I38" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>-46.25</v>
+        <v>-89.36</v>
       </c>
       <c r="K38" t="n">
-        <v>112.91</v>
+        <v>-24</v>
       </c>
       <c r="L38" t="n">
-        <v>122.01</v>
+        <v>92.53</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:18:06</t>
+          <t>07:13:05</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="F39" t="n">
-        <v>3.62</v>
+        <v>5.81</v>
       </c>
       <c r="G39" t="n">
-        <v>229.5</v>
+        <v>231.7</v>
       </c>
       <c r="H39" t="n">
-        <v>55.2</v>
+        <v>71.2</v>
       </c>
       <c r="I39" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>79.26000000000001</v>
+        <v>-142.21</v>
       </c>
       <c r="K39" t="n">
-        <v>-104.42</v>
+        <v>-13.31</v>
       </c>
       <c r="L39" t="n">
-        <v>131.1</v>
+        <v>142.83</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:20:18</t>
+          <t>07:14:59</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.31</v>
+        <v>1.68</v>
       </c>
       <c r="F40" t="n">
         <v>6.21</v>
       </c>
       <c r="G40" t="n">
-        <v>233.8</v>
+        <v>231.3</v>
       </c>
       <c r="H40" t="n">
-        <v>60.4</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J40" t="n">
-        <v>99.76000000000001</v>
+        <v>62.26</v>
       </c>
       <c r="K40" t="n">
-        <v>102.23</v>
+        <v>-96.81999999999999</v>
       </c>
       <c r="L40" t="n">
-        <v>142.84</v>
+        <v>115.11</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:25:12</t>
+          <t>07:19:21</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1.68</v>
+        <v>1.89</v>
       </c>
       <c r="F41" t="n">
-        <v>5.04</v>
+        <v>6.15</v>
       </c>
       <c r="G41" t="n">
-        <v>227.2</v>
+        <v>226.3</v>
       </c>
       <c r="H41" t="n">
-        <v>8.1</v>
+        <v>59.7</v>
       </c>
       <c r="I41" t="n">
         <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>43.04</v>
+        <v>137.14</v>
       </c>
       <c r="K41" t="n">
-        <v>-111.52</v>
+        <v>-31.6</v>
       </c>
       <c r="L41" t="n">
-        <v>119.54</v>
+        <v>140.74</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:27:15</t>
+          <t>07:20:43</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.54</v>
+        <v>1.94</v>
       </c>
       <c r="F42" t="n">
-        <v>5.09</v>
+        <v>6.21</v>
       </c>
       <c r="G42" t="n">
-        <v>244.2</v>
+        <v>234.8</v>
       </c>
       <c r="H42" t="n">
-        <v>54.4</v>
+        <v>58.4</v>
       </c>
       <c r="I42" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J42" t="n">
-        <v>-155.46</v>
+        <v>164.82</v>
       </c>
       <c r="K42" t="n">
-        <v>25.79</v>
+        <v>-72.23</v>
       </c>
       <c r="L42" t="n">
-        <v>157.58</v>
+        <v>179.95</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:28:25</t>
+          <t>07:22:54</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>1.36</v>
+        <v>1.85</v>
       </c>
       <c r="F43" t="n">
-        <v>3.82</v>
+        <v>3.52</v>
       </c>
       <c r="G43" t="n">
-        <v>230.3</v>
+        <v>233.3</v>
       </c>
       <c r="H43" t="n">
-        <v>40.4</v>
+        <v>32.6</v>
       </c>
       <c r="I43" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>-80.09999999999999</v>
+        <v>-49.48</v>
       </c>
       <c r="K43" t="n">
-        <v>-117.82</v>
+        <v>-139.05</v>
       </c>
       <c r="L43" t="n">
-        <v>142.47</v>
+        <v>147.59</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:37:15</t>
+          <t>07:32:13</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1.72</v>
+        <v>1.54</v>
       </c>
       <c r="F44" t="n">
-        <v>6.21</v>
+        <v>5.65</v>
       </c>
       <c r="G44" t="n">
-        <v>212.7</v>
+        <v>216.4</v>
       </c>
       <c r="H44" t="n">
-        <v>40.8</v>
+        <v>34.6</v>
       </c>
       <c r="I44" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J44" t="n">
-        <v>14.95</v>
+        <v>-19.44</v>
       </c>
       <c r="K44" t="n">
-        <v>-30.1</v>
+        <v>5.53</v>
       </c>
       <c r="L44" t="n">
-        <v>33.6</v>
+        <v>20.21</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:39:29</t>
+          <t>07:32:51</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1.49</v>
+        <v>1.63</v>
       </c>
       <c r="F45" t="n">
-        <v>5.42</v>
+        <v>6.21</v>
       </c>
       <c r="G45" t="n">
-        <v>229.3</v>
+        <v>232.1</v>
       </c>
       <c r="H45" t="n">
-        <v>16.8</v>
+        <v>23.3</v>
       </c>
       <c r="I45" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>-23.52</v>
+        <v>22.69</v>
       </c>
       <c r="K45" t="n">
-        <v>-13.42</v>
+        <v>-22.05</v>
       </c>
       <c r="L45" t="n">
-        <v>27.07</v>
+        <v>31.63</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:40:44</t>
+          <t>07:34:09</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="F46" t="n">
-        <v>6.21</v>
+        <v>3.98</v>
       </c>
       <c r="G46" t="n">
-        <v>224.2</v>
+        <v>223</v>
       </c>
       <c r="H46" t="n">
-        <v>21.7</v>
+        <v>53.9</v>
       </c>
       <c r="I46" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>28.35</v>
+        <v>21.25</v>
       </c>
       <c r="K46" t="n">
-        <v>-20.31</v>
+        <v>14.11</v>
       </c>
       <c r="L46" t="n">
-        <v>34.88</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:44:02</t>
+          <t>07:38:48</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>1.32</v>
+        <v>1.56</v>
       </c>
       <c r="F47" t="n">
-        <v>3.15</v>
+        <v>4.46</v>
       </c>
       <c r="G47" t="n">
-        <v>216.7</v>
+        <v>226.4</v>
       </c>
       <c r="H47" t="n">
-        <v>60.2</v>
+        <v>51.3</v>
       </c>
       <c r="I47" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>32.45</v>
+        <v>-11.53</v>
       </c>
       <c r="K47" t="n">
-        <v>-31.77</v>
+        <v>-48.89</v>
       </c>
       <c r="L47" t="n">
-        <v>45.41</v>
+        <v>50.23</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:45:38</t>
+          <t>07:41:11</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="F48" t="n">
-        <v>5.44</v>
+        <v>3.24</v>
       </c>
       <c r="G48" t="n">
-        <v>230.2</v>
+        <v>234.7</v>
       </c>
       <c r="H48" t="n">
-        <v>53.8</v>
+        <v>31.7</v>
       </c>
       <c r="I48" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J48" t="n">
-        <v>-56.95</v>
+        <v>41.95</v>
       </c>
       <c r="K48" t="n">
-        <v>-11.96</v>
+        <v>19.39</v>
       </c>
       <c r="L48" t="n">
-        <v>58.2</v>
+        <v>46.22</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:47:00</t>
+          <t>07:42:34</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="F49" t="n">
-        <v>5.24</v>
+        <v>6.21</v>
       </c>
       <c r="G49" t="n">
-        <v>220.9</v>
+        <v>231.6</v>
       </c>
       <c r="H49" t="n">
-        <v>41.3</v>
+        <v>46.7</v>
       </c>
       <c r="I49" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>-65.36</v>
+        <v>-51.4</v>
       </c>
       <c r="K49" t="n">
-        <v>6.96</v>
+        <v>14.13</v>
       </c>
       <c r="L49" t="n">
-        <v>65.73</v>
+        <v>53.31</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07:52:00</t>
+          <t>07:47:05</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>1.72</v>
+        <v>1.43</v>
       </c>
       <c r="F50" t="n">
-        <v>6.12</v>
+        <v>2.75</v>
       </c>
       <c r="G50" t="n">
-        <v>239</v>
+        <v>212.4</v>
       </c>
       <c r="H50" t="n">
-        <v>79.2</v>
+        <v>62</v>
       </c>
       <c r="I50" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J50" t="n">
-        <v>-79.48999999999999</v>
+        <v>-25.71</v>
       </c>
       <c r="K50" t="n">
-        <v>32.01</v>
+        <v>12.65</v>
       </c>
       <c r="L50" t="n">
-        <v>85.69</v>
+        <v>28.65</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07:54:34</t>
+          <t>07:49:22</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="F51" t="n">
         <v>6.21</v>
       </c>
       <c r="G51" t="n">
-        <v>229.9</v>
+        <v>240.5</v>
       </c>
       <c r="H51" t="n">
-        <v>36.5</v>
+        <v>83</v>
       </c>
       <c r="I51" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>-18.54</v>
+        <v>71.54000000000001</v>
       </c>
       <c r="K51" t="n">
-        <v>56.69</v>
+        <v>17.35</v>
       </c>
       <c r="L51" t="n">
-        <v>59.64</v>
+        <v>73.62</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07:56:11</t>
+          <t>07:51:39</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>1.93</v>
+        <v>1.3</v>
       </c>
       <c r="F52" t="n">
-        <v>4.11</v>
+        <v>6.21</v>
       </c>
       <c r="G52" t="n">
-        <v>238.4</v>
+        <v>228.6</v>
       </c>
       <c r="H52" t="n">
-        <v>36.6</v>
+        <v>37.8</v>
       </c>
       <c r="I52" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J52" t="n">
-        <v>1.2</v>
+        <v>69.72</v>
       </c>
       <c r="K52" t="n">
-        <v>102.76</v>
+        <v>-19.11</v>
       </c>
       <c r="L52" t="n">
-        <v>102.77</v>
+        <v>72.29000000000001</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:01:00</t>
+          <t>07:57:05</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="F53" t="n">
-        <v>5.68</v>
+        <v>4.79</v>
       </c>
       <c r="G53" t="n">
-        <v>233.4</v>
+        <v>231.9</v>
       </c>
       <c r="H53" t="n">
-        <v>33.6</v>
+        <v>79.5</v>
       </c>
       <c r="I53" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J53" t="n">
-        <v>-25.57</v>
+        <v>84.23</v>
       </c>
       <c r="K53" t="n">
-        <v>-98.81</v>
+        <v>-91.58</v>
       </c>
       <c r="L53" t="n">
-        <v>102.07</v>
+        <v>124.43</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:03:03</t>
+          <t>07:59:43</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="F54" t="n">
-        <v>2.92</v>
+        <v>6.21</v>
       </c>
       <c r="G54" t="n">
-        <v>220.4</v>
+        <v>232.9</v>
       </c>
       <c r="H54" t="n">
-        <v>66</v>
+        <v>51.6</v>
       </c>
       <c r="I54" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>65.73999999999999</v>
+        <v>92.31</v>
       </c>
       <c r="K54" t="n">
-        <v>138.9</v>
+        <v>-30.08</v>
       </c>
       <c r="L54" t="n">
-        <v>153.68</v>
+        <v>97.09</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:05:01</t>
+          <t>08:01:47</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2353,28 +2353,28 @@
         <v>6.21</v>
       </c>
       <c r="G55" t="n">
-        <v>231.8</v>
+        <v>217.7</v>
       </c>
       <c r="H55" t="n">
-        <v>40.2</v>
+        <v>58.6</v>
       </c>
       <c r="I55" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-89.29000000000001</v>
+        <v>48.92</v>
       </c>
       <c r="K55" t="n">
-        <v>51.88</v>
+        <v>-120.37</v>
       </c>
       <c r="L55" t="n">
-        <v>103.26</v>
+        <v>129.94</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:09:18</t>
+          <t>08:06:57</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="F56" t="n">
-        <v>4.25</v>
+        <v>5.61</v>
       </c>
       <c r="G56" t="n">
-        <v>229.3</v>
+        <v>218.2</v>
       </c>
       <c r="H56" t="n">
-        <v>100</v>
+        <v>56.1</v>
       </c>
       <c r="I56" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>76</v>
+        <v>54.66</v>
       </c>
       <c r="K56" t="n">
-        <v>-97.56</v>
+        <v>141.27</v>
       </c>
       <c r="L56" t="n">
-        <v>123.67</v>
+        <v>151.47</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:11:07</t>
+          <t>08:07:39</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.02</v>
+        <v>1.82</v>
       </c>
       <c r="F57" t="n">
         <v>6.21</v>
       </c>
       <c r="G57" t="n">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="H57" t="n">
-        <v>36.8</v>
+        <v>50.1</v>
       </c>
       <c r="I57" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>-190.74</v>
+        <v>-90.84</v>
       </c>
       <c r="K57" t="n">
-        <v>10.16</v>
+        <v>90.12</v>
       </c>
       <c r="L57" t="n">
-        <v>191.01</v>
+        <v>127.96</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:13:07</t>
+          <t>08:08:43</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="F58" t="n">
-        <v>6.21</v>
+        <v>4.35</v>
       </c>
       <c r="G58" t="n">
-        <v>215.8</v>
+        <v>228</v>
       </c>
       <c r="H58" t="n">
-        <v>18.7</v>
+        <v>44.6</v>
       </c>
       <c r="I58" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J58" t="n">
-        <v>191.99</v>
+        <v>-98.68000000000001</v>
       </c>
       <c r="K58" t="n">
-        <v>37.02</v>
+        <v>-109.43</v>
       </c>
       <c r="L58" t="n">
-        <v>195.53</v>
+        <v>147.35</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:23:25</t>
+          <t>08:21:08</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="F59" t="n">
         <v>6.21</v>
       </c>
       <c r="G59" t="n">
-        <v>249.1</v>
+        <v>232.4</v>
       </c>
       <c r="H59" t="n">
-        <v>14.2</v>
+        <v>39.2</v>
       </c>
       <c r="I59" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>-29.6</v>
+        <v>19.79</v>
       </c>
       <c r="K59" t="n">
-        <v>26.86</v>
+        <v>14.3</v>
       </c>
       <c r="L59" t="n">
-        <v>39.97</v>
+        <v>24.41</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:24:14</t>
+          <t>08:23:28</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>1.85</v>
+        <v>1.51</v>
       </c>
       <c r="F60" t="n">
-        <v>6.07</v>
+        <v>6.14</v>
       </c>
       <c r="G60" t="n">
-        <v>226.2</v>
+        <v>221.4</v>
       </c>
       <c r="H60" t="n">
-        <v>43.3</v>
+        <v>16.3</v>
       </c>
       <c r="I60" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J60" t="n">
-        <v>-8.050000000000001</v>
+        <v>-22.34</v>
       </c>
       <c r="K60" t="n">
-        <v>-36.57</v>
+        <v>18.84</v>
       </c>
       <c r="L60" t="n">
-        <v>37.44</v>
+        <v>29.23</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:25:16</t>
+          <t>08:24:51</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="F61" t="n">
         <v>6.21</v>
       </c>
       <c r="G61" t="n">
-        <v>223.2</v>
+        <v>243.9</v>
       </c>
       <c r="H61" t="n">
-        <v>81.2</v>
+        <v>49.2</v>
       </c>
       <c r="I61" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J61" t="n">
-        <v>22.11</v>
+        <v>-19.07</v>
       </c>
       <c r="K61" t="n">
-        <v>22.55</v>
+        <v>-1.45</v>
       </c>
       <c r="L61" t="n">
-        <v>31.58</v>
+        <v>19.13</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:29:38</t>
+          <t>08:28:15</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>1.48</v>
+        <v>1.9</v>
       </c>
       <c r="F62" t="n">
         <v>6.21</v>
       </c>
       <c r="G62" t="n">
-        <v>237.4</v>
+        <v>226.8</v>
       </c>
       <c r="H62" t="n">
-        <v>27.5</v>
+        <v>59.7</v>
       </c>
       <c r="I62" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>41.09</v>
+        <v>-28.82</v>
       </c>
       <c r="K62" t="n">
-        <v>-10.28</v>
+        <v>15.26</v>
       </c>
       <c r="L62" t="n">
-        <v>42.36</v>
+        <v>32.61</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:32:14</t>
+          <t>08:29:56</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="F63" t="n">
-        <v>3.69</v>
+        <v>4.57</v>
       </c>
       <c r="G63" t="n">
-        <v>228.3</v>
+        <v>224.3</v>
       </c>
       <c r="H63" t="n">
-        <v>51.9</v>
+        <v>55.1</v>
       </c>
       <c r="I63" t="n">
         <v>23</v>
       </c>
       <c r="J63" t="n">
-        <v>-17.2</v>
+        <v>-41.47</v>
       </c>
       <c r="K63" t="n">
-        <v>-51.7</v>
+        <v>-6.05</v>
       </c>
       <c r="L63" t="n">
-        <v>54.48</v>
+        <v>41.91</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:34:02</t>
+          <t>08:32:09</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="F64" t="n">
-        <v>3.49</v>
+        <v>6.21</v>
       </c>
       <c r="G64" t="n">
-        <v>230.7</v>
+        <v>247.1</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>61.6</v>
       </c>
       <c r="I64" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>-47.64</v>
+        <v>-18.68</v>
       </c>
       <c r="K64" t="n">
-        <v>-27.42</v>
+        <v>-46.53</v>
       </c>
       <c r="L64" t="n">
-        <v>54.97</v>
+        <v>50.14</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:37:55</t>
+          <t>08:38:22</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>1.6</v>
+        <v>2.07</v>
       </c>
       <c r="F65" t="n">
-        <v>3.32</v>
+        <v>4.92</v>
       </c>
       <c r="G65" t="n">
-        <v>229.3</v>
+        <v>215.6</v>
       </c>
       <c r="H65" t="n">
-        <v>33.9</v>
+        <v>50.7</v>
       </c>
       <c r="I65" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>72.12</v>
+        <v>4.54</v>
       </c>
       <c r="K65" t="n">
-        <v>29.41</v>
+        <v>75.84</v>
       </c>
       <c r="L65" t="n">
-        <v>77.89</v>
+        <v>75.97</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:39:37</t>
+          <t>08:39:47</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="F66" t="n">
-        <v>4.86</v>
+        <v>6.21</v>
       </c>
       <c r="G66" t="n">
-        <v>225.5</v>
+        <v>216.1</v>
       </c>
       <c r="H66" t="n">
-        <v>32.9</v>
+        <v>49.7</v>
       </c>
       <c r="I66" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>-69.52</v>
+        <v>-57.38</v>
       </c>
       <c r="K66" t="n">
-        <v>-18.09</v>
+        <v>4.62</v>
       </c>
       <c r="L66" t="n">
-        <v>71.83</v>
+        <v>57.57</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:41:14</t>
+          <t>08:42:20</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="F67" t="n">
-        <v>5.48</v>
+        <v>4.45</v>
       </c>
       <c r="G67" t="n">
-        <v>234.9</v>
+        <v>239.1</v>
       </c>
       <c r="H67" t="n">
-        <v>75.59999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="I67" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>0.27</v>
+        <v>-59.92</v>
       </c>
       <c r="K67" t="n">
-        <v>-86.09</v>
+        <v>-12.81</v>
       </c>
       <c r="L67" t="n">
-        <v>86.09</v>
+        <v>61.28</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:44:29</t>
+          <t>08:46:56</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>1.96</v>
+        <v>1.69</v>
       </c>
       <c r="F68" t="n">
-        <v>6.18</v>
+        <v>6.21</v>
       </c>
       <c r="G68" t="n">
-        <v>228.1</v>
+        <v>221.7</v>
       </c>
       <c r="H68" t="n">
-        <v>76.2</v>
+        <v>22.3</v>
       </c>
       <c r="I68" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="J68" t="n">
-        <v>-53.24</v>
+        <v>-34.89</v>
       </c>
       <c r="K68" t="n">
-        <v>-146.72</v>
+        <v>66.58</v>
       </c>
       <c r="L68" t="n">
-        <v>156.08</v>
+        <v>75.17</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:45:51</t>
+          <t>08:48:30</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>1.75</v>
+        <v>1.97</v>
       </c>
       <c r="F69" t="n">
-        <v>3.2</v>
+        <v>4.81</v>
       </c>
       <c r="G69" t="n">
-        <v>225.1</v>
+        <v>224.3</v>
       </c>
       <c r="H69" t="n">
-        <v>30.2</v>
+        <v>78.3</v>
       </c>
       <c r="I69" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="J69" t="n">
-        <v>88.09999999999999</v>
+        <v>32.5</v>
       </c>
       <c r="K69" t="n">
-        <v>75.66</v>
+        <v>124.11</v>
       </c>
       <c r="L69" t="n">
-        <v>116.13</v>
+        <v>128.3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:47:49</t>
+          <t>08:50:22</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="F70" t="n">
-        <v>4.87</v>
+        <v>4.31</v>
       </c>
       <c r="G70" t="n">
-        <v>246.6</v>
+        <v>219.9</v>
       </c>
       <c r="H70" t="n">
-        <v>29.7</v>
+        <v>43.6</v>
       </c>
       <c r="I70" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>98.25</v>
+        <v>29.08</v>
       </c>
       <c r="K70" t="n">
-        <v>28.12</v>
+        <v>-106.84</v>
       </c>
       <c r="L70" t="n">
-        <v>102.19</v>
+        <v>110.73</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:51:51</t>
+          <t>08:53:34</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>1.77</v>
+        <v>2.28</v>
       </c>
       <c r="F71" t="n">
-        <v>6.21</v>
+        <v>6.05</v>
       </c>
       <c r="G71" t="n">
-        <v>226.8</v>
+        <v>228.1</v>
       </c>
       <c r="H71" t="n">
-        <v>38.3</v>
+        <v>10.8</v>
       </c>
       <c r="I71" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="J71" t="n">
-        <v>124.42</v>
+        <v>-157.42</v>
       </c>
       <c r="K71" t="n">
-        <v>-68.97</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="L71" t="n">
-        <v>142.26</v>
+        <v>182.03</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:54:05</t>
+          <t>08:54:45</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="F72" t="n">
         <v>6.21</v>
       </c>
       <c r="G72" t="n">
-        <v>232</v>
+        <v>228.2</v>
       </c>
       <c r="H72" t="n">
-        <v>57.4</v>
+        <v>51.7</v>
       </c>
       <c r="I72" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-98.58</v>
+        <v>88.11</v>
       </c>
       <c r="K72" t="n">
-        <v>-132</v>
+        <v>94.76000000000001</v>
       </c>
       <c r="L72" t="n">
-        <v>164.75</v>
+        <v>129.39</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08:55:34</t>
+          <t>08:56:29</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="F73" t="n">
-        <v>1.99</v>
+        <v>6.21</v>
       </c>
       <c r="G73" t="n">
-        <v>225.2</v>
+        <v>229.6</v>
       </c>
       <c r="H73" t="n">
-        <v>58.5</v>
+        <v>77.2</v>
       </c>
       <c r="I73" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J73" t="n">
-        <v>-140.81</v>
+        <v>104.77</v>
       </c>
       <c r="K73" t="n">
-        <v>-82.56</v>
+        <v>-141.8</v>
       </c>
       <c r="L73" t="n">
-        <v>163.23</v>
+        <v>176.3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:07:24</t>
+          <t>09:05:06</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="F74" t="n">
-        <v>4.97</v>
+        <v>6.21</v>
       </c>
       <c r="G74" t="n">
-        <v>220.7</v>
+        <v>237.2</v>
       </c>
       <c r="H74" t="n">
-        <v>64.2</v>
+        <v>53.2</v>
       </c>
       <c r="I74" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="J74" t="n">
-        <v>31.36</v>
+        <v>14.95</v>
       </c>
       <c r="K74" t="n">
-        <v>13.7</v>
+        <v>-29.37</v>
       </c>
       <c r="L74" t="n">
-        <v>34.22</v>
+        <v>32.96</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:09:51</t>
+          <t>09:06:20</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="F75" t="n">
         <v>6.21</v>
       </c>
       <c r="G75" t="n">
-        <v>231.9</v>
+        <v>237.8</v>
       </c>
       <c r="H75" t="n">
-        <v>14.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="I75" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="J75" t="n">
-        <v>-34.87</v>
+        <v>-30.06</v>
       </c>
       <c r="K75" t="n">
-        <v>-4.31</v>
+        <v>-27.2</v>
       </c>
       <c r="L75" t="n">
-        <v>35.14</v>
+        <v>40.54</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:11:56</t>
+          <t>09:08:18</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="F76" t="n">
-        <v>2.09</v>
+        <v>6.21</v>
       </c>
       <c r="G76" t="n">
-        <v>232.1</v>
+        <v>236.7</v>
       </c>
       <c r="H76" t="n">
-        <v>27.8</v>
+        <v>14.8</v>
       </c>
       <c r="I76" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J76" t="n">
-        <v>-15.75</v>
+        <v>-28.43</v>
       </c>
       <c r="K76" t="n">
-        <v>30.42</v>
+        <v>-28.34</v>
       </c>
       <c r="L76" t="n">
-        <v>34.26</v>
+        <v>40.14</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:17:20</t>
+          <t>09:13:19</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>1.94</v>
+        <v>2.95</v>
       </c>
       <c r="F77" t="n">
-        <v>5.61</v>
+        <v>6.21</v>
       </c>
       <c r="G77" t="n">
-        <v>224.1</v>
+        <v>219.7</v>
       </c>
       <c r="H77" t="n">
-        <v>20.4</v>
+        <v>15.8</v>
       </c>
       <c r="I77" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>-55.01</v>
+        <v>71.75</v>
       </c>
       <c r="K77" t="n">
-        <v>13.36</v>
+        <v>-6.18</v>
       </c>
       <c r="L77" t="n">
-        <v>56.61</v>
+        <v>72.01000000000001</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:19:17</t>
+          <t>09:14:17</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="F78" t="n">
-        <v>2.37</v>
+        <v>3.6</v>
       </c>
       <c r="G78" t="n">
-        <v>235.8</v>
+        <v>221.9</v>
       </c>
       <c r="H78" t="n">
-        <v>55.6</v>
+        <v>42.7</v>
       </c>
       <c r="I78" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>-15.2</v>
+        <v>-28.37</v>
       </c>
       <c r="K78" t="n">
-        <v>-52.53</v>
+        <v>37.78</v>
       </c>
       <c r="L78" t="n">
-        <v>54.69</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:20:22</t>
+          <t>09:16:36</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="F79" t="n">
-        <v>6.21</v>
+        <v>5.53</v>
       </c>
       <c r="G79" t="n">
-        <v>233.9</v>
+        <v>221.1</v>
       </c>
       <c r="H79" t="n">
-        <v>69.8</v>
+        <v>44.6</v>
       </c>
       <c r="I79" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>21.23</v>
+        <v>47.16</v>
       </c>
       <c r="K79" t="n">
-        <v>-42.21</v>
+        <v>-11.4</v>
       </c>
       <c r="L79" t="n">
-        <v>47.25</v>
+        <v>48.51</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:26:39</t>
+          <t>09:22:19</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>1.46</v>
+        <v>1.69</v>
       </c>
       <c r="F80" t="n">
-        <v>5.48</v>
+        <v>5.21</v>
       </c>
       <c r="G80" t="n">
-        <v>219</v>
+        <v>234.6</v>
       </c>
       <c r="H80" t="n">
-        <v>71.7</v>
+        <v>41.5</v>
       </c>
       <c r="I80" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="J80" t="n">
-        <v>-93.34999999999999</v>
+        <v>-58.31</v>
       </c>
       <c r="K80" t="n">
-        <v>7.88</v>
+        <v>37.18</v>
       </c>
       <c r="L80" t="n">
-        <v>93.68000000000001</v>
+        <v>69.16</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:27:48</t>
+          <t>09:23:27</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="F81" t="n">
-        <v>6.21</v>
+        <v>5.91</v>
       </c>
       <c r="G81" t="n">
-        <v>238.5</v>
+        <v>227.3</v>
       </c>
       <c r="H81" t="n">
-        <v>37.4</v>
+        <v>61.6</v>
       </c>
       <c r="I81" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J81" t="n">
-        <v>-41.6</v>
+        <v>6.7</v>
       </c>
       <c r="K81" t="n">
-        <v>-91.48999999999999</v>
+        <v>91.20999999999999</v>
       </c>
       <c r="L81" t="n">
-        <v>100.5</v>
+        <v>91.45999999999999</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:29:04</t>
+          <t>09:24:34</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="F82" t="n">
-        <v>6.21</v>
+        <v>5.14</v>
       </c>
       <c r="G82" t="n">
-        <v>237</v>
+        <v>234.9</v>
       </c>
       <c r="H82" t="n">
-        <v>34.8</v>
+        <v>65</v>
       </c>
       <c r="I82" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J82" t="n">
-        <v>36.69</v>
+        <v>-27.87</v>
       </c>
       <c r="K82" t="n">
-        <v>-76.22</v>
+        <v>-71.06</v>
       </c>
       <c r="L82" t="n">
-        <v>84.59</v>
+        <v>76.33</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:33:47</t>
+          <t>09:29:38</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>1.66</v>
+        <v>1.94</v>
       </c>
       <c r="F83" t="n">
         <v>6.21</v>
       </c>
       <c r="G83" t="n">
-        <v>232</v>
+        <v>218.5</v>
       </c>
       <c r="H83" t="n">
-        <v>54.3</v>
+        <v>26.4</v>
       </c>
       <c r="I83" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-3.04</v>
+        <v>-60.83</v>
       </c>
       <c r="K83" t="n">
-        <v>-108.54</v>
+        <v>-18.16</v>
       </c>
       <c r="L83" t="n">
-        <v>108.58</v>
+        <v>63.49</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:35:56</t>
+          <t>09:31:20</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="F84" t="n">
         <v>6.21</v>
       </c>
       <c r="G84" t="n">
-        <v>222.8</v>
+        <v>246.3</v>
       </c>
       <c r="H84" t="n">
-        <v>36.4</v>
+        <v>54.1</v>
       </c>
       <c r="I84" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>-116.91</v>
+        <v>-41.73</v>
       </c>
       <c r="K84" t="n">
-        <v>70.89</v>
+        <v>105.06</v>
       </c>
       <c r="L84" t="n">
-        <v>136.73</v>
+        <v>113.04</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:37:39</t>
+          <t>09:32:52</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>1.9</v>
+        <v>1.43</v>
       </c>
       <c r="F85" t="n">
-        <v>4.38</v>
+        <v>1.73</v>
       </c>
       <c r="G85" t="n">
-        <v>226.1</v>
+        <v>229.7</v>
       </c>
       <c r="H85" t="n">
-        <v>40.1</v>
+        <v>23.7</v>
       </c>
       <c r="I85" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J85" t="n">
-        <v>-36.46</v>
+        <v>78.83</v>
       </c>
       <c r="K85" t="n">
-        <v>109.53</v>
+        <v>-3.83</v>
       </c>
       <c r="L85" t="n">
-        <v>115.43</v>
+        <v>78.92</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:42:19</t>
+          <t>09:36:15</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="F86" t="n">
-        <v>5.93</v>
+        <v>5.73</v>
       </c>
       <c r="G86" t="n">
-        <v>231.2</v>
+        <v>232.7</v>
       </c>
       <c r="H86" t="n">
-        <v>74.40000000000001</v>
+        <v>31.6</v>
       </c>
       <c r="I86" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J86" t="n">
-        <v>-150.98</v>
+        <v>-152.06</v>
       </c>
       <c r="K86" t="n">
-        <v>-62.25</v>
+        <v>77.8</v>
       </c>
       <c r="L86" t="n">
-        <v>163.31</v>
+        <v>170.8</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:43:29</t>
+          <t>09:37:39</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="F87" t="n">
         <v>6.21</v>
       </c>
       <c r="G87" t="n">
-        <v>231.4</v>
+        <v>212.4</v>
       </c>
       <c r="H87" t="n">
-        <v>25.8</v>
+        <v>48.7</v>
       </c>
       <c r="I87" t="n">
         <v>29</v>
       </c>
       <c r="J87" t="n">
-        <v>-153.25</v>
+        <v>36.02</v>
       </c>
       <c r="K87" t="n">
-        <v>-45.01</v>
+        <v>-156.47</v>
       </c>
       <c r="L87" t="n">
-        <v>159.72</v>
+        <v>160.57</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:44:27</t>
+          <t>09:40:01</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>1.87</v>
+        <v>1.43</v>
       </c>
       <c r="F88" t="n">
-        <v>6.21</v>
+        <v>4.41</v>
       </c>
       <c r="G88" t="n">
-        <v>231.6</v>
+        <v>230.2</v>
       </c>
       <c r="H88" t="n">
-        <v>64.90000000000001</v>
+        <v>24.8</v>
       </c>
       <c r="I88" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="J88" t="n">
-        <v>-160.08</v>
+        <v>63.74</v>
       </c>
       <c r="K88" t="n">
-        <v>-65.25</v>
+        <v>108.7</v>
       </c>
       <c r="L88" t="n">
-        <v>172.87</v>
+        <v>126.01</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-08-25.xlsx
+++ b/output/2024-08-25.xlsx
@@ -640,13 +640,13 @@
         <v>29</v>
       </c>
       <c r="J14" t="n">
-        <v>23.47</v>
+        <v>23.13</v>
       </c>
       <c r="K14" t="n">
-        <v>-25.76</v>
+        <v>-25.39</v>
       </c>
       <c r="L14" t="n">
-        <v>34.85</v>
+        <v>34.35</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>27</v>
       </c>
       <c r="J15" t="n">
-        <v>-13.97</v>
+        <v>-12.82</v>
       </c>
       <c r="K15" t="n">
-        <v>46.51</v>
+        <v>42.68</v>
       </c>
       <c r="L15" t="n">
-        <v>48.57</v>
+        <v>44.56</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>27</v>
       </c>
       <c r="J16" t="n">
-        <v>33.85</v>
+        <v>33.38</v>
       </c>
       <c r="K16" t="n">
-        <v>9.119999999999999</v>
+        <v>9</v>
       </c>
       <c r="L16" t="n">
-        <v>35.05</v>
+        <v>34.57</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>-33.04</v>
+        <v>-34.43</v>
       </c>
       <c r="K17" t="n">
-        <v>-36.49</v>
+        <v>-38.03</v>
       </c>
       <c r="L17" t="n">
-        <v>49.23</v>
+        <v>51.29</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>24</v>
       </c>
       <c r="J18" t="n">
-        <v>-62.92</v>
+        <v>-58.94</v>
       </c>
       <c r="K18" t="n">
-        <v>-34.23</v>
+        <v>-32.06</v>
       </c>
       <c r="L18" t="n">
-        <v>71.63</v>
+        <v>67.09999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>41.93</v>
+        <v>42.24</v>
       </c>
       <c r="K19" t="n">
-        <v>26.19</v>
+        <v>26.38</v>
       </c>
       <c r="L19" t="n">
-        <v>49.43</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>60.99</v>
+        <v>66.28</v>
       </c>
       <c r="K20" t="n">
-        <v>30.68</v>
+        <v>33.34</v>
       </c>
       <c r="L20" t="n">
-        <v>68.27</v>
+        <v>74.19</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>23</v>
       </c>
       <c r="J21" t="n">
-        <v>64.04000000000001</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>-25.6</v>
+        <v>-28.72</v>
       </c>
       <c r="L21" t="n">
-        <v>68.97</v>
+        <v>77.37</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>37.98</v>
+        <v>39.94</v>
       </c>
       <c r="K22" t="n">
-        <v>62.51</v>
+        <v>65.73</v>
       </c>
       <c r="L22" t="n">
-        <v>73.14</v>
+        <v>76.91</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>28</v>
       </c>
       <c r="J23" t="n">
-        <v>-17.75</v>
+        <v>-20.65</v>
       </c>
       <c r="K23" t="n">
-        <v>-80.59</v>
+        <v>-93.73999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>82.53</v>
+        <v>95.98999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>28</v>
       </c>
       <c r="J24" t="n">
-        <v>-74.53</v>
+        <v>-80.51000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>68.34</v>
+        <v>73.81999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>101.12</v>
+        <v>109.23</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>-130.04</v>
+        <v>-132.38</v>
       </c>
       <c r="K25" t="n">
-        <v>-92.70999999999999</v>
+        <v>-94.37</v>
       </c>
       <c r="L25" t="n">
-        <v>159.7</v>
+        <v>162.57</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>29</v>
       </c>
       <c r="J26" t="n">
-        <v>123.82</v>
+        <v>140.99</v>
       </c>
       <c r="K26" t="n">
-        <v>31.51</v>
+        <v>35.88</v>
       </c>
       <c r="L26" t="n">
-        <v>127.76</v>
+        <v>145.48</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>-98.2</v>
+        <v>-113.8</v>
       </c>
       <c r="K27" t="n">
-        <v>113.49</v>
+        <v>131.53</v>
       </c>
       <c r="L27" t="n">
-        <v>150.08</v>
+        <v>173.93</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>-136.01</v>
+        <v>-153.82</v>
       </c>
       <c r="K28" t="n">
-        <v>-84.34</v>
+        <v>-95.38</v>
       </c>
       <c r="L28" t="n">
-        <v>160.04</v>
+        <v>180.99</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>29</v>
       </c>
       <c r="J29" t="n">
-        <v>24.7</v>
+        <v>24.79</v>
       </c>
       <c r="K29" t="n">
-        <v>20.43</v>
+        <v>20.51</v>
       </c>
       <c r="L29" t="n">
-        <v>32.06</v>
+        <v>32.18</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>44.64</v>
+        <v>42.05</v>
       </c>
       <c r="K30" t="n">
-        <v>-23.24</v>
+        <v>-21.89</v>
       </c>
       <c r="L30" t="n">
-        <v>50.33</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>-42.96</v>
+        <v>-39.54</v>
       </c>
       <c r="K31" t="n">
-        <v>29.27</v>
+        <v>26.94</v>
       </c>
       <c r="L31" t="n">
-        <v>51.99</v>
+        <v>47.85</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>7.66</v>
+        <v>7.88</v>
       </c>
       <c r="K32" t="n">
-        <v>-47.56</v>
+        <v>-48.94</v>
       </c>
       <c r="L32" t="n">
-        <v>48.18</v>
+        <v>49.57</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>-68.94</v>
+        <v>-63.15</v>
       </c>
       <c r="K33" t="n">
-        <v>-24.43</v>
+        <v>-22.38</v>
       </c>
       <c r="L33" t="n">
-        <v>73.14</v>
+        <v>67</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>28</v>
       </c>
       <c r="J34" t="n">
-        <v>61.12</v>
+        <v>56.49</v>
       </c>
       <c r="K34" t="n">
-        <v>22.7</v>
+        <v>20.98</v>
       </c>
       <c r="L34" t="n">
-        <v>65.2</v>
+        <v>60.26</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>28.61</v>
+        <v>30.14</v>
       </c>
       <c r="K35" t="n">
-        <v>-77.16</v>
+        <v>-81.28</v>
       </c>
       <c r="L35" t="n">
-        <v>82.29000000000001</v>
+        <v>86.69</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>27</v>
       </c>
       <c r="J36" t="n">
-        <v>42.29</v>
+        <v>44.74</v>
       </c>
       <c r="K36" t="n">
-        <v>-52.5</v>
+        <v>-55.54</v>
       </c>
       <c r="L36" t="n">
-        <v>67.41</v>
+        <v>71.31999999999999</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>-29.4</v>
+        <v>-29.78</v>
       </c>
       <c r="K37" t="n">
-        <v>84.44</v>
+        <v>85.52</v>
       </c>
       <c r="L37" t="n">
-        <v>89.41</v>
+        <v>90.56</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-122.18</v>
+        <v>-127.13</v>
       </c>
       <c r="K38" t="n">
-        <v>55.97</v>
+        <v>58.24</v>
       </c>
       <c r="L38" t="n">
-        <v>134.39</v>
+        <v>139.83</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>52.78</v>
+        <v>58.91</v>
       </c>
       <c r="K39" t="n">
-        <v>91.01000000000001</v>
+        <v>101.58</v>
       </c>
       <c r="L39" t="n">
-        <v>105.21</v>
+        <v>117.43</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>29</v>
       </c>
       <c r="J40" t="n">
-        <v>57.01</v>
+        <v>63.57</v>
       </c>
       <c r="K40" t="n">
-        <v>69.11</v>
+        <v>77.06999999999999</v>
       </c>
       <c r="L40" t="n">
-        <v>89.59</v>
+        <v>99.91</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>98.2</v>
+        <v>110.76</v>
       </c>
       <c r="K41" t="n">
-        <v>-106.9</v>
+        <v>-120.56</v>
       </c>
       <c r="L41" t="n">
-        <v>145.16</v>
+        <v>163.72</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>26</v>
       </c>
       <c r="J42" t="n">
-        <v>11.6</v>
+        <v>11.83</v>
       </c>
       <c r="K42" t="n">
-        <v>-229.23</v>
+        <v>-233.76</v>
       </c>
       <c r="L42" t="n">
-        <v>229.52</v>
+        <v>234.06</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>-27.03</v>
+        <v>-33.12</v>
       </c>
       <c r="K43" t="n">
-        <v>-116.7</v>
+        <v>-142.99</v>
       </c>
       <c r="L43" t="n">
-        <v>119.79</v>
+        <v>146.78</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>-8.210000000000001</v>
+        <v>-8.08</v>
       </c>
       <c r="K44" t="n">
-        <v>37.44</v>
+        <v>36.86</v>
       </c>
       <c r="L44" t="n">
-        <v>38.33</v>
+        <v>37.73</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>11.67</v>
+        <v>12.56</v>
       </c>
       <c r="K45" t="n">
-        <v>28.66</v>
+        <v>30.85</v>
       </c>
       <c r="L45" t="n">
-        <v>30.94</v>
+        <v>33.31</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>28</v>
       </c>
       <c r="J46" t="n">
-        <v>13.19</v>
+        <v>12.44</v>
       </c>
       <c r="K46" t="n">
-        <v>-45.79</v>
+        <v>-43.19</v>
       </c>
       <c r="L46" t="n">
-        <v>47.65</v>
+        <v>44.95</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>24</v>
       </c>
       <c r="J47" t="n">
-        <v>34.48</v>
+        <v>32.85</v>
       </c>
       <c r="K47" t="n">
-        <v>-65.72</v>
+        <v>-62.61</v>
       </c>
       <c r="L47" t="n">
-        <v>74.22</v>
+        <v>70.7</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>29</v>
       </c>
       <c r="J48" t="n">
-        <v>-39.05</v>
+        <v>-39.34</v>
       </c>
       <c r="K48" t="n">
-        <v>9.300000000000001</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="L48" t="n">
-        <v>40.14</v>
+        <v>40.44</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>45.07</v>
+        <v>46.19</v>
       </c>
       <c r="K49" t="n">
-        <v>-22.16</v>
+        <v>-22.71</v>
       </c>
       <c r="L49" t="n">
-        <v>50.23</v>
+        <v>51.47</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>45.76</v>
+        <v>48.57</v>
       </c>
       <c r="K50" t="n">
-        <v>-64.77</v>
+        <v>-68.75</v>
       </c>
       <c r="L50" t="n">
-        <v>79.3</v>
+        <v>84.18000000000001</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>56.79</v>
+        <v>58.31</v>
       </c>
       <c r="K51" t="n">
-        <v>-65.43000000000001</v>
+        <v>-67.18000000000001</v>
       </c>
       <c r="L51" t="n">
-        <v>86.64</v>
+        <v>88.95</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>-42.88</v>
+        <v>-46.04</v>
       </c>
       <c r="K52" t="n">
-        <v>53.18</v>
+        <v>57.1</v>
       </c>
       <c r="L52" t="n">
-        <v>68.31</v>
+        <v>73.34999999999999</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>-103.08</v>
+        <v>-114.12</v>
       </c>
       <c r="K53" t="n">
-        <v>-12.62</v>
+        <v>-13.97</v>
       </c>
       <c r="L53" t="n">
-        <v>103.85</v>
+        <v>114.97</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-12.5</v>
+        <v>-13.58</v>
       </c>
       <c r="K54" t="n">
-        <v>123.57</v>
+        <v>134.23</v>
       </c>
       <c r="L54" t="n">
-        <v>124.2</v>
+        <v>134.91</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>-75.67</v>
+        <v>-87.33</v>
       </c>
       <c r="K55" t="n">
-        <v>-47.88</v>
+        <v>-55.27</v>
       </c>
       <c r="L55" t="n">
-        <v>89.55</v>
+        <v>103.35</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>178.12</v>
+        <v>193.63</v>
       </c>
       <c r="K56" t="n">
-        <v>-30.55</v>
+        <v>-33.21</v>
       </c>
       <c r="L56" t="n">
-        <v>180.72</v>
+        <v>196.46</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>-157.62</v>
+        <v>-171.26</v>
       </c>
       <c r="K57" t="n">
-        <v>-90.79000000000001</v>
+        <v>-98.64</v>
       </c>
       <c r="L57" t="n">
-        <v>181.9</v>
+        <v>197.64</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>149.79</v>
+        <v>168.12</v>
       </c>
       <c r="K58" t="n">
-        <v>48</v>
+        <v>53.88</v>
       </c>
       <c r="L58" t="n">
-        <v>157.29</v>
+        <v>176.54</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>-26.95</v>
+        <v>-27.54</v>
       </c>
       <c r="K59" t="n">
-        <v>-22.99</v>
+        <v>-23.5</v>
       </c>
       <c r="L59" t="n">
-        <v>35.42</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>28</v>
       </c>
       <c r="J60" t="n">
-        <v>-30.88</v>
+        <v>-29.41</v>
       </c>
       <c r="K60" t="n">
-        <v>-28.43</v>
+        <v>-27.07</v>
       </c>
       <c r="L60" t="n">
-        <v>41.98</v>
+        <v>39.97</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>28</v>
       </c>
       <c r="J61" t="n">
-        <v>35.5</v>
+        <v>33.47</v>
       </c>
       <c r="K61" t="n">
-        <v>31.36</v>
+        <v>29.56</v>
       </c>
       <c r="L61" t="n">
-        <v>47.36</v>
+        <v>44.66</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>36.3</v>
+        <v>36.5</v>
       </c>
       <c r="K62" t="n">
-        <v>37.58</v>
+        <v>37.79</v>
       </c>
       <c r="L62" t="n">
-        <v>52.25</v>
+        <v>52.54</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>29</v>
       </c>
       <c r="J63" t="n">
-        <v>12.24</v>
+        <v>13.07</v>
       </c>
       <c r="K63" t="n">
-        <v>-5.38</v>
+        <v>-5.75</v>
       </c>
       <c r="L63" t="n">
-        <v>13.37</v>
+        <v>14.28</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>37.75</v>
+        <v>36.69</v>
       </c>
       <c r="K64" t="n">
-        <v>56.83</v>
+        <v>55.24</v>
       </c>
       <c r="L64" t="n">
-        <v>68.23</v>
+        <v>66.31</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>68.37</v>
+        <v>73</v>
       </c>
       <c r="K65" t="n">
-        <v>-48.49</v>
+        <v>-51.77</v>
       </c>
       <c r="L65" t="n">
-        <v>83.81999999999999</v>
+        <v>89.5</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>27</v>
       </c>
       <c r="J66" t="n">
-        <v>44.45</v>
+        <v>50.21</v>
       </c>
       <c r="K66" t="n">
-        <v>-35.07</v>
+        <v>-39.61</v>
       </c>
       <c r="L66" t="n">
-        <v>56.61</v>
+        <v>63.95</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>-87.2</v>
+        <v>-89.37</v>
       </c>
       <c r="K67" t="n">
-        <v>30.24</v>
+        <v>30.99</v>
       </c>
       <c r="L67" t="n">
-        <v>92.3</v>
+        <v>94.59</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>27</v>
       </c>
       <c r="J68" t="n">
-        <v>-76.79000000000001</v>
+        <v>-86.68000000000001</v>
       </c>
       <c r="K68" t="n">
-        <v>-46.35</v>
+        <v>-52.32</v>
       </c>
       <c r="L68" t="n">
-        <v>89.7</v>
+        <v>101.25</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>28</v>
       </c>
       <c r="J69" t="n">
-        <v>-103.02</v>
+        <v>-112.9</v>
       </c>
       <c r="K69" t="n">
-        <v>3.47</v>
+        <v>3.8</v>
       </c>
       <c r="L69" t="n">
-        <v>103.08</v>
+        <v>112.96</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>-20.15</v>
+        <v>-21.46</v>
       </c>
       <c r="K70" t="n">
-        <v>126.7</v>
+        <v>134.95</v>
       </c>
       <c r="L70" t="n">
-        <v>128.29</v>
+        <v>136.65</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>16.77</v>
+        <v>19.96</v>
       </c>
       <c r="K71" t="n">
-        <v>-136.14</v>
+        <v>-161.98</v>
       </c>
       <c r="L71" t="n">
-        <v>137.17</v>
+        <v>163.2</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>28</v>
       </c>
       <c r="J72" t="n">
-        <v>135.16</v>
+        <v>149.27</v>
       </c>
       <c r="K72" t="n">
-        <v>108.01</v>
+        <v>119.29</v>
       </c>
       <c r="L72" t="n">
-        <v>173.01</v>
+        <v>191.08</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>29</v>
       </c>
       <c r="J73" t="n">
-        <v>-155.02</v>
+        <v>-170.56</v>
       </c>
       <c r="K73" t="n">
-        <v>42.58</v>
+        <v>46.85</v>
       </c>
       <c r="L73" t="n">
-        <v>160.76</v>
+        <v>176.87</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>29</v>
       </c>
       <c r="J74" t="n">
-        <v>7.81</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="K74" t="n">
-        <v>-28.8</v>
+        <v>-30.01</v>
       </c>
       <c r="L74" t="n">
-        <v>29.84</v>
+        <v>31.09</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="K75" t="n">
-        <v>-41.57</v>
+        <v>-40.14</v>
       </c>
       <c r="L75" t="n">
-        <v>41.59</v>
+        <v>40.16</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>30.83</v>
+        <v>30.94</v>
       </c>
       <c r="K76" t="n">
-        <v>-21.21</v>
+        <v>-21.28</v>
       </c>
       <c r="L76" t="n">
-        <v>37.42</v>
+        <v>37.55</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>54.56</v>
+        <v>54.95</v>
       </c>
       <c r="K77" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="L77" t="n">
-        <v>54.62</v>
+        <v>55.01</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>29</v>
       </c>
       <c r="J78" t="n">
-        <v>-7.43</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="K78" t="n">
-        <v>-26.67</v>
+        <v>-29.75</v>
       </c>
       <c r="L78" t="n">
-        <v>27.68</v>
+        <v>30.88</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>28</v>
       </c>
       <c r="J79" t="n">
-        <v>-58.31</v>
+        <v>-59.22</v>
       </c>
       <c r="K79" t="n">
-        <v>-27.18</v>
+        <v>-27.6</v>
       </c>
       <c r="L79" t="n">
-        <v>64.34</v>
+        <v>65.34</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>63.47</v>
+        <v>63.56</v>
       </c>
       <c r="K80" t="n">
-        <v>-69.13</v>
+        <v>-69.23999999999999</v>
       </c>
       <c r="L80" t="n">
-        <v>93.84999999999999</v>
+        <v>93.98999999999999</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>-11.41</v>
+        <v>-12.06</v>
       </c>
       <c r="K81" t="n">
-        <v>-79.31</v>
+        <v>-83.86</v>
       </c>
       <c r="L81" t="n">
-        <v>80.13</v>
+        <v>84.72</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>23</v>
       </c>
       <c r="J82" t="n">
-        <v>80.29000000000001</v>
+        <v>77.5</v>
       </c>
       <c r="K82" t="n">
-        <v>101.01</v>
+        <v>97.48999999999999</v>
       </c>
       <c r="L82" t="n">
-        <v>129.03</v>
+        <v>124.54</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>-114.62</v>
+        <v>-117.08</v>
       </c>
       <c r="K83" t="n">
-        <v>-81.34999999999999</v>
+        <v>-83.09</v>
       </c>
       <c r="L83" t="n">
-        <v>140.56</v>
+        <v>143.57</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>-90.38</v>
+        <v>-102.98</v>
       </c>
       <c r="K84" t="n">
-        <v>-26.65</v>
+        <v>-30.37</v>
       </c>
       <c r="L84" t="n">
-        <v>94.23</v>
+        <v>107.37</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>-69.75</v>
+        <v>-76.40000000000001</v>
       </c>
       <c r="K85" t="n">
-        <v>-67.52</v>
+        <v>-73.95999999999999</v>
       </c>
       <c r="L85" t="n">
-        <v>97.08</v>
+        <v>106.34</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>-96.28</v>
+        <v>-109.38</v>
       </c>
       <c r="K86" t="n">
-        <v>113.26</v>
+        <v>128.66</v>
       </c>
       <c r="L86" t="n">
-        <v>148.66</v>
+        <v>168.87</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>-87.14</v>
+        <v>-95.55</v>
       </c>
       <c r="K87" t="n">
-        <v>-180.27</v>
+        <v>-197.66</v>
       </c>
       <c r="L87" t="n">
-        <v>200.23</v>
+        <v>219.54</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>181.18</v>
+        <v>187.48</v>
       </c>
       <c r="K88" t="n">
-        <v>-191.77</v>
+        <v>-198.44</v>
       </c>
       <c r="L88" t="n">
-        <v>263.82</v>
+        <v>273</v>
       </c>
     </row>
   </sheetData>
